--- a/analysis_three_runs.xlsx
+++ b/analysis_three_runs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\desktop\pdfbisai\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\desktop\multimodal_table_recognition\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B5B42AD-F464-435B-A6CE-21017E746F3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2C420AC-25C4-4382-ACED-F8144C7251B3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="25824" windowHeight="15504" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="一致497" sheetId="1" r:id="rId1"/>
@@ -5373,628 +5373,629 @@
     <t>请按表中顺序列出以下字段的答案：中标价、工期、项目经理、合同签订时间。</t>
   </si>
   <si>
+    <t>["10.41%","合同签订之日起至2024年12月31日，具体项目及工期按每个项目施工合同中确定","['王永平', '梁卫凤', '胡浙明']","2023年4月12日"]</t>
+  </si>
+  <si>
+    <t>["10.41%","合同签订之日起至2024年12月31日，具体项目及工期按每个项目施工合同中确定","王永平","梁卫凤","胡浙明","2023年4月12日"]</t>
+  </si>
+  <si>
+    <t>杨周</t>
+  </si>
+  <si>
+    <t>Number of passengers 乘车人数</t>
+  </si>
+  <si>
+    <t>Pick-Up Locations 接送地点</t>
+  </si>
+  <si>
+    <t>中英混合</t>
+  </si>
+  <si>
+    <t>Iron 2%</t>
+  </si>
+  <si>
+    <t>Amount Per Serving</t>
+  </si>
+  <si>
+    <t>Iron</t>
+  </si>
+  <si>
+    <t>% Daily Value</t>
+  </si>
+  <si>
+    <t>% RP % AR</t>
+  </si>
+  <si>
+    <t>% RI* % AR**</t>
+  </si>
+  <si>
+    <t>% RI* % AR*</t>
+  </si>
+  <si>
+    <t>请提取“套餐分类之一”对应的值。</t>
+  </si>
+  <si>
+    <t>酷睿i7-8750H 8G DDR4</t>
+  </si>
+  <si>
+    <t>官方标配(原封)</t>
+  </si>
+  <si>
+    <t>家庭版</t>
+  </si>
+  <si>
+    <t>请按表中顺序列出以下字段的答案：最低活动价、最高活动价、备注中是否含退换规则、表格下方说明条数。</t>
+  </si>
+  <si>
+    <t>["20299","59999","true","3"]</t>
+  </si>
+  <si>
+    <t>[399,79999,"否",3]</t>
+  </si>
+  <si>
+    <t>[399,79999,"是",3]</t>
+  </si>
+  <si>
+    <t>包含蓝色标签的模块一共有多少个？</t>
+  </si>
+  <si>
+    <t>英伟达</t>
+  </si>
+  <si>
+    <t>澎湃·美数课</t>
+  </si>
+  <si>
+    <t>CEO总薪酬</t>
+  </si>
+  <si>
+    <t>请恢复 59.pdf 中“Table 6 DeepSeek-V4-Pro-Max 与其他模型对比”的表头行结构。</t>
+  </si>
+  <si>
+    <t>{"row_count":1,"col_count":7,"cells":[{"text":"Benchmark (Metric)","row":0,"col":0,"rowspan":1,"colspan":1},{"text":"Opus-4.6 Max","row":0,"col":1,"rowspan":1,"colspan":1},{"text":"GPT-5.4 xHigh","row":0,"col":2,"rowspan":1,"colspan":1},{"text":"Gemini-3.1-Pro High","row":0,"col":3,"rowspan":1,"colspan":1},{"text":"K2.6 Thinking","row":0,"col":4,"rowspan":1,"colspan":1},{"text":"GLM-5.1 Thinking","row":0,"col":5,"rowspan":1,"colspan":1},{"text":"DS-V4-Pro Max","row":0,"col":6,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>{"row_count":24,"col_count":7,"cells":[{"text":"Benchmark (Metric)","row":0,"col":0,"rowspan":2,"colspan":1},{"text":"Opus-4.6","row":0,"col":1,"rowspan":1,"colspan":1},{"text":"GPT-5.4","row":0,"col":2,"rowspan":1,"colspan":1},{"text":"Gemini-3.1-Pro","row":0,"col":3,"rowspan":1,"colspan":1},{"text":"K2.6","row":0,"col":4,"rowspan":1,"colspan":1},{"text":"GLM-5.1","row":0,"col":5,"rowspan":1,"colspan":1},{"text":"DS-V4-Pro","row":0,"col":6,"rowspan":1,"colspan":1},{"text":"Max","row":1,"col":1,"rowspan":1,"colspan":1},{"text":"xHigh","row":1,"col":2,"rowspan":1,"colspan":1},{"text":"High","row":1,"col":3,"rowspan":1,"colspan":1},{"text":"Thinking","row":1,"col":4,"rowspan":1,"colspan":1},{"text":"Thinking","row":1,"col":5,"rowspan":1,"colspan":1},{"text":"Max","row":1,"col":6,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>{"row_count":23,"col_count":8,"cells":[{"text":"Benchmark (Metric)","row":0,"col":0,"rowspan":1,"colspan":2},{"text":"Opus-4.6 Max","row":0,"col":2,"rowspan":1,"colspan":1},{"text":"GPT-5.4 xHigh","row":0,"col":3,"rowspan":1,"colspan":1},{"text":"Gemini-3.1-Pro High","row":0,"col":4,"rowspan":1,"colspan":1},{"text":"K2.6 Thinking","row":0,"col":5,"rowspan":1,"colspan":1},{"text":"GLM-5.1 Thinking","row":0,"col":6,"rowspan":1,"colspan":1},{"text":"DS-V4-Pro Max","row":0,"col":7,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>请从 61.pdf 的“Table 12 中文功能写作评估”中提取：Business Writing 的 Subtotal 行。</t>
+  </si>
+  <si>
+    <t>["Business Writing","Subtotal (小计)",1349,879,436,34,"65.16","32.32","2.52"]</t>
+  </si>
+  <si>
+    <t>["Subtotal (小计)","1349","879","436","34","65.16","32.32","2.52"]</t>
+  </si>
+  <si>
+    <t>["Subtotal (小计)",1349,879,436,34,"65.16","32.32","2.52"]</t>
+  </si>
+  <si>
+    <t>["Subtotal (小计)",1349,879,436,34,65.16,32.32,2.52]</t>
+  </si>
+  <si>
+    <t>请恢复 62.pdf 中“Table 13 中文创意写作评估”的表头行结构。</t>
+  </si>
+  <si>
+    <t>{"row_count":3,"col_count":14,"cells":[{"text":"Subcategory (文体)","row":0,"col":0,"rowspan":2,"colspan":1},{"text":"#","row":0,"col":1,"rowspan":2,"colspan":1},{"text":"Instruction Following(指令遵循)","row":0,"col":2,"rowspan":1,"colspan":6},{"text":"Writing Quality (写作质量)","row":0,"col":8,"rowspan":1,"colspan":6},{"text":"DS","row":1,"col":2,"rowspan":1,"colspan":1},{"text":"Gem","row":1,"col":3,"rowspan":1,"colspan":1},{"text":"Tie","row":1,"col":4,"rowspan":1,"colspan":1},{"text":"DS%","row":1,"col":5,"rowspan":1,"colspan":1},{"text":"Gem%","row":1,"col":6,"rowspan":1,"colspan":1},{"text":"Tie%","row":1,"col":7,"rowspan":1,"colspan":1},{"text":"DS","row":1,"col":8,"rowspan":1,"colspan":1},{"text":"Gem","row":1,"col":9,"rowspan":1,"colspan":1},{"text":"Tie","row":1,"col":10,"rowspan":1,"colspan":1},{"text":"DS%","row":1,"col":11,"rowspan":1,"colspan":1},{"text":"Gem%","row":1,"col":12,"rowspan":1,"colspan":1},{"text":"Tie%","row":1,"col":13,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>{"row_count":20,"col_count":14,"cells":[{"text":"Subcategory (文体)","row":0,"col":0,"rowspan":2,"colspan":1},{"text":"#","row":0,"col":1,"rowspan":2,"colspan":1},{"text":"Instruction Following(指令遵循)","row":0,"col":2,"rowspan":1,"colspan":6},{"text":"Writing Quality (写作质量)","row":0,"col":8,"rowspan":1,"colspan":6},{"text":"DS","row":1,"col":2,"rowspan":1,"colspan":1},{"text":"Gem","row":1,"col":3,"rowspan":1,"colspan":1},{"text":"Tie","row":1,"col":4,"rowspan":1,"colspan":1},{"text":"DS%","row":1,"col":5,"rowspan":1,"colspan":1},{"text":"Gem%","row":1,"col":6,"rowspan":1,"colspan":1},{"text":"Tie%","row":1,"col":7,"rowspan":1,"colspan":1},{"text":"DS","row":1,"col":8,"rowspan":1,"colspan":1},{"text":"Gem","row":1,"col":9,"rowspan":1,"colspan":1},{"text":"Tie","row":1,"col":10,"rowspan":1,"colspan":1},{"text":"DS%","row":1,"col":11,"rowspan":1,"colspan":1},{"text":"Gem%","row":1,"col":12,"rowspan":1,"colspan":1},{"text":"Tie%","row":1,"col":13,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>{"row_count":21,"col_count":14,"cells":[{"text":"Subcategory (文体)","row":0,"col":0,"rowspan":2,"colspan":1},{"text":"#","row":0,"col":1,"rowspan":2,"colspan":1},{"text":"Instruction Following(指令遵循)","row":0,"col":2,"rowspan":1,"colspan":6},{"text":"Writing Quality (写作质量)","row":0,"col":8,"rowspan":1,"colspan":6},{"text":"DS","row":1,"col":2,"rowspan":1,"colspan":1},{"text":"Gem","row":1,"col":3,"rowspan":1,"colspan":1},{"text":"Tie","row":1,"col":4,"rowspan":1,"colspan":1},{"text":"DS%","row":1,"col":5,"rowspan":1,"colspan":1},{"text":"Gem%","row":1,"col":6,"rowspan":1,"colspan":1},{"text":"Tie%","row":1,"col":7,"rowspan":1,"colspan":1},{"text":"DS","row":1,"col":8,"rowspan":1,"colspan":1},{"text":"Gem","row":1,"col":9,"rowspan":1,"colspan":1},{"text":"Tie","row":1,"col":10,"rowspan":1,"colspan":1},{"text":"DS%","row":1,"col":11,"rowspan":1,"colspan":1},{"text":"Gem%","row":1,"col":12,"rowspan":1,"colspan":1},{"text":"Tie%","row":1,"col":13,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>请从 63.pdf 的“Table 1 catchment site characteristics”中提取：Cathedral Peak 3 (SA) 的 Mean annual rainfall (mm)。</t>
+  </si>
+  <si>
+    <t>1436</t>
+  </si>
+  <si>
+    <t>1134</t>
+  </si>
+  <si>
+    <t>1504</t>
+  </si>
+  <si>
+    <t>请找出 BFI 最高的 catchment。</t>
+  </si>
+  <si>
+    <t>Lambrechbos A (SA)</t>
+  </si>
+  <si>
+    <t>Lambrechbos B (SA)</t>
+  </si>
+  <si>
+    <t>Lambrechthos B (SA)</t>
+  </si>
+  <si>
+    <t>Lambrechtbos B (SA)</t>
+  </si>
+  <si>
+    <t>请从 65.pdf 的“盈利预测和财务指标”中提取：合理估值区间。</t>
+  </si>
+  <si>
+    <t>6.50–7.00 元</t>
+  </si>
+  <si>
+    <t>6.50 - 7.00 元</t>
+  </si>
+  <si>
+    <t>6.50-7.00元</t>
+  </si>
+  <si>
+    <t>请计算 2024-2026 年调整后归母净利润合计。</t>
+  </si>
+  <si>
+    <t>74.6</t>
+  </si>
+  <si>
+    <t>请找出 WTQ 表中 test 最高的模型。</t>
+  </si>
+  <si>
+    <t>TAPAS_LARGE inter-sqa TABLEFORMER_LARGE inter-sqa</t>
+  </si>
+  <si>
+    <t>TABLEFORMER_LARGE inter-sqa</t>
+  </si>
+  <si>
+    <t>TableFormerLarge inter-sqa</t>
+  </si>
+  <si>
+    <t>请恢复 69.pdf 中“Table 1 SQA perturbation results”的表头行结构。</t>
+  </si>
+  <si>
+    <t>{"row_count":3,"col_count":6,"cells":[{"text":"Before Perturb","row":0,"col":0,"rowspan":1,"colspan":3},{"text":"After Perturb","row":0,"col":3,"rowspan":1,"colspan":2},{"text":"ALL","row":1,"col":0,"rowspan":1,"colspan":1},{"text":"SEQ","row":1,"col":1,"rowspan":1,"colspan":1},{"text":"ALL_d","row":1,"col":2,"rowspan":1,"colspan":1},{"text":"ALL","row":1,"col":3,"rowspan":1,"colspan":1},{"text":"VP","row":1,"col":4,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>{"row_count":14,"col_count":6,"cells":[{"text":"Before Perturb","row":0,"col":1,"rowspan":1,"colspan":3},{"text":"After Perturb","row":0,"col":4,"rowspan":1,"colspan":2},{"text":"ALL","row":1,"col":1,"rowspan":1,"colspan":1},{"text":"SEQ","row":1,"col":2,"rowspan":1,"colspan":1},{"text":"ALLd","row":1,"col":3,"rowspan":1,"colspan":1},{"text":"ALL","row":1,"col":4,"rowspan":1,"colspan":1},{"text":"VP","row":1,"col":5,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>{"row_count":14,"col_count":6,"cells":[{"text":"","row":0,"col":0,"rowspan":2,"colspan":1},{"text":"Before Perturb","row":0,"col":1,"rowspan":1,"colspan":3},{"text":"After Perturb","row":0,"col":4,"rowspan":1,"colspan":2},{"text":"ALL","row":1,"col":1,"rowspan":1,"colspan":1},{"text":"SEQ","row":1,"col":2,"rowspan":1,"colspan":1},{"text":"ALL_d","row":1,"col":3,"rowspan":1,"colspan":1},{"text":"ALL","row":1,"col":4,"rowspan":1,"colspan":1},{"text":"VP","row":1,"col":5,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>请找出表中 VP 最高的模型。</t>
+  </si>
+  <si>
+    <t>TAPASBASE inter</t>
+  </si>
+  <si>
+    <t>TAPASLARGE</t>
+  </si>
+  <si>
+    <t>TapasLarge</t>
+  </si>
+  <si>
+    <t>请恢复 70.pdf 中“Table II real-time stereo matching methods”的表头行结构。</t>
+  </si>
+  <si>
+    <t>{"row_count":2,"col_count":5,"cells":[{"text":"Method","row":0,"col":0,"rowspan":1,"colspan":1},{"text":"GPU","row":0,"col":1,"rowspan":1,"colspan":1},{"text":"MDE/s¹","row":0,"col":2,"rowspan":1,"colspan":1},{"text":"FPS²","row":0,"col":3,"rowspan":1,"colspan":1},{"text":"Error³","row":0,"col":4,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>{"row_count":9,"col_count":5,"cells":[{"text":"Method","row":0,"col":0,"rowspan":1,"colspan":1},{"text":"GPU","row":0,"col":1,"rowspan":1,"colspan":1},{"text":"MDE/s1","row":0,"col":2,"rowspan":1,"colspan":1},{"text":"FPS2","row":0,"col":3,"rowspan":1,"colspan":1},{"text":"Error3","row":0,"col":4,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>{"row_count":9,"col_count":5,"cells":[{"text":"Method","row":0,"col":0,"rowspan":1,"colspan":1},{"text":"GPU","row":0,"col":1,"rowspan":1,"colspan":1},{"text":"MDE/s¹","row":0,"col":2,"rowspan":1,"colspan":1},{"text":"FPS²","row":0,"col":3,"rowspan":1,"colspan":1},{"text":"Error³","row":0,"col":4,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>请从 71.pdf 的“表1 工业纯钛、α型和近α型钛合金牌号和化学成分”中提取：TA11 的名义化学成分。</t>
+  </si>
+  <si>
+    <t>Al: 2.0～3.0, Mo: 1.0～2.0, Nb: 0.5～1.5</t>
+  </si>
+  <si>
+    <t>Ti-6.5Al-4.5Sn-2Zr-1Mo-1Nd-0.25Si</t>
+  </si>
+  <si>
+    <t>Ti-8Al-1Mo-1V</t>
+  </si>
+  <si>
+    <t>请从 71.pdf 的“表1 工业纯钛、α型和近α型钛合金牌号和化学成分”中提取：TA14 的 Zr 范围。</t>
+  </si>
+  <si>
+    <t>0.6~1.2</t>
+  </si>
+  <si>
+    <t>0.5~1.5</t>
+  </si>
+  <si>
+    <t>1.5~2.5</t>
+  </si>
+  <si>
+    <t>4.0~6.0</t>
+  </si>
+  <si>
+    <t>请找出该页表头中横跨 Fe、C、N、H、O 的上级栏目名称。</t>
+  </si>
+  <si>
+    <t>主要成分</t>
+  </si>
+  <si>
+    <t>杂质-不大于</t>
+  </si>
+  <si>
+    <t>杂质，不大于</t>
+  </si>
+  <si>
+    <t>杂质,不大于</t>
+  </si>
+  <si>
+    <t>请从 72.pdf 的“表1（续）和表2 β型和近β型钛合金牌号及化学成分”中提取：TB2 的名义化学成分。</t>
+  </si>
+  <si>
+    <t>余量</t>
+  </si>
+  <si>
+    <t>Ti-5Mo-5V-8Cr-3Al</t>
+  </si>
+  <si>
+    <t>Ti-5Mo-5V-8Cr-5Al</t>
+  </si>
+  <si>
+    <t>请从 72.pdf 的“表1（续）和表2 β型和近β型钛合金牌号及化学成分”中提取：TB4 的 Al 范围。</t>
+  </si>
+  <si>
+    <t>2.5～3.5</t>
+  </si>
+  <si>
+    <t>4.5～5.5</t>
+  </si>
+  <si>
+    <t>3.0~4.5</t>
+  </si>
+  <si>
+    <t>3.0～4.5</t>
+  </si>
+  <si>
+    <t>请恢复 73.pdf 中“表2（续）”的表头行结构。</t>
+  </si>
+  <si>
+    <t>{"row_count":3,"col_count":18,"cells":[{"text":"合金牌号","row":0,"col":0,"rowspan":3,"colspan":1},{"text":"名义化学成分","row":0,"col":1,"rowspan":3,"colspan":1},{"text":"主要成分","row":0,"col":2,"rowspan":1,"colspan":14},{"text":"杂质，不大于","row":0,"col":16,"rowspan":1,"colspan":2},{"text":"Ti","row":1,"col":2,"rowspan":2,"colspan":1},{"text":"Al","row":1,"col":3,"rowspan":2,"colspan":1},{"text":"Si","row":1,"col":4,"rowspan":2,"colspan":1},{"text":"V","row":1,"col":5,"rowspan":2,"colspan":1},{"text":"Cr","row":1,"col":6,"rowspan":2,"colspan":1},{"text":"Fe","row":1,"col":7,"rowspan":2,"colspan":1},{"text":"Zr","row":1,"col":8,"rowspan":2,"colspan":1},{"text":"Nb","row":1,"col":9,"rowspan":2,"colspan":1},{"text":"Mo","row":1,"col":10,"rowspan":2,"colspan":1},{"text":"Pd","row":1,"col":11,"rowspan":2,"colspan":1},{"text":"Sn","row":1,"col":12,"rowspan":2,"colspan":1},{"text":"Fe","row":1,"col":13,"rowspan":2,"colspan":1},{"text":"C","row":1,"col":14,"rowspan":2,"colspan":1},{"text":"N","row":1,"col":15,"rowspan":2,"colspan":1},{"text":"H","row":1,"col":16,"rowspan":2,"colspan":1},{"text":"O","row":1,"col":17,"rowspan":2,"colspan":1},{"text":"其他元素","row":2,"col":16,"rowspan":1,"colspan":1},{"text":"单一","row":2,"col":17,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>{"row_count":3,"col_count":20,"cells":[{"text":"合金牌号","row":0,"col":0,"rowspan":2,"colspan":1},{"text":"名义化学成分","row":0,"col":1,"rowspan":2,"colspan":1},{"text":"化学成分(质量分数)/%","row":0,"col":2,"rowspan":1,"colspan":18},{"text":"主要成分","row":1,"col":2,"rowspan":1,"colspan":11},{"text":"杂质,不大于","row":1,"col":13,"rowspan":1,"colspan":5},{"text":"其他元素","row":1,"col":18,"rowspan":1,"colspan":2},{"text":"Ti","row":2,"col":2,"rowspan":1,"colspan":1},{"text":"Al","row":2,"col":3,"rowspan":1,"colspan":1},{"text":"Si","row":2,"col":4,"rowspan":1,"colspan":1},{"text":"V","row":2,"col":5,"rowspan":1,"colspan":1},{"text":"Cr","row":2,"col":6,"rowspan":1,"colspan":1},{"text":"Fe","row":2,"col":7,"rowspan":1,"colspan":1},{"text":"Zr","row":2,"col":8,"rowspan":1,"colspan":1},{"text":"Nb","row":2,"col":9,"rowspan":1,"colspan":1},{"text":"Mo","row":2,"col":10,"rowspan":1,"colspan":1},{"text":"Pd","row":2,"col":11,"rowspan":1,"colspan":1},{"text":"Sn","row":2,"col":12,"rowspan":1,"colspan":1},{"text":"Fe","row":2,"col":13,"rowspan":1,"colspan":1},{"text":"C","row":2,"col":14,"rowspan":1,"colspan":1},{"text":"N","row":2,"col":15,"rowspan":1,"colspan":1},{"text":"H","row":2,"col":16,"rowspan":1,"colspan":1},{"text":"O","row":2,"col":17,"rowspan":1,"colspan":1},{"text":"单一","row":2,"col":18,"rowspan":1,"colspan":1},{"text":"总和","row":2,"col":19,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>{"row_count":17,"col_count":21,"cells":[{"text":"合金牌号","row":0,"col":0,"rowspan":4,"colspan":1},{"text":"名义化学成分","row":0,"col":1,"rowspan":4,"colspan":1},{"text":"化学成分（质量分数）/%","row":0,"col":2,"rowspan":1,"colspan":19},{"text":"主要成分","row":1,"col":2,"rowspan":1,"colspan":12},{"text":"杂质，不大于","row":1,"col":14,"rowspan":1,"colspan":7},{"text":"Ti","row":2,"col":2,"rowspan":2,"colspan":1},{"text":"Al","row":2,"col":3,"rowspan":2,"colspan":1},{"text":"Si","row":2,"col":4,"rowspan":2,"colspan":1},{"text":"V","row":2,"col":5,"rowspan":2,"colspan":1},{"text":"Cr","row":2,"col":6,"rowspan":2,"colspan":1},{"text":"Mn","row":2,"col":7,"rowspan":2,"colspan":1},{"text":"Fe","row":2,"col":8,"rowspan":2,"colspan":1},{"text":"Zr","row":2,"col":9,"rowspan":2,"colspan":1},{"text":"Nb","row":2,"col":10,"rowspan":2,"colspan":1},{"text":"Mo","row":2,"col":11,"rowspan":2,"colspan":1},{"text":"Pd","row":2,"col":12,"rowspan":2,"colspan":1},{"text":"Sn","row":2,"col":13,"rowspan":2,"colspan":1},{"text":"Fe","row":2,"col":14,"rowspan":2,"colspan":1},{"text":"C","row":2,"col":15,"rowspan":2,"colspan":1},{"text":"N","row":2,"col":16,"rowspan":2,"colspan":1},{"text":"H","row":2,"col":17,"rowspan":2,"colspan":1},{"text":"O","row":2,"col":18,"rowspan":2,"colspan":1},{"text":"其他元素","row":2,"col":19,"rowspan":1,"colspan":2},{"text":"单一","row":3,"col":19,"rowspan":1,"colspan":1},{"text":"总和","row":3,"col":20,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>{"row_count":18,"col_count":20,"cells":[{"text":"合金牌号","row":0,"col":0,"rowspan":4,"colspan":1},{"text":"名义化学成分","row":0,"col":1,"rowspan":4,"colspan":1},{"text":"化学成分(质量分数)/%","row":0,"col":2,"rowspan":1,"colspan":18},{"text":"主要成分","row":1,"col":2,"rowspan":1,"colspan":11},{"text":"杂质,不大于","row":1,"col":13,"rowspan":1,"colspan":7},{"text":"Ti","row":2,"col":2,"rowspan":2,"colspan":1},{"text":"Al","row":2,"col":3,"rowspan":2,"colspan":1},{"text":"Si","row":2,"col":4,"rowspan":2,"colspan":1},{"text":"V","row":2,"col":5,"rowspan":2,"colspan":1},{"text":"Cr","row":2,"col":6,"rowspan":2,"colspan":1},{"text":"Fe","row":2,"col":7,"rowspan":2,"colspan":1},{"text":"Zr","row":2,"col":8,"rowspan":2,"colspan":1},{"text":"Nb","row":2,"col":9,"rowspan":2,"colspan":1},{"text":"Mo","row":2,"col":10,"rowspan":2,"colspan":1},{"text":"Pd","row":2,"col":11,"rowspan":2,"colspan":1},{"text":"Sn","row":2,"col":12,"rowspan":2,"colspan":1},{"text":"Fe","row":2,"col":13,"rowspan":2,"colspan":1},{"text":"C","row":2,"col":14,"rowspan":2,"colspan":1},{"text":"N","row":2,"col":15,"rowspan":2,"colspan":1},{"text":"H","row":2,"col":16,"rowspan":2,"colspan":1},{"text":"O","row":2,"col":17,"rowspan":2,"colspan":1},{"text":"其他元素","row":2,"col":18,"rowspan":1,"colspan":2},{"text":"单一","row":3,"col":18,"rowspan":1,"colspan":1},{"text":"总和","row":3,"col":19,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>请从 73.pdf 的“表2（续）”中TB6的铁含量是多少。</t>
+  </si>
+  <si>
+    <t>1.8~2.2</t>
+  </si>
+  <si>
+    <t>1.8~2.8</t>
+  </si>
+  <si>
+    <t>1.6～2.2</t>
+  </si>
+  <si>
+    <t>请从 73.pdf 的“表2（续）”中那种合金的杂质含量最多</t>
+  </si>
+  <si>
+    <t>TC17</t>
+  </si>
+  <si>
+    <t>TB9</t>
+  </si>
+  <si>
+    <t>TB8</t>
+  </si>
+  <si>
+    <t>请从 73.pdf 的“表2（续）”中提取：表格中的 Al 列单元格内容。</t>
+  </si>
+  <si>
+    <t>["2.5～3.5","2.6～3.4","—","2.5～3.5","3.0～4.0","2.5～3.5","—","3.0～4.5","3.5～4.5","—","余量","余量","—","余量","余量","余量","余量","余量","余量","余量","余量","余量","余量","余量","余量","余量","余量","余量","余量","余量","余量","余量"]</t>
+  </si>
+  <si>
+    <t>["2.5~3.5","2.8~3.4","—","2.5~3.5","3.0~4.0","2.5~3.5","余量","—","3.0~4.5","—","3.5~4.5","2.5~3.5","3.5~4.5"]</t>
+  </si>
+  <si>
+    <t>["2.5～3.5","2.6～3.4","—","2.5～3.5","3.0～4.0","2.5～3.5","—","—","3.0～4.5","—","3.5～4.5","2.5～3.5","3.5～4.5"]</t>
+  </si>
+  <si>
+    <t>["2.5~3.5","2.6~3.4","—","2.5~3.5","3.0~4.0","2.5~3.5","—","—","3.0~4.5","—","3.5~4.5","2.5~3.5","3.5~5.5"]</t>
+  </si>
+  <si>
+    <t>请从 73.pdf 的““表2（续）”中Mo元素含量大于 0.5 的有多少个?</t>
+  </si>
+  <si>
+    <t>请从 73.pdf 的““表2（续）”中TB14中含量最多的元素？</t>
+  </si>
+  <si>
+    <t>Al</t>
+  </si>
+  <si>
+    <t>Ti</t>
+  </si>
+  <si>
+    <t>Nb</t>
+  </si>
+  <si>
+    <t>请恢复 75.jpg 中“Pro Forma Capitalization Table”的表头行结构。</t>
+  </si>
+  <si>
+    <t>{"row_count":3,"col_count":10,"cells":[{"text":"Common Stock","row":0,"col":0,"rowspan":1,"colspan":4},{"text":"Investor Rounds","row":0,"col":4,"rowspan":1,"colspan":4},{"text":"Exit","row":0,"col":8,"rowspan":1,"colspan":2},{"text":"Founders' Shares","row":1,"col":0,"rowspan":1,"colspan":2},{"text":"Stock Options","row":1,"col":2,"rowspan":1,"colspan":2},{"text":"$","row":1,"col":4,"rowspan":1,"colspan":1},{"text":"Round 1","row":1,"col":5,"rowspan":1,"colspan":2},{"text":"$","row":1,"col":7,"rowspan":1,"colspan":1},{"text":"Round 2","row":1,"col":8,"rowspan":1,"colspan":2},{"text":"Shares","row":2,"col":0,"rowspan":1,"colspan":1},{"text":"%","row":2,"col":1,"rowspan":1,"colspan":1},{"text":"Shares","row":2,"col":2,"rowspan":1,"colspan":1},{"text":"%","row":2,"col":3,"rowspan":1,"colspan":1},{"text":"Shares","row":2,"col":5,"rowspan":1,"colspan":1},{"text":"%","row":2,"col":6,"rowspan":1,"colspan":1},{"text":"Shares","row":2,"col":8,"rowspan":1,"colspan":1},{"text":"%","row":2,"col":9,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>{"row_count":25,"col_count":13,"cells":[{"text":"","row":0,"col":0,"rowspan":3,"colspan":1},{"text":"Common Stock","row":0,"col":1,"rowspan":1,"colspan":4},{"text":"Investor Rounds","row":0,"col":5,"rowspan":1,"colspan":6},{"text":"Exit","row":0,"col":11,"rowspan":1,"colspan":2},{"text":"Founders' Shares","row":1,"col":1,"rowspan":1,"colspan":2},{"text":"Stock Options","row":1,"col":3,"rowspan":1,"colspan":2},{"text":"Round 1","row":1,"col":5,"rowspan":1,"colspan":3},{"text":"Round 2","row":1,"col":8,"rowspan":1,"colspan":3},{"text":"$20,000,000","row":1,"col":11,"rowspan":1,"colspan":1},{"text":"Multiple","row":1,"col":12,"rowspan":1,"colspan":1},{"text":"Shares","row":2,"col":1,"rowspan":1,"colspan":1},{"text":"%","row":2,"col":2,"rowspan":1,"colspan":1},{"text":"Shares","row":2,"col":3,"rowspan":1,"colspan":1},{"text":"%","row":2,"col":4,"rowspan":1,"colspan":1},{"text":"$","row":2,"col":5,"rowspan":1,"colspan":1},{"text":"Shares","row":2,"col":6,"rowspan":1,"colspan":1},{"text":"%","row":2,"col":7,"rowspan":1,"colspan":1},{"text":"$","row":2,"col":8,"rowspan":1,"colspan":1},{"text":"Shares","row":2,"col":9,"rowspan":1,"colspan":1},{"text":"%","row":2,"col":10,"rowspan":1,"colspan":1},{"text":"","row":2,"col":11,"rowspan":1,"colspan":1},{"text":"","row":2,"col":12,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>{"row_count":33,"col_count":13,"cells":[{"text":"","row":0,"col":0,"rowspan":2,"colspan":1},{"text":"Common Stock","row":0,"col":1,"rowspan":1,"colspan":4},{"text":"Investor Rounds","row":0,"col":5,"rowspan":1,"colspan":6},{"text":"Exit","row":0,"col":11,"rowspan":1,"colspan":2},{"text":"Founders' Shares","row":1,"col":1,"rowspan":1,"colspan":2},{"text":"Stock Options","row":1,"col":3,"rowspan":1,"colspan":2},{"text":"Round 1","row":1,"col":5,"rowspan":1,"colspan":3},{"text":"Round 2","row":1,"col":8,"rowspan":1,"colspan":3},{"text":"$20000000","row":1,"col":11,"rowspan":1,"colspan":1},{"text":"Multiple","row":1,"col":12,"rowspan":1,"colspan":1},{"text":"Common","row":2,"col":0,"rowspan":1,"colspan":1},{"text":"Shares","row":2,"col":1,"rowspan":1,"colspan":1},{"text":"%","row":2,"col":2,"rowspan":1,"colspan":1},{"text":"Shares","row":2,"col":3,"rowspan":1,"colspan":1},{"text":"%","row":2,"col":4,"rowspan":1,"colspan":1},{"text":"$","row":2,"col":5,"rowspan":1,"colspan":1},{"text":"Shares","row":2,"col":6,"rowspan":1,"colspan":1},{"text":"%","row":2,"col":7,"rowspan":1,"colspan":1},{"text":"$","row":2,"col":8,"rowspan":1,"colspan":1},{"text":"Shares","row":2,"col":9,"rowspan":1,"colspan":1},{"text":"%","row":2,"col":10,"rowspan":1,"colspan":1},{"text":"","row":2,"col":11,"rowspan":1,"colspan":1},{"text":"","row":2,"col":12,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>{"row_count":20,"col_count":13,"cells":[{"text":"Common","row":0,"col":0,"rowspan":3,"colspan":1},{"text":"Common Stock","row":0,"col":1,"rowspan":1,"colspan":4},{"text":"Investor Rounds","row":0,"col":5,"rowspan":1,"colspan":6},{"text":"Exit","row":0,"col":11,"rowspan":1,"colspan":2},{"text":"Founders' Shares","row":1,"col":1,"rowspan":1,"colspan":2},{"text":"Stock Options","row":1,"col":3,"rowspan":1,"colspan":2},{"text":"Round 1","row":1,"col":5,"rowspan":1,"colspan":3},{"text":"Round 2","row":1,"col":8,"rowspan":1,"colspan":3},{"text":"$20000000","row":1,"col":11,"rowspan":2,"colspan":1},{"text":"Multiple","row":1,"col":12,"rowspan":2,"colspan":1},{"text":"Shares","row":2,"col":1,"rowspan":1,"colspan":1},{"text":"%","row":2,"col":2,"rowspan":1,"colspan":1},{"text":"Shares","row":2,"col":3,"rowspan":1,"colspan":1},{"text":"%","row":2,"col":4,"rowspan":1,"colspan":1},{"text":"$","row":2,"col":5,"rowspan":1,"colspan":1},{"text":"Shares","row":2,"col":6,"rowspan":1,"colspan":1},{"text":"%","row":2,"col":7,"rowspan":1,"colspan":1},{"text":"$","row":2,"col":8,"rowspan":1,"colspan":1},{"text":"Shares","row":2,"col":9,"rowspan":1,"colspan":1},{"text":"%","row":2,"col":10,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>请恢复 76.jpg 中“Simple Income Statement”的表头行结构。</t>
+  </si>
+  <si>
+    <t>{"row_count":2,"col_count":2,"cells":[{"text":"Income Statement:","row":0,"col":0,"rowspan":1,"colspan":1},{"text":"Year 1","row":0,"col":1,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>{"row_count":35,"col_count":3,"cells":[{"text":"Income Statement:","row":0,"col":0,"rowspan":1,"colspan":3},{"text":"Revenue:","row":1,"col":0,"rowspan":1,"colspan":1},{"text":"Year 1","row":1,"col":1,"rowspan":1,"colspan":2}]}</t>
+  </si>
+  <si>
+    <t>{"row_count":27,"col_count":2,"cells":[{"text":"Income Statement:","row":0,"col":0,"rowspan":1,"colspan":2},{"text":"Revenue:","row":1,"col":0,"rowspan":1,"colspan":1},{"text":"Year 1","row":1,"col":1,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>请恢复 77.pdf 中“Monster Beverage consolidated financial statements”的表头行结构。</t>
+  </si>
+  <si>
+    <t>{"row_count":3,"col_count":4,"cells":[{"text":"MONSTER BEVERAGE CORPORATION AND SUBSIDIARIES CONSOLIDATED BALANCE SHEETS AS OF DECEMBER 31, 2021 AND 2020 (In Thousands, Except Par Value)","row":0,"col":0,"rowspan":1,"colspan":4},{"text":"December 31, 2021","row":1,"col":1,"rowspan":1,"colspan":1},{"text":"December 31, 2020","row":1,"col":2,"rowspan":1,"colspan":1},{"text":"ASSETS","row":2,"col":0,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>{"row_count":16,"col_count":4,"cells":[{"text":"2021","row":0,"col":1,"rowspan":1,"colspan":1},{"text":"2020","row":0,"col":2,"rowspan":1,"colspan":1},{"text":"2019","row":0,"col":3,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>{"row_count":37,"col_count":3,"cells":[{"text":"","row":0,"col":0,"rowspan":1,"colspan":1},{"text":"December 31, 2021","row":0,"col":1,"rowspan":1,"colspan":1},{"text":"December 31, 2020","row":0,"col":2,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>请恢复 79.png 中“Amazon consolidated statements of cash flows”的表头行结构。</t>
+  </si>
+  <si>
+    <t>{"row_count":3,"col_count":4,"cells":[{"text":"Year Ended December 31,","row":0,"col":1,"rowspan":1,"colspan":3},{"text":"2015","row":1,"col":1,"rowspan":1,"colspan":1},{"text":"2016","row":1,"col":2,"rowspan":1,"colspan":1},{"text":"2017","row":1,"col":3,"rowspan":1,"colspan":1},{"text":"$","row":2,"col":1,"rowspan":1,"colspan":1},{"text":"$","row":2,"col":2,"rowspan":1,"colspan":1},{"text":"$","row":2,"col":3,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>{"row_count":2,"col_count":4,"cells":[{"text":"","row":0,"col":0,"rowspan":2,"colspan":1},{"text":"Year Ended December 31,","row":0,"col":1,"rowspan":1,"colspan":3},{"text":"2015","row":1,"col":1,"rowspan":1,"colspan":1},{"text":"2016","row":1,"col":2,"rowspan":1,"colspan":1},{"text":"2017","row":1,"col":3,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>{"row_count":40,"col_count":4,"cells":[{"text":"Year Ended December 31,","row":0,"col":1,"rowspan":1,"colspan":3},{"text":"2015","row":1,"col":1,"rowspan":1,"colspan":1},{"text":"2016","row":1,"col":2,"rowspan":1,"colspan":1},{"text":"2017","row":1,"col":3,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>{"row_count":40,"col_count":4,"cells":[{"text":"","row":0,"col":0,"rowspan":1,"colspan":1},{"text":"Year Ended December 31,","row":0,"col":1,"rowspan":1,"colspan":3},{"text":"","row":1,"col":0,"rowspan":1,"colspan":1},{"text":"2015","row":1,"col":1,"rowspan":1,"colspan":1},{"text":"2016","row":1,"col":2,"rowspan":1,"colspan":1},{"text":"2017","row":1,"col":3,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>请计算 2017 Sales and maturities of marketable securities 减 Purchases of marketable securities。</t>
+  </si>
+  <si>
+    <t>-3779</t>
+  </si>
+  <si>
+    <t>-3789</t>
+  </si>
+  <si>
+    <t>23765</t>
+  </si>
+  <si>
+    <t>请恢复 80.png 中 Balance 表的 Cash 行，对应在 CashFlow 表的哪一行？</t>
+  </si>
+  <si>
+    <t>Closing Cash Balance</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>请恢复 81.png 中“School board classes table”的表头行结构。</t>
+  </si>
+  <si>
+    <t>{"row_count":2,"col_count":3,"cells":[{"text":"SCHOOL","row":0,"col":0,"rowspan":1,"colspan":1},{"text":"BOARD","row":0,"col":1,"rowspan":1,"colspan":1},{"text":"CLASSES","row":0,"col":2,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>{"row_count":3,"col_count":3,"cells":[{"text":"SCHOOL","row":0,"col":0,"rowspan":1,"colspan":1},{"text":"BOARD","row":0,"col":1,"rowspan":1,"colspan":1},{"text":"CLASSES","row":0,"col":2,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>{"row_count":8,"col_count":5,"cells":[{"text":"SCHOOL","row":0,"col":0,"rowspan":1,"colspan":1},{"text":"BOARD","row":0,"col":1,"rowspan":1,"colspan":1},{"text":"CLASSES","row":0,"col":2,"rowspan":1,"colspan":3},{"text":"CLASS","row":1,"col":2,"rowspan":1,"colspan":1},{"text":"STRENGTH","row":1,"col":3,"rowspan":1,"colspan":1},{"text":"SPORTS","row":1,"col":4,"rowspan":1,"colspan":1},{"text":"CLASS","row":4,"col":2,"rowspan":1,"colspan":1},{"text":"STRENGTH","row":4,"col":3,"rowspan":1,"colspan":1},{"text":"SPORTS","row":4,"col":4,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>请恢复 82.png 中“表1-2 分部分项工程量清单及计价表（号清单）”的表头行结构。</t>
+  </si>
+  <si>
+    <t>{"row_count":3,"col_count":12,"cells":[{"text":"序号","row":0,"col":0,"rowspan":3,"colspan":1},{"text":"项目编码","row":0,"col":1,"rowspan":3,"colspan":1},{"text":"项目名称","row":0,"col":2,"rowspan":3,"colspan":1},{"text":"项目特征描述","row":0,"col":3,"rowspan":3,"colspan":1},{"text":"计量单位","row":0,"col":4,"rowspan":3,"colspan":1},{"text":"工程量","row":0,"col":5,"rowspan":3,"colspan":1},{"text":"综合单价(元)","row":0,"col":6,"rowspan":3,"colspan":1},{"text":"合价(元)","row":0,"col":7,"rowspan":3,"colspan":1},{"text":"其中","row":0,"col":8,"rowspan":1,"colspan":3},{"text":"备注","row":0,"col":11,"rowspan":3,"colspan":1},{"text":"人工费","row":1,"col":8,"rowspan":2,"colspan":1},{"text":"机械费","row":1,"col":9,"rowspan":2,"colspan":1},{"text":"管理费","row":1,"col":10,"rowspan":2,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>{"row_count":2,"col_count":12,"cells":[{"text":"序号","row":0,"col":0,"rowspan":2,"colspan":1},{"text":"项目编码","row":0,"col":1,"rowspan":2,"colspan":1},{"text":"项目名称","row":0,"col":2,"rowspan":2,"colspan":1},{"text":"项目特征描述","row":0,"col":3,"rowspan":2,"colspan":1},{"text":"计量单位","row":0,"col":4,"rowspan":2,"colspan":1},{"text":"工程量","row":0,"col":5,"rowspan":2,"colspan":1},{"text":"综合单价(元)","row":0,"col":6,"rowspan":2,"colspan":1},{"text":"合价(元)","row":0,"col":7,"rowspan":2,"colspan":1},{"text":"其中","row":0,"col":8,"rowspan":1,"colspan":3},{"text":"备注","row":0,"col":11,"rowspan":2,"colspan":1},{"text":"人工费","row":1,"col":8,"rowspan":1,"colspan":1},{"text":"机械费","row":1,"col":9,"rowspan":1,"colspan":1},{"text":"管理费","row":1,"col":10,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>{"row_count":8,"col_count":12,"cells":[{"text":"序号","row":0,"col":0,"rowspan":2,"colspan":1},{"text":"项目编码","row":0,"col":1,"rowspan":2,"colspan":1},{"text":"项目名称","row":0,"col":2,"rowspan":2,"colspan":1},{"text":"项目特征描述","row":0,"col":3,"rowspan":2,"colspan":1},{"text":"计量单位","row":0,"col":4,"rowspan":2,"colspan":1},{"text":"工程量","row":0,"col":5,"rowspan":2,"colspan":1},{"text":"综合单价(元)","row":0,"col":6,"rowspan":2,"colspan":1},{"text":"合价(元)","row":0,"col":7,"rowspan":2,"colspan":1},{"text":"其中","row":0,"col":8,"rowspan":1,"colspan":3},{"text":"备注","row":0,"col":11,"rowspan":2,"colspan":1},{"text":"人工费","row":1,"col":8,"rowspan":1,"colspan":1},{"text":"机械费","row":1,"col":9,"rowspan":1,"colspan":1},{"text":"管理费","row":1,"col":10,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>请从 82.png 的“表1-2 分部分项工程量清单及计价表（号清单）”中提取：表格标题。</t>
+  </si>
+  <si>
+    <t>表1-2 分部分项工程量清单及计价表（号清单）</t>
+  </si>
+  <si>
+    <t>表1-2 分部分项工程量清单及计价表（ 号清单）</t>
+  </si>
+  <si>
+    <t>表1-2 分部分项工程量清单及计价表(号清单)</t>
+  </si>
+  <si>
+    <t>请计算序号24、25、26、27 四行合价合计。</t>
+  </si>
+  <si>
+    <t>10260</t>
+  </si>
+  <si>
+    <t>12786</t>
+  </si>
+  <si>
+    <t>12586</t>
+  </si>
+  <si>
+    <t>请恢复 83.png 中“The Error Rate on Different Forms”的表头行结构。</t>
+  </si>
+  <si>
+    <t>{"row_count":9,"col_count":7,"cells":[{"text":"Form name","row":0,"col":0,"rowspan":2,"colspan":1},{"text":"A","row":0,"col":1,"rowspan":2,"colspan":1},{"text":"B","row":0,"col":2,"rowspan":2,"colspan":1},{"text":"Total fields (X = A × B)","row":0,"col":3,"rowspan":2,"colspan":1},{"text":"Fields with errors (Y)","row":0,"col":4,"rowspan":2,"colspan":1},{"text":"Error rate* (Y/X) × 100 (%)","row":0,"col":5,"rowspan":1,"colspan":2},{"text":"X/Y","row":1,"col":5,"rowspan":1,"colspan":1},{"text":"%age","row":1,"col":6,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>{"row_count":3,"col_count":7,"cells":[{"text":"The Error Rate on Different Forms","row":0,"col":0,"rowspan":1,"colspan":7},{"text":"Form name","row":1,"col":0,"rowspan":2,"colspan":1},{"text":"A","row":1,"col":1,"rowspan":2,"colspan":1},{"text":"B","row":1,"col":2,"rowspan":2,"colspan":1},{"text":"Total fields (X = A × B)","row":1,"col":3,"rowspan":2,"colspan":1},{"text":"Fields with errors (Y)","row":1,"col":4,"rowspan":2,"colspan":1},{"text":"Error rate (Y/X) × 100 (%)","row":1,"col":5,"rowspan":1,"colspan":2},{"text":"X/Y","row":2,"col":5,"rowspan":1,"colspan":1},{"text":"%age","row":2,"col":6,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>{"row_count":11,"col_count":7,"cells":[{"text":"Form name","row":1,"col":0,"rowspan":2,"colspan":1},{"text":"A","row":1,"col":1,"rowspan":2,"colspan":1},{"text":"B","row":1,"col":2,"rowspan":2,"colspan":1},{"text":"Total fields (X = A × B)","row":1,"col":3,"rowspan":2,"colspan":1},{"text":"Fields with errors (Y)","row":1,"col":4,"rowspan":2,"colspan":1},{"text":"Error rate* (Y/X) × 100 (%)","row":1,"col":5,"rowspan":1,"colspan":2},{"text":"X/Y","row":2,"col":5,"rowspan":1,"colspan":1},{"text":"%age","row":2,"col":6,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>{"row_count":12,"col_count":7,"cells":[{"text":"Form name","row":1,"col":0,"rowspan":2,"colspan":1},{"text":"A","row":1,"col":1,"rowspan":2,"colspan":1},{"text":"B","row":1,"col":2,"rowspan":2,"colspan":1},{"text":"Total fields (X = A × B)","row":1,"col":3,"rowspan":2,"colspan":1},{"text":"Fields with errors (Y)","row":1,"col":4,"rowspan":2,"colspan":1},{"text":"Error rate* (Y/X) × 100 (%)","row":1,"col":5,"rowspan":1,"colspan":2},{"text":"X/Y","row":2,"col":5,"rowspan":1,"colspan":1},{"text":"%age","row":2,"col":6,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>请恢复 84.png 中“Catalog of chemicals”的表头行结构。</t>
+  </si>
+  <si>
+    <t>{"row_count":15,"col_count":12,"cells":[{"text":"Chemical name","row":0,"col":0,"rowspan":1,"colspan":1},{"text":"International number","row":0,"col":1,"rowspan":1,"colspan":1},{"text":"Vendor","row":0,"col":2,"rowspan":1,"colspan":1},{"text":"Resistance index","row":0,"col":3,"rowspan":1,"colspan":1},{"text":"Density","row":0,"col":4,"rowspan":1,"colspan":1},{"text":"Viscosity","row":0,"col":5,"rowspan":1,"colspan":1},{"text":"Freezing point","row":0,"col":6,"rowspan":1,"colspan":1},{"text":"Packaging","row":0,"col":7,"rowspan":1,"colspan":1},{"text":"Pack size","row":0,"col":8,"rowspan":1,"colspan":1},{"text":"Unit","row":0,"col":9,"rowspan":1,"colspan":1},{"text":"Price","row":0,"col":10,"rowspan":1,"colspan":1},{"text":"Last update","row":0,"col":11,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>{"row_count":2,"col_count":13,"cells":[{"text":"Chemical name","row":0,"col":1,"rowspan":1,"colspan":1},{"text":"International number","row":0,"col":2,"rowspan":1,"colspan":1},{"text":"Vendor","row":0,"col":3,"rowspan":1,"colspan":1},{"text":"Resistance index","row":0,"col":4,"rowspan":1,"colspan":1},{"text":"Density","row":0,"col":5,"rowspan":1,"colspan":1},{"text":"Viscosity","row":0,"col":6,"rowspan":1,"colspan":1},{"text":"Freezing point","row":0,"col":7,"rowspan":1,"colspan":1},{"text":"Packaging","row":0,"col":8,"rowspan":1,"colspan":1},{"text":"Pack size","row":0,"col":9,"rowspan":1,"colspan":1},{"text":"Unit","row":0,"col":10,"rowspan":1,"colspan":1},{"text":"Price","row":0,"col":11,"rowspan":1,"colspan":1},{"text":"Last update","row":0,"col":12,"rowspan":1,"colspan":1},{"text":"g/m³","row":1,"col":5,"rowspan":1,"colspan":1},{"text":"m²/s","row":1,"col":6,"rowspan":1,"colspan":1},{"text":"°C","row":1,"col":7,"rowspan":1,"colspan":1},{"text":"$","row":1,"col":11,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>{"row_count":16,"col_count":13,"cells":[{"text":"","row":0,"col":0,"rowspan":1,"colspan":1},{"text":"Chemical name","row":0,"col":1,"rowspan":1,"colspan":1},{"text":"International number","row":0,"col":2,"rowspan":1,"colspan":1},{"text":"Vendor","row":0,"col":3,"rowspan":1,"colspan":1},{"text":"Resistance index","row":0,"col":4,"rowspan":1,"colspan":1},{"text":"Density g/m³","row":0,"col":5,"rowspan":1,"colspan":1},{"text":"Viscosity m²/s","row":0,"col":6,"rowspan":1,"colspan":1},{"text":"Freezing point °C","row":0,"col":7,"rowspan":1,"colspan":1},{"text":"Packaging","row":0,"col":8,"rowspan":1,"colspan":1},{"text":"Pack size","row":0,"col":9,"rowspan":1,"colspan":1},{"text":"Unit","row":0,"col":10,"rowspan":1,"colspan":1},{"text":"Price $","row":0,"col":11,"rowspan":1,"colspan":1},{"text":"Last update","row":0,"col":12,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>{"row_count":17,"col_count":13,"cells":[{"text":"","row":0,"col":0,"rowspan":1,"colspan":1},{"text":"Chemical name","row":0,"col":1,"rowspan":1,"colspan":1},{"text":"International number","row":0,"col":2,"rowspan":1,"colspan":1},{"text":"Vendor","row":0,"col":3,"rowspan":1,"colspan":1},{"text":"Resistance index","row":0,"col":4,"rowspan":1,"colspan":1},{"text":"Density g/m³","row":0,"col":5,"rowspan":1,"colspan":1},{"text":"Viscosity m²/s","row":0,"col":6,"rowspan":1,"colspan":1},{"text":"Freezing point °C","row":0,"col":7,"rowspan":1,"colspan":1},{"text":"Packaging","row":0,"col":8,"rowspan":1,"colspan":1},{"text":"Pack size","row":0,"col":9,"rowspan":1,"colspan":1},{"text":"Unit","row":0,"col":10,"rowspan":1,"colspan":1},{"text":"Price $","row":0,"col":11,"rowspan":1,"colspan":1},{"text":"Last update","row":0,"col":12,"rowspan":1,"colspan":1},{"text":"","row":1,"col":0,"rowspan":1,"colspan":1},{"text":"","row":1,"col":1,"rowspan":1,"colspan":1},{"text":"","row":1,"col":2,"rowspan":1,"colspan":1},{"text":"All","row":1,"col":3,"rowspan":1,"colspan":1},{"text":"&lt; 1","row":1,"col":4,"rowspan":1,"colspan":1},{"text":"All","row":1,"col":5,"rowspan":1,"colspan":1},{"text":"All","row":1,"col":6,"rowspan":1,"colspan":1},{"text":"","row":1,"col":7,"rowspan":1,"colspan":1},{"text":"All","row":1,"col":8,"rowspan":1,"colspan":1},{"text":"","row":1,"col":9,"rowspan":1,"colspan":1},{"text":"All","row":1,"col":10,"rowspan":1,"colspan":1},{"text":"","row":1,"col":11,"rowspan":1,"colspan":1},{"text":"","row":1,"col":12,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>请找出可见行中 Resistance index 最高的化学品。</t>
+  </si>
+  <si>
+    <t>Caustic Potash</t>
+  </si>
+  <si>
+    <t>Stearalkonium Chloride</t>
+  </si>
+  <si>
+    <t>["Stearalkonium Chloride","Guar Gum"]</t>
+  </si>
+  <si>
+    <t>请恢复 88.png 中“Games by Continent”的表头行结构。</t>
+  </si>
+  <si>
+    <t>{"row_count":7,"col_count":10,"cells":[{"text":"Games by Continent","row":0,"col":0,"rowspan":1,"colspan":10},{"text":"Place","row":1,"col":1,"rowspan":1,"colspan":4},{"text":"Dates","row":1,"col":5,"rowspan":1,"colspan":4},{"text":"Season","row":3,"col":0,"rowspan":1,"colspan":1},{"text":"Number","row":3,"col":1,"rowspan":1,"colspan":1},{"text":"Flag","row":3,"col":2,"rowspan":1,"colspan":1},{"text":"City","row":3,"col":3,"rowspan":1,"colspan":1},{"text":"Country","row":3,"col":4,"rowspan":1,"colspan":1},{"text":"Year","row":3,"col":5,"rowspan":1,"colspan":1},{"text":"From","row":3,"col":6,"rowspan":1,"colspan":1},{"text":"To","row":3,"col":7,"rowspan":1,"colspan":1},{"text":"Status","row":3,"col":8,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>{"row_count":10,"col_count":9,"cells":[{"text":"Games by Continent","row":0,"col":0,"rowspan":1,"colspan":9},{"text":"","row":1,"col":0,"rowspan":1,"colspan":1},{"text":"Place","row":1,"col":1,"rowspan":1,"colspan":4},{"text":"Dates","row":1,"col":5,"rowspan":1,"colspan":3},{"text":"","row":1,"col":8,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>{"row_count":10,"col_count":9,"cells":[{"text":"Games by Continent","row":0,"col":0,"rowspan":1,"colspan":9},{"text":"","row":1,"col":0,"rowspan":1,"colspan":2},{"text":"Place","row":1,"col":2,"rowspan":1,"colspan":3},{"text":"Dates","row":1,"col":5,"rowspan":1,"colspan":3},{"text":"","row":1,"col":8,"rowspan":1,"colspan":1},{"text":"Season","row":6,"col":0,"rowspan":1,"colspan":1},{"text":"Number","row":6,"col":1,"rowspan":1,"colspan":1},{"text":"Flag","row":6,"col":2,"rowspan":1,"colspan":1},{"text":"City","row":6,"col":3,"rowspan":1,"colspan":1},{"text":"Country","row":6,"col":4,"rowspan":1,"colspan":1},{"text":"Year","row":6,"col":5,"rowspan":1,"colspan":1},{"text":"From","row":6,"col":6,"rowspan":1,"colspan":1},{"text":"To","row":6,"col":7,"rowspan":1,"colspan":1},{"text":"Status","row":6,"col":8,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>请恢复 89.png 中红色的方块一共有多少个？</t>
+  </si>
+  <si>
+    <t>{"row_count":18,"col_count":6,"cells":[{"text":"1","row":0,"col":0,"rowspan":1,"colspan":1},{"text":"","row":0,"col":1,"rowspan":1,"colspan":2},{"text":"2","row":0,"col":3,"rowspan":1,"colspan":2},{"text":"","row":1,"col":0,"rowspan":1,"colspan":1},{"text":"3","row":1,"col":1,"rowspan":1,"colspan":2},{"text":"","row":1,"col":3,"rowspan":1,"colspan":2},{"text":"4","row":2,"col":0,"rowspan":1,"colspan":4},{"text":"","row":2,"col":4,"rowspan":1,"colspan":2},{"text":"5","row":3,"col":0,"rowspan":1,"colspan":1},{"text":"","row":3,"col":1,"rowspan":1,"colspan":2},{"text":"","row":3,"col":3,"rowspan":1,"colspan":1},{"text":"","row":3,"col":4,"rowspan":1,"colspan":2},{"text":"6","row":4,"col":0,"rowspan":1,"colspan":1},{"text":"","row":4,"col":1,"rowspan":1,"colspan":2},{"text":"","row":4,"col":3,"rowspan":1,"colspan":1},{"text":"","row":4,"col":4,"rowspan":1,"colspan":2},{"text":"7","row":5,"col":0,"rowspan":3,"colspan":2},{"text":"9","row":5,"col":2,"rowspan":1,"colspan":1},{"text":"8","row":5,"col":3,"rowspan":2,"colspan":3},{"text":"10","row":6,"col":2,"rowspan":1,"colspan":1},{"text":"11","row":7,"col":0,"rowspan":1,"colspan":1},{"text":"12","row":7,"col":1,"rowspan":1,"colspan":2},{"text":"","row":7,"col":3,"rowspan":1,"colspan":1},{"text":"","row":7,"col":4,"rowspan":1,"colspan":2},{"text":"13","row":8,"col":0,"rowspan":5,"colspan":3},{"text":"","row":8,"col":3,"rowspan":1,"colspan":1},{"text":"","row":8,"col":4,"rowspan":1,"colspan":2},{"text":"14","row":9,"col":3,"rowspan":1,"colspan":1},{"text":"","row":9,"col":4,"rowspan":1,"colspan":2},{"text":"15","row":10,"col":3,"rowspan":1,"colspan":1},{"text":"","row":10,"col":4,"rowspan":1,"colspan":2},{"text":"16","row":11,"col":3,"rowspan":2,"colspan":2},{"text":"","row":11,"col":5,"rowspan":1,"colspan":1},{"text":"17","row":12,"col":0,"rowspan":1,"colspan":1},{"text":"","row":12,"col":1,"rowspan":1,"colspan":2},{"text":"","row":12,"col":3,"rowspan":1,"colspan":2},{"text":"18","row":13,"col":0,"rowspan":1,"colspan":6}]}</t>
+  </si>
+  <si>
+    <t>{"row_count":18,"col_count":8,"cells":[{"text":"1","row":0,"col":0,"rowspan":2,"colspan":1},{"text":"","row":0,"col":1,"rowspan":1,"colspan":1},{"text":"2","row":0,"col":2,"rowspan":1,"colspan":1},{"text":"","row":0,"col":3,"rowspan":1,"colspan":1},{"text":"","row":0,"col":4,"rowspan":2,"colspan":1},{"text":"","row":0,"col":5,"rowspan":1,"colspan":1},{"text":"","row":0,"col":6,"rowspan":1,"colspan":1},{"text":"","row":0,"col":7,"rowspan":1,"colspan":1},{"text":"","row":1,"col":1,"rowspan":1,"colspan":1},{"text":"3","row":1,"col":2,"rowspan":1,"colspan":1},{"text":"","row":1,"col":3,"rowspan":1,"colspan":1},{"text":"","row":1,"col":5,"rowspan":1,"colspan":1},{"text":"","row":1,"col":6,"rowspan":1,"colspan":1},{"text":"","row":1,"col":7,"rowspan":1,"colspan":1},{"text":"4","row":2,"col":0,"rowspan":1,"colspan":1},{"text":"","row":2,"col":1,"rowspan":1,"colspan":2},{"text":"","row":2,"col":3,"rowspan":1,"colspan":4},{"text":"","row":2,"col":7,"rowspan":2,"colspan":1},{"text":"5","row":3,"col":0,"rowspan":1,"colspan":1},{"text":"","row":3,"col":1,"rowspan":1,"colspan":2},{"text":"","row":3,"col":3,"rowspan":2,"colspan":1},{"text":"","row":3,"col":4,"rowspan":1,"colspan":3},{"text":"6","row":4,"col":0,"rowspan":1,"colspan":1},{"text":"","row":4,"col":1,"rowspan":1,"colspan":2},{"text":"","row":4,"col":4,"rowspan":1,"colspan":4},{"text":"7","row":5,"col":0,"rowspan":5,"colspan":1},{"text":"","row":5,"col":1,"rowspan":3,"colspan":2},{"text":"","row":5,"col":3,"rowspan":3,"colspan":5},{"text":"9","row":8,"col":1,"rowspan":1,"colspan":1},{"text":"","row":8,"col":2,"rowspan":1,"colspan":1},{"text":"8","row":8,"col":3,"rowspan":2,"colspan":1},{"text":"","row":8,"col":4,"rowspan":2,"colspan":4},{"text":"10","row":9,"col":1,"rowspan":1,"colspan":1},{"text":"","row":9,"col":2,"rowspan":1,"colspan":1},{"text":"11","row":10,"col":0,"rowspan":1,"colspan":1},{"text":"","row":10,"col":1,"rowspan":1,"colspan":5},{"text":"","row":10,"col":6,"rowspan":1,"colspan":1},{"text":"","row":10,"col":7,"rowspan":2,"colspan":1},{"text":"12","row":11,"col":0,"rowspan":1,"colspan":3},{"text":"","row":11,"col":3,"rowspan":2,"colspan":1},{"text":"","row":11,"col":4,"rowspan":1,"colspan":2},{"text":"","row":11,"col":6,"rowspan":1,"colspan":1},{"text":"13","row":12,"col":0,"rowspan":4,"colspan":3},{"text":"","row":12,"col":4,"rowspan":1,"colspan":2},{"text":"","row":12,"col":6,"rowspan":1,"colspan":1},{"text":"","row":12,"col":7,"rowspan":1,"colspan":1},{"text":"14","row":13,"col":3,"rowspan":1,"colspan":1},{"text":"","row":13,"col":4,"rowspan":1,"colspan":4},{"text":"15","row":14,"col":3,"rowspan":1,"colspan":1},{"text":"","row":14,"col":4,"rowspan":1,"colspan":4},{"text":"16","row":15,"col":3,"rowspan":2,"colspan":1},{"text":"","row":15,"col":4,"rowspan":1,"colspan":4},{"text":"17","row":16,"col":0,"rowspan":1,"colspan":1},{"text":"","row":16,"col":1,"rowspan":1,"colspan":2},{"text":"","row":16,"col":4,"rowspan":1,"colspan":4},{"text":"18","row":17,"col":0,"rowspan":1,"colspan":1},{"text":"","row":17,"col":1,"rowspan":1,"colspan":7}]}</t>
+  </si>
+  <si>
+    <t>{"row_count":17,"col_count":7,"cells":[{"text":"1","row":0,"col":0,"rowspan":3,"colspan":1},{"text":"","row":0,"col":1,"rowspan":2,"colspan":1},{"text":"","row":0,"col":2,"rowspan":1,"colspan":2},{"text":"","row":0,"col":4,"rowspan":3,"colspan":1},{"text":"","row":0,"col":5,"rowspan":1,"colspan":2},{"text":"8","row":7,"col":3,"rowspan":2,"colspan":1},{"text":"","row":7,"col":4,"rowspan":2,"colspan":3},{"text":"15","row":13,"col":3,"rowspan":1,"colspan":1},{"text":"","row":13,"col":4,"rowspan":1,"colspan":1},{"text":"","row":13,"col":5,"rowspan":2,"colspan":2}]}</t>
+  </si>
+  <si>
+    <t>{"row_count":18,"col_count":7,"cells":[{"text":"1","row":0,"col":0,"rowspan":3,"colspan":1},{"text":"","row":0,"col":1,"rowspan":2,"colspan":1},{"text":"","row":0,"col":2,"rowspan":1,"colspan":2},{"text":"","row":0,"col":4,"rowspan":3,"colspan":1},{"text":"","row":0,"col":5,"rowspan":1,"colspan":2},{"text":"8","row":8,"col":3,"rowspan":3,"colspan":1},{"text":"","row":8,"col":4,"rowspan":3,"colspan":3},{"text":"15","row":15,"col":3,"rowspan":1,"colspan":1},{"text":"","row":15,"col":4,"rowspan":1,"colspan":1},{"text":"","row":15,"col":5,"rowspan":2,"colspan":2}]}</t>
+  </si>
+  <si>
+    <t>请从 89.png 的“colored merged-cell layout”中提取：黄色小块中位于上方的编号。</t>
+  </si>
+  <si>
+    <t>请按从上到下列出最左列可见编号。</t>
+  </si>
+  <si>
+    <t>[1,4,5,6,7,11,13,17,18]</t>
+  </si>
+  <si>
+    <t>["1","4","5","6","7","11","12","13","17","18"]</t>
+  </si>
+  <si>
+    <t>[1,4,5,6,7,11,12,13,17,18]</t>
+  </si>
+  <si>
+    <t>请从 90.png 的“merged-cell spreadsheet example”中提取：Row 7 蓝色区域显示的文本。</t>
+  </si>
+  <si>
+    <t>Row 6</t>
+  </si>
+  <si>
+    <t>请恢复 92.jpg 中“Funnel management plan conversion rates”的表头行结构。</t>
+  </si>
+  <si>
+    <t>{"row_count":5,"col_count":12,"cells":[{"text":"Account Manager","row":0,"col":0,"rowspan":1,"colspan":1},{"text":"1","row":0,"col":1,"rowspan":1,"colspan":1},{"text":"2","row":0,"col":2,"rowspan":1,"colspan":1},{"text":"3","row":0,"col":3,"rowspan":1,"colspan":1},{"text":"4","row":0,"col":4,"rowspan":1,"colspan":1},{"text":"5","row":0,"col":5,"rowspan":1,"colspan":1},{"text":"6","row":0,"col":6,"rowspan":1,"colspan":1},{"text":"7","row":0,"col":7,"rowspan":1,"colspan":1},{"text":"8","row":0,"col":8,"rowspan":1,"colspan":1},{"text":"9","row":0,"col":9,"rowspan":1,"colspan":1},{"text":"10","row":0,"col":10,"rowspan":1,"colspan":1},{"text":"11","row":0,"col":11,"rowspan":1,"colspan":1},{"text":"ANNUAL TARGET","row":1,"col":0,"rowspan":1,"colspan":1},{"text":"AVG CONTRACT VALUE (CURRENT AVG VALUE)","row":1,"col":1,"rowspan":1,"colspan":1},{"text":"NO. OF CONTRACTS REQUIRED","row":1,"col":2,"rowspan":1,"colspan":1},{"text":"TOTAL MEETINGS TO BE DONE PER MONTH","row":1,"col":3,"rowspan":1,"colspan":1},{"text":"DISCUSSION TO PROPOSAL CONVERSION RATIO (CURRENT RATIO)","row":1,"col":4,"rowspan":1,"colspan":1},{"text":"# PROPOSALS TO BE GENERATED PER MONTH","row":1,"col":5,"rowspan":1,"colspan":1},{"text":"PIPELINE VALUE PER MONTH","row":1,"col":6,"rowspan":1,"colspan":1},{"text":"PROPOSAL TO ORDERBOOK (CURRENT RATIO)","row":1,"col":7,"rowspan":1,"colspan":1},{"text":"# CONTRACTS GENERATED PER MONTH","row":1,"col":8,"rowspan":1,"colspan":1},{"text":"ORDER BOOK VALUE GENERATED PER MONTH","row":1,"col":9,"rowspan":1,"colspan":1},{"text":"AVG TARGET PER MONTH","row":1,"col":10,"rowspan":1,"colspan":1},{"text":"SHORTFALL / SURPLUS","row":1,"col":11,"rowspan":1,"colspan":1},{"text":"DATA FROM","row":2,"col":0,"rowspan":1,"colspan":1},{"text":"TARGET SHEET","row":2,"col":1,"rowspan":1,"colspan":1},{"text":"APRIL TO JAN CONTRACT AVG","row":2,"col":2,"rowspan":1,"colspan":1},{"text":"STEP 1 / STEP 2","row":2,"col":3,"rowspan":1,"colspan":1},{"text":"ACCOUNT MANAGEMENT PLAN","row":2,"col":4,"rowspan":1,"colspan":1},{"text":"YTD DAILY ACTIVITY REPORT (PROPOSAL / DISCUSSION %)","row":2,"col":5,"rowspan":1,"colspan":1},{"text":"STEP 4 * STEP 5","row":2,"col":6,"rowspan":1,"colspan":1},{"text":"STEP 6 * STEP 2","row":2,"col":7,"rowspan":1,"colspan":1},{"text":"YTD DAILY ACTIVITY REPORT (PROPOSAL / BUSINESS GENERATED %)","row":2,"col":8,"rowspan":1,"colspan":1},{"text":"STEP 6 * STEP 8","row":2,"col":9,"rowspan":1,"colspan":1},{"text":"STEP 9 * STEP 2","row":2,"col":10,"rowspan":1,"colspan":1},{"text":"STEP 11 / 12","row":2,"col":11,"rowspan":1,"colspan":1},{"text":"2016-17","row":3,"col":0,"rowspan":1,"colspan":1},{"text":"16000000","row":3,"col":1,"rowspan":1,"colspan":1},{"text":"214500","row":3,"col":2,"rowspan":1,"colspan":1},{"text":"75","row":3,"col":3,"rowspan":1,"colspan":1},{"text":"19","row":3,"col":4,"rowspan":1,"colspan":1},{"text":"13%","row":3,"col":5,"rowspan":1,"colspan":1},{"text":"2","row":3,"col":6,"rowspan":1,"colspan":1},{"text":"535113","row":3,"col":7,"rowspan":1,"colspan":1},{"text":"42%","row":3,"col":8,"rowspan":1,"colspan":1},{"text":"1.05","row":3,"col":9,"rowspan":1,"colspan":1},{"text":"224426","row":3,"col":10,"rowspan":1,"colspan":1},{"text":"1333333","row":3,"col":11,"rowspan":1,"colspan":1},{"text":"Rework","row":4,"col":0,"rowspan":1,"colspan":1},{"text":"16000000","row":4,"col":1,"rowspan":1,"colspan":1},{"text":"500000","row":4,"col":2,"rowspan":1,"colspan":1},{"text":"32","row":4,"col":3,"rowspan":1,"colspan":1},{"text":"30","row":4,"col":4,"rowspan":1,"colspan":1},{"text":"25%","row":4,"col":5,"rowspan":1,"colspan":1},{"text":"8","row":4,"col":6,"rowspan":1,"colspan":1},{"text":"3750000","row":4,"col":7,"rowspan":1,"colspan":1},{"text":"90%","row":4,"col":8,"rowspan":1,"colspan":1},{"text":"6.75","row":4,"col":9,"rowspan":1,"colspan":1},{"text":"3375000","row":4,"col":10,"rowspan":1,"colspan":1},{"text":"1333333","row":4,"col":11,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>{"row_count":3,"col_count":13,"cells":[{"text":"FUNNEL MANAGEMENT PLAN BASED ON INDIVIDUAL CONVERSION RATES","row":0,"col":0,"rowspan":1,"colspan":13},{"text":"Account Manager","row":1,"col":0,"rowspan":1,"colspan":2},{"text":"Debjit Mukherjee","row":1,"col":2,"rowspan":1,"colspan":11},{"text":"1","row":2,"col":0,"rowspan":1,"colspan":1},{"text":"2","row":2,"col":1,"rowspan":1,"colspan":1},{"text":"3","row":2,"col":2,"rowspan":1,"colspan":1},{"text":"4","row":2,"col":3,"rowspan":1,"colspan":1},{"text":"5","row":2,"col":4,"rowspan":1,"colspan":1},{"text":"6","row":2,"col":5,"rowspan":1,"colspan":1},{"text":"7","row":2,"col":6,"rowspan":1,"colspan":1},{"text":"8","row":2,"col":7,"rowspan":1,"colspan":1},{"text":"9","row":2,"col":8,"rowspan":1,"colspan":1},{"text":"10","row":2,"col":9,"rowspan":1,"colspan":1},{"text":"11","row":2,"col":10,"rowspan":1,"colspan":1},{"text":"12","row":2,"col":11,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>{"row_count":11,"col_count":13,"cells":[{"text":"FUNNEL MANAGEMENT PLAN BASED ON INDIVIDUAL CONVERSION RATES","row":0,"col":0,"rowspan":1,"colspan":13},{"text":"Account Manager","row":1,"col":0,"rowspan":1,"colspan":3},{"text":"Debajit Mukherjee","row":1,"col":3,"rowspan":1,"colspan":10},{"text":"","row":2,"col":0,"rowspan":1,"colspan":1},{"text":"1","row":2,"col":1,"rowspan":1,"colspan":1},{"text":"2","row":2,"col":2,"rowspan":1,"colspan":1},{"text":"3","row":2,"col":3,"rowspan":1,"colspan":1},{"text":"4","row":2,"col":4,"rowspan":1,"colspan":1},{"text":"5","row":2,"col":5,"rowspan":1,"colspan":1},{"text":"6","row":2,"col":6,"rowspan":1,"colspan":1},{"text":"7","row":2,"col":7,"rowspan":1,"colspan":1},{"text":"8","row":2,"col":8,"rowspan":1,"colspan":1},{"text":"9","row":2,"col":9,"rowspan":1,"colspan":1},{"text":"10","row":2,"col":10,"rowspan":1,"colspan":1},{"text":"11","row":2,"col":11,"rowspan":1,"colspan":1},{"text":"12","row":2,"col":12,"rowspan":1,"colspan":1},{"text":"","row":3,"col":0,"rowspan":1,"colspan":1},{"text":"ANNUAL TARGET","row":3,"col":1,"rowspan":1,"colspan":1},{"text":"AVG CONTRACT VALUE (CURRENT AVG VALUE)","row":3,"col":2,"rowspan":1,"colspan":1},{"text":"NO. OF CONTRACTS REQUIRED","row":3,"col":3,"rowspan":1,"colspan":1},{"text":"TOTAL MEETINGS TO BE DONE PER MONTH","row":3,"col":4,"rowspan":1,"colspan":1},{"text":"DISCUSSION TO PROPOSAL CONVERSION RATIO (CURRENT RATIO)","row":3,"col":5,"rowspan":1,"colspan":1},{"text":"# PROPOSALS TO BE GENERATED PER MONTH","row":3,"col":6,"rowspan":1,"colspan":1},{"text":"PIPELINE VALUE PER MONTH","row":3,"col":7,"rowspan":1,"colspan":1},{"text":"PROPOSAL TO ORDERBOOK (CURRENT RATIO)","row":3,"col":8,"rowspan":1,"colspan":1},{"text":"# CONTRACTS GENERATED PER MONTH","row":3,"col":9,"rowspan":1,"colspan":1},{"text":"ORDER BOOK VALUE GENERATED PER MONTH","row":3,"col":10,"rowspan":1,"colspan":1},{"text":"AVG TARGET PER MONTH","row":3,"col":11,"rowspan":1,"colspan":1},{"text":"SHORTFALL / SURPLUS","row":3,"col":12,"rowspan":1,"colspan":1},{"text":"ANNUAL","row":4,"col":0,"rowspan":1,"colspan":13},{"text":"DATA FROM","row":5,"col":0,"rowspan":1,"colspan":1},{"text":"TARGET SHEET","row":5,"col":1,"rowspan":1,"colspan":1},{"text":"APRIL TO JAN CONTRACT AVG","row":5,"col":2,"rowspan":1,"colspan":1},{"text":"STEP 1 / STEP 2","row":5,"col":3,"rowspan":1,"colspan":1},{"text":"ACCOUNT MANAGEMENT PLAN","row":5,"col":4,"rowspan":1,"colspan":1},{"text":"YTD DAILY ACTIVITY REPORT (PROPOSAL / DISCUSSION %)","row":5,"col":5,"rowspan":1,"colspan":1},{"text":"STEP 4 * STEP 5","row":5,"col":6,"rowspan":1,"colspan":1},{"text":"STEP 6 * STEP 2","row":5,"col":7,"rowspan":1,"colspan":1},{"text":"YTD DAILY ACTIVITY REPORT (PROPOSAL / BUSINESS GENERATED %)","row":5,"col":8,"rowspan":1,"colspan":1},{"text":"STEP 6 * STEP 8","row":5,"col":9,"rowspan":1,"colspan":1},{"text":"STEP 9 * STEP 2","row":5,"col":10,"rowspan":1,"colspan":1},{"text":"STEP 1 / 12","row":5,"col":11,"rowspan":1,"colspan":1},{"text":"STEP 10- STEP 11","row":5,"col":12,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>请从 92.jpg 的“Funnel management plan conversion rates”中提取：Account Manager。</t>
+  </si>
+  <si>
+    <t>Account Manager</t>
+  </si>
+  <si>
+    <t>Debash Mukherjee</t>
+  </si>
+  <si>
+    <t>Debajit Mukherjee</t>
+  </si>
+  <si>
+    <t>请恢复 93.jpg 中“ASCII Summary records table”的表头行结构。</t>
+  </si>
+  <si>
+    <t>{"row_count":5,"col_count":3,"cells":[{"text":"XXX","row":0,"col":0,"rowspan":1,"colspan":1},{"text":"Summary","row":0,"col":1,"rowspan":1,"colspan":2},{"text":"Description","row":1,"col":1,"rowspan":1,"colspan":1},{"text":"Variable Names(units)","row":1,"col":2,"rowspan":1,"colspan":1},{"text":"Note: The following records relate to first pass","row":2,"col":0,"rowspan":1,"colspan":3}]}</t>
+  </si>
+  <si>
+    <t>{"row_count":6,"col_count":3,"cells":[{"text":"XXX","row":0,"col":0,"rowspan":2,"colspan":1},{"text":"Summary","row":0,"col":1,"rowspan":1,"colspan":2},{"text":"Description","row":1,"col":1,"rowspan":1,"colspan":1},{"text":"Variable Names(units)","row":1,"col":2,"rowspan":1,"colspan":1},{"text":"Note: The following records relate to first pass","row":2,"col":0,"rowspan":1,"colspan":3}]}</t>
+  </si>
+  <si>
+    <t>{"row_count":5,"col_count":3,"cells":[{"text":"XXX","row":0,"col":0,"rowspan":2,"colspan":1},{"text":"Summary","row":0,"col":1,"rowspan":1,"colspan":2},{"text":"Description","row":1,"col":1,"rowspan":1,"colspan":1},{"text":"Variable Names(units)","row":1,"col":2,"rowspan":1,"colspan":1},{"text":"Note: The following records relate to first pass","row":2,"col":0,"rowspan":1,"colspan":3}]}</t>
+  </si>
+  <si>
+    <t>{"row_count":5,"col_count":3,"cells":[{"text":"XXX","row":0,"col":0,"rowspan":2,"colspan":1},{"text":"Summary","row":0,"col":1,"rowspan":1,"colspan":2},{"text":"Description","row":1,"col":1,"rowspan":1,"colspan":1},{"text":"Variable Names(units)","row":1,"col":2,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>请从 93.jpg 的“ASCII Summary records table”中提取：RECORDS 下 basic structure 的变量名。</t>
+  </si>
+  <si>
+    <t>["NNN","NNN1","NNN2","NNNNN2","XYZDDD","SOURCE","TARGET"]</t>
+  </si>
+  <si>
+    <t>NNN, NNN1, NNN2, NNNNNNN2, XYZDDD, SOURCE, TARGET</t>
+  </si>
+  <si>
+    <t>["NNN","NNN1","NNN2","NNNNNN2","XYZDDD","SOURCE","TARGET"]</t>
+  </si>
+  <si>
+    <t>[""]</t>
+  </si>
+  <si>
+    <t>{"row_count":39,"col_count":25,"cells":[{"text":"合金牌号","row":0,"col":0,"rowspan":4,"colspan":1},{"text":"名义化学成分","row":0,"col":1,"rowspan":4,"colspan":1},{"text":"化学成分(质量分数)/%","row":0,"col":2,"rowspan":1,"colspan":23},{"text":"主要成分","row":1,"col":2,"rowspan":1,"colspan":16},{"text":"杂质,不大于","row":1,"col":18,"rowspan":1,"colspan":7},{"text":"Ti","row":2,"col":2,"rowspan":2,"colspan":1},{"text":"Al","row":2,"col":3,"rowspan":2,"colspan":1},{"text":"Si","row":2,"col":4,"rowspan":2,"colspan":1},{"text":"V","row":2,"col":5,"rowspan":2,"colspan":1},{"text":"Mn","row":2,"col":6,"rowspan":2,"colspan":1},{"text":"Fe","row":2,"col":7,"rowspan":2,"colspan":1},{"text":"Ni","row":2,"col":8,"rowspan":2,"colspan":1},{"text":"Cu","row":2,"col":9,"rowspan":2,"colspan":1},{"text":"Zr","row":2,"col":10,"rowspan":2,"colspan":1},{"text":"Nb","row":2,"col":11,"rowspan":2,"colspan":1},{"text":"Mo","row":2,"col":12,"rowspan":2,"colspan":1},{"text":"Ru","row":2,"col":13,"rowspan":2,"colspan":1},{"text":"Pd","row":2,"col":14,"rowspan":2,"colspan":1},{"text":"Sn","row":2,"col":15,"rowspan":2,"colspan":1},{"text":"Ta","row":2,"col":16,"rowspan":2,"colspan":1},{"text":"Nd","row":2,"col":17,"rowspan":2,"colspan":1},{"text":"Fe","row":2,"col":18,"rowspan":2,"colspan":1},{"text":"C","row":2,"col":19,"rowspan":2,"colspan":1},{"text":"N","row":2,"col":20,"rowspan":2,"colspan":1},{"text":"H","row":2,"col":21,"rowspan":2,"colspan":1},{"text":"O","row":2,"col":22,"rowspan":2,"colspan":1},{"text":"其他元素","row":2,"col":23,"rowspan":1,"colspan":2},{"text":"单一","row":3,"col":23,"rowspan":1,"colspan":1},{"text":"总和","row":3,"col":24,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>{"row_count":21,"col_count":20,"cells":[{"text":"合金牌号","row":0,"col":0,"rowspan":4,"colspan":1},{"text":"名义化学成分","row":0,"col":1,"rowspan":4,"colspan":1},{"text":"化学成分(质量分数)/%","row":0,"col":2,"rowspan":1,"colspan":18},{"text":"主要成分","row":1,"col":2,"rowspan":1,"colspan":11},{"text":"杂质,不大于","row":1,"col":13,"rowspan":1,"colspan":7},{"text":"Ti","row":2,"col":2,"rowspan":2,"colspan":1},{"text":"Al","row":2,"col":3,"rowspan":2,"colspan":1},{"text":"Si","row":2,"col":4,"rowspan":2,"colspan":1},{"text":"V","row":2,"col":5,"rowspan":2,"colspan":1},{"text":"Cr","row":2,"col":6,"rowspan":2,"colspan":1},{"text":"Fe","row":2,"col":7,"rowspan":2,"colspan":1},{"text":"Zr","row":2,"col":8,"rowspan":2,"colspan":1},{"text":"Nb","row":2,"col":9,"rowspan":2,"colspan":1},{"text":"Mo","row":2,"col":10,"rowspan":2,"colspan":1},{"text":"Pd","row":2,"col":11,"rowspan":2,"colspan":1},{"text":"Sn","row":2,"col":12,"rowspan":2,"colspan":1},{"text":"Fe","row":2,"col":13,"rowspan":2,"colspan":1},{"text":"C","row":2,"col":14,"rowspan":2,"colspan":1},{"text":"N","row":2,"col":15,"rowspan":2,"colspan":1},{"text":"H","row":2,"col":16,"rowspan":2,"colspan":1},{"text":"O","row":2,"col":17,"rowspan":2,"colspan":1},{"text":"其他元素","row":2,"col":18,"rowspan":1,"colspan":2},{"text":"单一","row":3,"col":18,"rowspan":1,"colspan":1},{"text":"总和","row":3,"col":19,"rowspan":1,"colspan":1}]}</t>
+  </si>
+  <si>
+    <t>["营业成本","税金及附加","销售费用","管理费用","研发费用","财务费用","其他收益","投资收益(损失以\"-\"号填列)","净敞口套期收益(损失以\"-\"号填列)","公允价值变动收益(损失以\"-\"号填列)","信用减值损失(损失以\"-\"号填列)","资产减值损失(损失以\"-\"号填列)","资产处置收益(损失以\"-\"号填列)"]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>["10.41%","合同签订之日起至2024年12月31日，具体项目及工期按每个项目施工合同中确定","王永平、梁卫凤、胡浙明","2023年4月12日"]</t>
-  </si>
-  <si>
-    <t>["10.41%","合同签订之日起至2024年12月31日，具体项目及工期按每个项目施工合同中确定","['王永平', '梁卫凤', '胡浙明']","2023年4月12日"]</t>
-  </si>
-  <si>
-    <t>["10.41%","合同签订之日起至2024年12月31日，具体项目及工期按每个项目施工合同中确定","王永平","梁卫凤","胡浙明","2023年4月12日"]</t>
-  </si>
-  <si>
-    <t>杨周</t>
-  </si>
-  <si>
-    <t>Number of passengers 乘车人数</t>
-  </si>
-  <si>
-    <t>Pick-Up Locations 接送地点</t>
-  </si>
-  <si>
-    <t>中英混合</t>
-  </si>
-  <si>
-    <t>Iron 2%</t>
-  </si>
-  <si>
-    <t>Amount Per Serving</t>
-  </si>
-  <si>
-    <t>Iron</t>
-  </si>
-  <si>
-    <t>% Daily Value</t>
-  </si>
-  <si>
-    <t>% RP % AR</t>
-  </si>
-  <si>
-    <t>% RI* % AR**</t>
-  </si>
-  <si>
-    <t>% RI* % AR*</t>
-  </si>
-  <si>
-    <t>请提取“套餐分类之一”对应的值。</t>
-  </si>
-  <si>
-    <t>酷睿i7-8750H 8G DDR4</t>
-  </si>
-  <si>
-    <t>官方标配(原封)</t>
-  </si>
-  <si>
-    <t>家庭版</t>
-  </si>
-  <si>
-    <t>请按表中顺序列出以下字段的答案：最低活动价、最高活动价、备注中是否含退换规则、表格下方说明条数。</t>
-  </si>
-  <si>
-    <t>["20299","59999","true","3"]</t>
-  </si>
-  <si>
-    <t>[399,79999,"否",3]</t>
-  </si>
-  <si>
-    <t>[399,79999,"是",3]</t>
-  </si>
-  <si>
-    <t>包含蓝色标签的模块一共有多少个？</t>
-  </si>
-  <si>
-    <t>英伟达</t>
-  </si>
-  <si>
-    <t>澎湃·美数课</t>
-  </si>
-  <si>
-    <t>CEO总薪酬</t>
-  </si>
-  <si>
-    <t>请恢复 59.pdf 中“Table 6 DeepSeek-V4-Pro-Max 与其他模型对比”的表头行结构。</t>
-  </si>
-  <si>
-    <t>{"row_count":1,"col_count":7,"cells":[{"text":"Benchmark (Metric)","row":0,"col":0,"rowspan":1,"colspan":1},{"text":"Opus-4.6 Max","row":0,"col":1,"rowspan":1,"colspan":1},{"text":"GPT-5.4 xHigh","row":0,"col":2,"rowspan":1,"colspan":1},{"text":"Gemini-3.1-Pro High","row":0,"col":3,"rowspan":1,"colspan":1},{"text":"K2.6 Thinking","row":0,"col":4,"rowspan":1,"colspan":1},{"text":"GLM-5.1 Thinking","row":0,"col":5,"rowspan":1,"colspan":1},{"text":"DS-V4-Pro Max","row":0,"col":6,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>{"row_count":24,"col_count":7,"cells":[{"text":"Benchmark (Metric)","row":0,"col":0,"rowspan":2,"colspan":1},{"text":"Opus-4.6","row":0,"col":1,"rowspan":1,"colspan":1},{"text":"GPT-5.4","row":0,"col":2,"rowspan":1,"colspan":1},{"text":"Gemini-3.1-Pro","row":0,"col":3,"rowspan":1,"colspan":1},{"text":"K2.6","row":0,"col":4,"rowspan":1,"colspan":1},{"text":"GLM-5.1","row":0,"col":5,"rowspan":1,"colspan":1},{"text":"DS-V4-Pro","row":0,"col":6,"rowspan":1,"colspan":1},{"text":"Max","row":1,"col":1,"rowspan":1,"colspan":1},{"text":"xHigh","row":1,"col":2,"rowspan":1,"colspan":1},{"text":"High","row":1,"col":3,"rowspan":1,"colspan":1},{"text":"Thinking","row":1,"col":4,"rowspan":1,"colspan":1},{"text":"Thinking","row":1,"col":5,"rowspan":1,"colspan":1},{"text":"Max","row":1,"col":6,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>{"row_count":23,"col_count":8,"cells":[{"text":"Benchmark (Metric)","row":0,"col":0,"rowspan":1,"colspan":2},{"text":"Opus-4.6 Max","row":0,"col":2,"rowspan":1,"colspan":1},{"text":"GPT-5.4 xHigh","row":0,"col":3,"rowspan":1,"colspan":1},{"text":"Gemini-3.1-Pro High","row":0,"col":4,"rowspan":1,"colspan":1},{"text":"K2.6 Thinking","row":0,"col":5,"rowspan":1,"colspan":1},{"text":"GLM-5.1 Thinking","row":0,"col":6,"rowspan":1,"colspan":1},{"text":"DS-V4-Pro Max","row":0,"col":7,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>请从 61.pdf 的“Table 12 中文功能写作评估”中提取：Business Writing 的 Subtotal 行。</t>
-  </si>
-  <si>
-    <t>["Business Writing","Subtotal (小计)",1349,879,436,34,"65.16","32.32","2.52"]</t>
-  </si>
-  <si>
-    <t>["Subtotal (小计)","1349","879","436","34","65.16","32.32","2.52"]</t>
-  </si>
-  <si>
-    <t>["Subtotal (小计)",1349,879,436,34,"65.16","32.32","2.52"]</t>
-  </si>
-  <si>
-    <t>["Subtotal (小计)",1349,879,436,34,65.16,32.32,2.52]</t>
-  </si>
-  <si>
-    <t>请恢复 62.pdf 中“Table 13 中文创意写作评估”的表头行结构。</t>
-  </si>
-  <si>
-    <t>{"row_count":3,"col_count":14,"cells":[{"text":"Subcategory (文体)","row":0,"col":0,"rowspan":2,"colspan":1},{"text":"#","row":0,"col":1,"rowspan":2,"colspan":1},{"text":"Instruction Following(指令遵循)","row":0,"col":2,"rowspan":1,"colspan":6},{"text":"Writing Quality (写作质量)","row":0,"col":8,"rowspan":1,"colspan":6},{"text":"DS","row":1,"col":2,"rowspan":1,"colspan":1},{"text":"Gem","row":1,"col":3,"rowspan":1,"colspan":1},{"text":"Tie","row":1,"col":4,"rowspan":1,"colspan":1},{"text":"DS%","row":1,"col":5,"rowspan":1,"colspan":1},{"text":"Gem%","row":1,"col":6,"rowspan":1,"colspan":1},{"text":"Tie%","row":1,"col":7,"rowspan":1,"colspan":1},{"text":"DS","row":1,"col":8,"rowspan":1,"colspan":1},{"text":"Gem","row":1,"col":9,"rowspan":1,"colspan":1},{"text":"Tie","row":1,"col":10,"rowspan":1,"colspan":1},{"text":"DS%","row":1,"col":11,"rowspan":1,"colspan":1},{"text":"Gem%","row":1,"col":12,"rowspan":1,"colspan":1},{"text":"Tie%","row":1,"col":13,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>{"row_count":20,"col_count":14,"cells":[{"text":"Subcategory (文体)","row":0,"col":0,"rowspan":2,"colspan":1},{"text":"#","row":0,"col":1,"rowspan":2,"colspan":1},{"text":"Instruction Following(指令遵循)","row":0,"col":2,"rowspan":1,"colspan":6},{"text":"Writing Quality (写作质量)","row":0,"col":8,"rowspan":1,"colspan":6},{"text":"DS","row":1,"col":2,"rowspan":1,"colspan":1},{"text":"Gem","row":1,"col":3,"rowspan":1,"colspan":1},{"text":"Tie","row":1,"col":4,"rowspan":1,"colspan":1},{"text":"DS%","row":1,"col":5,"rowspan":1,"colspan":1},{"text":"Gem%","row":1,"col":6,"rowspan":1,"colspan":1},{"text":"Tie%","row":1,"col":7,"rowspan":1,"colspan":1},{"text":"DS","row":1,"col":8,"rowspan":1,"colspan":1},{"text":"Gem","row":1,"col":9,"rowspan":1,"colspan":1},{"text":"Tie","row":1,"col":10,"rowspan":1,"colspan":1},{"text":"DS%","row":1,"col":11,"rowspan":1,"colspan":1},{"text":"Gem%","row":1,"col":12,"rowspan":1,"colspan":1},{"text":"Tie%","row":1,"col":13,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>{"row_count":21,"col_count":14,"cells":[{"text":"Subcategory (文体)","row":0,"col":0,"rowspan":2,"colspan":1},{"text":"#","row":0,"col":1,"rowspan":2,"colspan":1},{"text":"Instruction Following(指令遵循)","row":0,"col":2,"rowspan":1,"colspan":6},{"text":"Writing Quality (写作质量)","row":0,"col":8,"rowspan":1,"colspan":6},{"text":"DS","row":1,"col":2,"rowspan":1,"colspan":1},{"text":"Gem","row":1,"col":3,"rowspan":1,"colspan":1},{"text":"Tie","row":1,"col":4,"rowspan":1,"colspan":1},{"text":"DS%","row":1,"col":5,"rowspan":1,"colspan":1},{"text":"Gem%","row":1,"col":6,"rowspan":1,"colspan":1},{"text":"Tie%","row":1,"col":7,"rowspan":1,"colspan":1},{"text":"DS","row":1,"col":8,"rowspan":1,"colspan":1},{"text":"Gem","row":1,"col":9,"rowspan":1,"colspan":1},{"text":"Tie","row":1,"col":10,"rowspan":1,"colspan":1},{"text":"DS%","row":1,"col":11,"rowspan":1,"colspan":1},{"text":"Gem%","row":1,"col":12,"rowspan":1,"colspan":1},{"text":"Tie%","row":1,"col":13,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>请从 63.pdf 的“Table 1 catchment site characteristics”中提取：Cathedral Peak 3 (SA) 的 Mean annual rainfall (mm)。</t>
-  </si>
-  <si>
-    <t>1436</t>
-  </si>
-  <si>
-    <t>1134</t>
-  </si>
-  <si>
-    <t>1504</t>
-  </si>
-  <si>
-    <t>请找出 BFI 最高的 catchment。</t>
-  </si>
-  <si>
-    <t>Lambrechbos A (SA)</t>
-  </si>
-  <si>
-    <t>Lambrechbos B (SA)</t>
-  </si>
-  <si>
-    <t>Lambrechthos B (SA)</t>
-  </si>
-  <si>
-    <t>Lambrechtbos B (SA)</t>
-  </si>
-  <si>
-    <t>请从 65.pdf 的“盈利预测和财务指标”中提取：合理估值区间。</t>
-  </si>
-  <si>
-    <t>6.50–7.00 元</t>
-  </si>
-  <si>
-    <t>6.50 - 7.00 元</t>
-  </si>
-  <si>
-    <t>6.50-7.00元</t>
-  </si>
-  <si>
-    <t>请计算 2024-2026 年调整后归母净利润合计。</t>
-  </si>
-  <si>
-    <t>74.6</t>
-  </si>
-  <si>
-    <t>请找出 WTQ 表中 test 最高的模型。</t>
-  </si>
-  <si>
-    <t>TAPAS_LARGE inter-sqa TABLEFORMER_LARGE inter-sqa</t>
-  </si>
-  <si>
-    <t>TABLEFORMER_LARGE inter-sqa</t>
-  </si>
-  <si>
-    <t>TableFormerLarge inter-sqa</t>
-  </si>
-  <si>
-    <t>请恢复 69.pdf 中“Table 1 SQA perturbation results”的表头行结构。</t>
-  </si>
-  <si>
-    <t>{"row_count":3,"col_count":6,"cells":[{"text":"Before Perturb","row":0,"col":0,"rowspan":1,"colspan":3},{"text":"After Perturb","row":0,"col":3,"rowspan":1,"colspan":2},{"text":"ALL","row":1,"col":0,"rowspan":1,"colspan":1},{"text":"SEQ","row":1,"col":1,"rowspan":1,"colspan":1},{"text":"ALL_d","row":1,"col":2,"rowspan":1,"colspan":1},{"text":"ALL","row":1,"col":3,"rowspan":1,"colspan":1},{"text":"VP","row":1,"col":4,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>{"row_count":14,"col_count":6,"cells":[{"text":"Before Perturb","row":0,"col":1,"rowspan":1,"colspan":3},{"text":"After Perturb","row":0,"col":4,"rowspan":1,"colspan":2},{"text":"ALL","row":1,"col":1,"rowspan":1,"colspan":1},{"text":"SEQ","row":1,"col":2,"rowspan":1,"colspan":1},{"text":"ALLd","row":1,"col":3,"rowspan":1,"colspan":1},{"text":"ALL","row":1,"col":4,"rowspan":1,"colspan":1},{"text":"VP","row":1,"col":5,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>{"row_count":14,"col_count":6,"cells":[{"text":"","row":0,"col":0,"rowspan":2,"colspan":1},{"text":"Before Perturb","row":0,"col":1,"rowspan":1,"colspan":3},{"text":"After Perturb","row":0,"col":4,"rowspan":1,"colspan":2},{"text":"ALL","row":1,"col":1,"rowspan":1,"colspan":1},{"text":"SEQ","row":1,"col":2,"rowspan":1,"colspan":1},{"text":"ALL_d","row":1,"col":3,"rowspan":1,"colspan":1},{"text":"ALL","row":1,"col":4,"rowspan":1,"colspan":1},{"text":"VP","row":1,"col":5,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>请找出表中 VP 最高的模型。</t>
-  </si>
-  <si>
-    <t>TAPASBASE inter</t>
-  </si>
-  <si>
-    <t>TAPASLARGE</t>
-  </si>
-  <si>
-    <t>TapasLarge</t>
-  </si>
-  <si>
-    <t>请恢复 70.pdf 中“Table II real-time stereo matching methods”的表头行结构。</t>
-  </si>
-  <si>
-    <t>{"row_count":2,"col_count":5,"cells":[{"text":"Method","row":0,"col":0,"rowspan":1,"colspan":1},{"text":"GPU","row":0,"col":1,"rowspan":1,"colspan":1},{"text":"MDE/s¹","row":0,"col":2,"rowspan":1,"colspan":1},{"text":"FPS²","row":0,"col":3,"rowspan":1,"colspan":1},{"text":"Error³","row":0,"col":4,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>{"row_count":9,"col_count":5,"cells":[{"text":"Method","row":0,"col":0,"rowspan":1,"colspan":1},{"text":"GPU","row":0,"col":1,"rowspan":1,"colspan":1},{"text":"MDE/s1","row":0,"col":2,"rowspan":1,"colspan":1},{"text":"FPS2","row":0,"col":3,"rowspan":1,"colspan":1},{"text":"Error3","row":0,"col":4,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>{"row_count":9,"col_count":5,"cells":[{"text":"Method","row":0,"col":0,"rowspan":1,"colspan":1},{"text":"GPU","row":0,"col":1,"rowspan":1,"colspan":1},{"text":"MDE/s¹","row":0,"col":2,"rowspan":1,"colspan":1},{"text":"FPS²","row":0,"col":3,"rowspan":1,"colspan":1},{"text":"Error³","row":0,"col":4,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>请从 71.pdf 的“表1 工业纯钛、α型和近α型钛合金牌号和化学成分”中提取：TA11 的名义化学成分。</t>
-  </si>
-  <si>
-    <t>Al: 2.0～3.0, Mo: 1.0～2.0, Nb: 0.5～1.5</t>
-  </si>
-  <si>
-    <t>Ti-6.5Al-4.5Sn-2Zr-1Mo-1Nd-0.25Si</t>
-  </si>
-  <si>
-    <t>Ti-8Al-1Mo-1V</t>
-  </si>
-  <si>
-    <t>请从 71.pdf 的“表1 工业纯钛、α型和近α型钛合金牌号和化学成分”中提取：TA14 的 Zr 范围。</t>
-  </si>
-  <si>
-    <t>0.6~1.2</t>
-  </si>
-  <si>
-    <t>0.5~1.5</t>
-  </si>
-  <si>
-    <t>1.5~2.5</t>
-  </si>
-  <si>
-    <t>4.0~6.0</t>
-  </si>
-  <si>
-    <t>请找出该页表头中横跨 Fe、C、N、H、O 的上级栏目名称。</t>
-  </si>
-  <si>
-    <t>主要成分</t>
-  </si>
-  <si>
-    <t>杂质-不大于</t>
-  </si>
-  <si>
-    <t>杂质，不大于</t>
-  </si>
-  <si>
-    <t>杂质,不大于</t>
-  </si>
-  <si>
-    <t>请从 72.pdf 的“表1（续）和表2 β型和近β型钛合金牌号及化学成分”中提取：TB2 的名义化学成分。</t>
-  </si>
-  <si>
-    <t>余量</t>
-  </si>
-  <si>
-    <t>Ti-5Mo-5V-8Cr-3Al</t>
-  </si>
-  <si>
-    <t>Ti-5Mo-5V-8Cr-5Al</t>
-  </si>
-  <si>
-    <t>请从 72.pdf 的“表1（续）和表2 β型和近β型钛合金牌号及化学成分”中提取：TB4 的 Al 范围。</t>
-  </si>
-  <si>
-    <t>2.5～3.5</t>
-  </si>
-  <si>
-    <t>4.5～5.5</t>
-  </si>
-  <si>
-    <t>3.0~4.5</t>
-  </si>
-  <si>
-    <t>3.0～4.5</t>
-  </si>
-  <si>
-    <t>请恢复 73.pdf 中“表2（续）”的表头行结构。</t>
-  </si>
-  <si>
-    <t>{"row_count":3,"col_count":18,"cells":[{"text":"合金牌号","row":0,"col":0,"rowspan":3,"colspan":1},{"text":"名义化学成分","row":0,"col":1,"rowspan":3,"colspan":1},{"text":"主要成分","row":0,"col":2,"rowspan":1,"colspan":14},{"text":"杂质，不大于","row":0,"col":16,"rowspan":1,"colspan":2},{"text":"Ti","row":1,"col":2,"rowspan":2,"colspan":1},{"text":"Al","row":1,"col":3,"rowspan":2,"colspan":1},{"text":"Si","row":1,"col":4,"rowspan":2,"colspan":1},{"text":"V","row":1,"col":5,"rowspan":2,"colspan":1},{"text":"Cr","row":1,"col":6,"rowspan":2,"colspan":1},{"text":"Fe","row":1,"col":7,"rowspan":2,"colspan":1},{"text":"Zr","row":1,"col":8,"rowspan":2,"colspan":1},{"text":"Nb","row":1,"col":9,"rowspan":2,"colspan":1},{"text":"Mo","row":1,"col":10,"rowspan":2,"colspan":1},{"text":"Pd","row":1,"col":11,"rowspan":2,"colspan":1},{"text":"Sn","row":1,"col":12,"rowspan":2,"colspan":1},{"text":"Fe","row":1,"col":13,"rowspan":2,"colspan":1},{"text":"C","row":1,"col":14,"rowspan":2,"colspan":1},{"text":"N","row":1,"col":15,"rowspan":2,"colspan":1},{"text":"H","row":1,"col":16,"rowspan":2,"colspan":1},{"text":"O","row":1,"col":17,"rowspan":2,"colspan":1},{"text":"其他元素","row":2,"col":16,"rowspan":1,"colspan":1},{"text":"单一","row":2,"col":17,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>{"row_count":3,"col_count":20,"cells":[{"text":"合金牌号","row":0,"col":0,"rowspan":2,"colspan":1},{"text":"名义化学成分","row":0,"col":1,"rowspan":2,"colspan":1},{"text":"化学成分(质量分数)/%","row":0,"col":2,"rowspan":1,"colspan":18},{"text":"主要成分","row":1,"col":2,"rowspan":1,"colspan":11},{"text":"杂质,不大于","row":1,"col":13,"rowspan":1,"colspan":5},{"text":"其他元素","row":1,"col":18,"rowspan":1,"colspan":2},{"text":"Ti","row":2,"col":2,"rowspan":1,"colspan":1},{"text":"Al","row":2,"col":3,"rowspan":1,"colspan":1},{"text":"Si","row":2,"col":4,"rowspan":1,"colspan":1},{"text":"V","row":2,"col":5,"rowspan":1,"colspan":1},{"text":"Cr","row":2,"col":6,"rowspan":1,"colspan":1},{"text":"Fe","row":2,"col":7,"rowspan":1,"colspan":1},{"text":"Zr","row":2,"col":8,"rowspan":1,"colspan":1},{"text":"Nb","row":2,"col":9,"rowspan":1,"colspan":1},{"text":"Mo","row":2,"col":10,"rowspan":1,"colspan":1},{"text":"Pd","row":2,"col":11,"rowspan":1,"colspan":1},{"text":"Sn","row":2,"col":12,"rowspan":1,"colspan":1},{"text":"Fe","row":2,"col":13,"rowspan":1,"colspan":1},{"text":"C","row":2,"col":14,"rowspan":1,"colspan":1},{"text":"N","row":2,"col":15,"rowspan":1,"colspan":1},{"text":"H","row":2,"col":16,"rowspan":1,"colspan":1},{"text":"O","row":2,"col":17,"rowspan":1,"colspan":1},{"text":"单一","row":2,"col":18,"rowspan":1,"colspan":1},{"text":"总和","row":2,"col":19,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>{"row_count":17,"col_count":21,"cells":[{"text":"合金牌号","row":0,"col":0,"rowspan":4,"colspan":1},{"text":"名义化学成分","row":0,"col":1,"rowspan":4,"colspan":1},{"text":"化学成分（质量分数）/%","row":0,"col":2,"rowspan":1,"colspan":19},{"text":"主要成分","row":1,"col":2,"rowspan":1,"colspan":12},{"text":"杂质，不大于","row":1,"col":14,"rowspan":1,"colspan":7},{"text":"Ti","row":2,"col":2,"rowspan":2,"colspan":1},{"text":"Al","row":2,"col":3,"rowspan":2,"colspan":1},{"text":"Si","row":2,"col":4,"rowspan":2,"colspan":1},{"text":"V","row":2,"col":5,"rowspan":2,"colspan":1},{"text":"Cr","row":2,"col":6,"rowspan":2,"colspan":1},{"text":"Mn","row":2,"col":7,"rowspan":2,"colspan":1},{"text":"Fe","row":2,"col":8,"rowspan":2,"colspan":1},{"text":"Zr","row":2,"col":9,"rowspan":2,"colspan":1},{"text":"Nb","row":2,"col":10,"rowspan":2,"colspan":1},{"text":"Mo","row":2,"col":11,"rowspan":2,"colspan":1},{"text":"Pd","row":2,"col":12,"rowspan":2,"colspan":1},{"text":"Sn","row":2,"col":13,"rowspan":2,"colspan":1},{"text":"Fe","row":2,"col":14,"rowspan":2,"colspan":1},{"text":"C","row":2,"col":15,"rowspan":2,"colspan":1},{"text":"N","row":2,"col":16,"rowspan":2,"colspan":1},{"text":"H","row":2,"col":17,"rowspan":2,"colspan":1},{"text":"O","row":2,"col":18,"rowspan":2,"colspan":1},{"text":"其他元素","row":2,"col":19,"rowspan":1,"colspan":2},{"text":"单一","row":3,"col":19,"rowspan":1,"colspan":1},{"text":"总和","row":3,"col":20,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>{"row_count":18,"col_count":20,"cells":[{"text":"合金牌号","row":0,"col":0,"rowspan":4,"colspan":1},{"text":"名义化学成分","row":0,"col":1,"rowspan":4,"colspan":1},{"text":"化学成分(质量分数)/%","row":0,"col":2,"rowspan":1,"colspan":18},{"text":"主要成分","row":1,"col":2,"rowspan":1,"colspan":11},{"text":"杂质,不大于","row":1,"col":13,"rowspan":1,"colspan":7},{"text":"Ti","row":2,"col":2,"rowspan":2,"colspan":1},{"text":"Al","row":2,"col":3,"rowspan":2,"colspan":1},{"text":"Si","row":2,"col":4,"rowspan":2,"colspan":1},{"text":"V","row":2,"col":5,"rowspan":2,"colspan":1},{"text":"Cr","row":2,"col":6,"rowspan":2,"colspan":1},{"text":"Fe","row":2,"col":7,"rowspan":2,"colspan":1},{"text":"Zr","row":2,"col":8,"rowspan":2,"colspan":1},{"text":"Nb","row":2,"col":9,"rowspan":2,"colspan":1},{"text":"Mo","row":2,"col":10,"rowspan":2,"colspan":1},{"text":"Pd","row":2,"col":11,"rowspan":2,"colspan":1},{"text":"Sn","row":2,"col":12,"rowspan":2,"colspan":1},{"text":"Fe","row":2,"col":13,"rowspan":2,"colspan":1},{"text":"C","row":2,"col":14,"rowspan":2,"colspan":1},{"text":"N","row":2,"col":15,"rowspan":2,"colspan":1},{"text":"H","row":2,"col":16,"rowspan":2,"colspan":1},{"text":"O","row":2,"col":17,"rowspan":2,"colspan":1},{"text":"其他元素","row":2,"col":18,"rowspan":1,"colspan":2},{"text":"单一","row":3,"col":18,"rowspan":1,"colspan":1},{"text":"总和","row":3,"col":19,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>请从 73.pdf 的“表2（续）”中TB6的铁含量是多少。</t>
-  </si>
-  <si>
-    <t>1.8~2.2</t>
-  </si>
-  <si>
-    <t>1.8~2.8</t>
-  </si>
-  <si>
-    <t>1.6～2.2</t>
-  </si>
-  <si>
-    <t>请从 73.pdf 的“表2（续）”中那种合金的杂质含量最多</t>
-  </si>
-  <si>
-    <t>TC17</t>
-  </si>
-  <si>
-    <t>TB9</t>
-  </si>
-  <si>
-    <t>TB8</t>
-  </si>
-  <si>
-    <t>请从 73.pdf 的“表2（续）”中提取：表格中的 Al 列单元格内容。</t>
-  </si>
-  <si>
-    <t>["2.5～3.5","2.6～3.4","—","2.5～3.5","3.0～4.0","2.5～3.5","—","3.0～4.5","3.5～4.5","—","余量","余量","—","余量","余量","余量","余量","余量","余量","余量","余量","余量","余量","余量","余量","余量","余量","余量","余量","余量","余量","余量"]</t>
-  </si>
-  <si>
-    <t>["2.5~3.5","2.8~3.4","—","2.5~3.5","3.0~4.0","2.5~3.5","余量","—","3.0~4.5","—","3.5~4.5","2.5~3.5","3.5~4.5"]</t>
-  </si>
-  <si>
-    <t>["2.5～3.5","2.6～3.4","—","2.5～3.5","3.0～4.0","2.5～3.5","—","—","3.0～4.5","—","3.5～4.5","2.5～3.5","3.5～4.5"]</t>
-  </si>
-  <si>
-    <t>["2.5~3.5","2.6~3.4","—","2.5~3.5","3.0~4.0","2.5~3.5","—","—","3.0~4.5","—","3.5~4.5","2.5~3.5","3.5~5.5"]</t>
-  </si>
-  <si>
-    <t>请从 73.pdf 的““表2（续）”中Mo元素含量大于 0.5 的有多少个?</t>
-  </si>
-  <si>
-    <t>请从 73.pdf 的““表2（续）”中TB14中含量最多的元素？</t>
-  </si>
-  <si>
-    <t>Al</t>
-  </si>
-  <si>
-    <t>Ti</t>
-  </si>
-  <si>
-    <t>Nb</t>
-  </si>
-  <si>
-    <t>请恢复 75.jpg 中“Pro Forma Capitalization Table”的表头行结构。</t>
-  </si>
-  <si>
-    <t>{"row_count":3,"col_count":10,"cells":[{"text":"Common Stock","row":0,"col":0,"rowspan":1,"colspan":4},{"text":"Investor Rounds","row":0,"col":4,"rowspan":1,"colspan":4},{"text":"Exit","row":0,"col":8,"rowspan":1,"colspan":2},{"text":"Founders' Shares","row":1,"col":0,"rowspan":1,"colspan":2},{"text":"Stock Options","row":1,"col":2,"rowspan":1,"colspan":2},{"text":"$","row":1,"col":4,"rowspan":1,"colspan":1},{"text":"Round 1","row":1,"col":5,"rowspan":1,"colspan":2},{"text":"$","row":1,"col":7,"rowspan":1,"colspan":1},{"text":"Round 2","row":1,"col":8,"rowspan":1,"colspan":2},{"text":"Shares","row":2,"col":0,"rowspan":1,"colspan":1},{"text":"%","row":2,"col":1,"rowspan":1,"colspan":1},{"text":"Shares","row":2,"col":2,"rowspan":1,"colspan":1},{"text":"%","row":2,"col":3,"rowspan":1,"colspan":1},{"text":"Shares","row":2,"col":5,"rowspan":1,"colspan":1},{"text":"%","row":2,"col":6,"rowspan":1,"colspan":1},{"text":"Shares","row":2,"col":8,"rowspan":1,"colspan":1},{"text":"%","row":2,"col":9,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>{"row_count":25,"col_count":13,"cells":[{"text":"","row":0,"col":0,"rowspan":3,"colspan":1},{"text":"Common Stock","row":0,"col":1,"rowspan":1,"colspan":4},{"text":"Investor Rounds","row":0,"col":5,"rowspan":1,"colspan":6},{"text":"Exit","row":0,"col":11,"rowspan":1,"colspan":2},{"text":"Founders' Shares","row":1,"col":1,"rowspan":1,"colspan":2},{"text":"Stock Options","row":1,"col":3,"rowspan":1,"colspan":2},{"text":"Round 1","row":1,"col":5,"rowspan":1,"colspan":3},{"text":"Round 2","row":1,"col":8,"rowspan":1,"colspan":3},{"text":"$20,000,000","row":1,"col":11,"rowspan":1,"colspan":1},{"text":"Multiple","row":1,"col":12,"rowspan":1,"colspan":1},{"text":"Shares","row":2,"col":1,"rowspan":1,"colspan":1},{"text":"%","row":2,"col":2,"rowspan":1,"colspan":1},{"text":"Shares","row":2,"col":3,"rowspan":1,"colspan":1},{"text":"%","row":2,"col":4,"rowspan":1,"colspan":1},{"text":"$","row":2,"col":5,"rowspan":1,"colspan":1},{"text":"Shares","row":2,"col":6,"rowspan":1,"colspan":1},{"text":"%","row":2,"col":7,"rowspan":1,"colspan":1},{"text":"$","row":2,"col":8,"rowspan":1,"colspan":1},{"text":"Shares","row":2,"col":9,"rowspan":1,"colspan":1},{"text":"%","row":2,"col":10,"rowspan":1,"colspan":1},{"text":"","row":2,"col":11,"rowspan":1,"colspan":1},{"text":"","row":2,"col":12,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>{"row_count":33,"col_count":13,"cells":[{"text":"","row":0,"col":0,"rowspan":2,"colspan":1},{"text":"Common Stock","row":0,"col":1,"rowspan":1,"colspan":4},{"text":"Investor Rounds","row":0,"col":5,"rowspan":1,"colspan":6},{"text":"Exit","row":0,"col":11,"rowspan":1,"colspan":2},{"text":"Founders' Shares","row":1,"col":1,"rowspan":1,"colspan":2},{"text":"Stock Options","row":1,"col":3,"rowspan":1,"colspan":2},{"text":"Round 1","row":1,"col":5,"rowspan":1,"colspan":3},{"text":"Round 2","row":1,"col":8,"rowspan":1,"colspan":3},{"text":"$20000000","row":1,"col":11,"rowspan":1,"colspan":1},{"text":"Multiple","row":1,"col":12,"rowspan":1,"colspan":1},{"text":"Common","row":2,"col":0,"rowspan":1,"colspan":1},{"text":"Shares","row":2,"col":1,"rowspan":1,"colspan":1},{"text":"%","row":2,"col":2,"rowspan":1,"colspan":1},{"text":"Shares","row":2,"col":3,"rowspan":1,"colspan":1},{"text":"%","row":2,"col":4,"rowspan":1,"colspan":1},{"text":"$","row":2,"col":5,"rowspan":1,"colspan":1},{"text":"Shares","row":2,"col":6,"rowspan":1,"colspan":1},{"text":"%","row":2,"col":7,"rowspan":1,"colspan":1},{"text":"$","row":2,"col":8,"rowspan":1,"colspan":1},{"text":"Shares","row":2,"col":9,"rowspan":1,"colspan":1},{"text":"%","row":2,"col":10,"rowspan":1,"colspan":1},{"text":"","row":2,"col":11,"rowspan":1,"colspan":1},{"text":"","row":2,"col":12,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>{"row_count":20,"col_count":13,"cells":[{"text":"Common","row":0,"col":0,"rowspan":3,"colspan":1},{"text":"Common Stock","row":0,"col":1,"rowspan":1,"colspan":4},{"text":"Investor Rounds","row":0,"col":5,"rowspan":1,"colspan":6},{"text":"Exit","row":0,"col":11,"rowspan":1,"colspan":2},{"text":"Founders' Shares","row":1,"col":1,"rowspan":1,"colspan":2},{"text":"Stock Options","row":1,"col":3,"rowspan":1,"colspan":2},{"text":"Round 1","row":1,"col":5,"rowspan":1,"colspan":3},{"text":"Round 2","row":1,"col":8,"rowspan":1,"colspan":3},{"text":"$20000000","row":1,"col":11,"rowspan":2,"colspan":1},{"text":"Multiple","row":1,"col":12,"rowspan":2,"colspan":1},{"text":"Shares","row":2,"col":1,"rowspan":1,"colspan":1},{"text":"%","row":2,"col":2,"rowspan":1,"colspan":1},{"text":"Shares","row":2,"col":3,"rowspan":1,"colspan":1},{"text":"%","row":2,"col":4,"rowspan":1,"colspan":1},{"text":"$","row":2,"col":5,"rowspan":1,"colspan":1},{"text":"Shares","row":2,"col":6,"rowspan":1,"colspan":1},{"text":"%","row":2,"col":7,"rowspan":1,"colspan":1},{"text":"$","row":2,"col":8,"rowspan":1,"colspan":1},{"text":"Shares","row":2,"col":9,"rowspan":1,"colspan":1},{"text":"%","row":2,"col":10,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>请恢复 76.jpg 中“Simple Income Statement”的表头行结构。</t>
-  </si>
-  <si>
-    <t>{"row_count":2,"col_count":2,"cells":[{"text":"Income Statement:","row":0,"col":0,"rowspan":1,"colspan":1},{"text":"Year 1","row":0,"col":1,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>{"row_count":35,"col_count":3,"cells":[{"text":"Income Statement:","row":0,"col":0,"rowspan":1,"colspan":3},{"text":"Revenue:","row":1,"col":0,"rowspan":1,"colspan":1},{"text":"Year 1","row":1,"col":1,"rowspan":1,"colspan":2}]}</t>
-  </si>
-  <si>
-    <t>{"row_count":27,"col_count":2,"cells":[{"text":"Income Statement:","row":0,"col":0,"rowspan":1,"colspan":2},{"text":"Revenue:","row":1,"col":0,"rowspan":1,"colspan":1},{"text":"Year 1","row":1,"col":1,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>请恢复 77.pdf 中“Monster Beverage consolidated financial statements”的表头行结构。</t>
-  </si>
-  <si>
-    <t>{"row_count":3,"col_count":4,"cells":[{"text":"MONSTER BEVERAGE CORPORATION AND SUBSIDIARIES CONSOLIDATED BALANCE SHEETS AS OF DECEMBER 31, 2021 AND 2020 (In Thousands, Except Par Value)","row":0,"col":0,"rowspan":1,"colspan":4},{"text":"December 31, 2021","row":1,"col":1,"rowspan":1,"colspan":1},{"text":"December 31, 2020","row":1,"col":2,"rowspan":1,"colspan":1},{"text":"ASSETS","row":2,"col":0,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>{"row_count":16,"col_count":4,"cells":[{"text":"2021","row":0,"col":1,"rowspan":1,"colspan":1},{"text":"2020","row":0,"col":2,"rowspan":1,"colspan":1},{"text":"2019","row":0,"col":3,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>{"row_count":37,"col_count":3,"cells":[{"text":"","row":0,"col":0,"rowspan":1,"colspan":1},{"text":"December 31, 2021","row":0,"col":1,"rowspan":1,"colspan":1},{"text":"December 31, 2020","row":0,"col":2,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>请恢复 79.png 中“Amazon consolidated statements of cash flows”的表头行结构。</t>
-  </si>
-  <si>
-    <t>{"row_count":3,"col_count":4,"cells":[{"text":"Year Ended December 31,","row":0,"col":1,"rowspan":1,"colspan":3},{"text":"2015","row":1,"col":1,"rowspan":1,"colspan":1},{"text":"2016","row":1,"col":2,"rowspan":1,"colspan":1},{"text":"2017","row":1,"col":3,"rowspan":1,"colspan":1},{"text":"$","row":2,"col":1,"rowspan":1,"colspan":1},{"text":"$","row":2,"col":2,"rowspan":1,"colspan":1},{"text":"$","row":2,"col":3,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>{"row_count":2,"col_count":4,"cells":[{"text":"","row":0,"col":0,"rowspan":2,"colspan":1},{"text":"Year Ended December 31,","row":0,"col":1,"rowspan":1,"colspan":3},{"text":"2015","row":1,"col":1,"rowspan":1,"colspan":1},{"text":"2016","row":1,"col":2,"rowspan":1,"colspan":1},{"text":"2017","row":1,"col":3,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>{"row_count":40,"col_count":4,"cells":[{"text":"Year Ended December 31,","row":0,"col":1,"rowspan":1,"colspan":3},{"text":"2015","row":1,"col":1,"rowspan":1,"colspan":1},{"text":"2016","row":1,"col":2,"rowspan":1,"colspan":1},{"text":"2017","row":1,"col":3,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>{"row_count":40,"col_count":4,"cells":[{"text":"","row":0,"col":0,"rowspan":1,"colspan":1},{"text":"Year Ended December 31,","row":0,"col":1,"rowspan":1,"colspan":3},{"text":"","row":1,"col":0,"rowspan":1,"colspan":1},{"text":"2015","row":1,"col":1,"rowspan":1,"colspan":1},{"text":"2016","row":1,"col":2,"rowspan":1,"colspan":1},{"text":"2017","row":1,"col":3,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>请计算 2017 Sales and maturities of marketable securities 减 Purchases of marketable securities。</t>
-  </si>
-  <si>
-    <t>-3779</t>
-  </si>
-  <si>
-    <t>-3789</t>
-  </si>
-  <si>
-    <t>23765</t>
-  </si>
-  <si>
-    <t>请恢复 80.png 中 Balance 表的 Cash 行，对应在 CashFlow 表的哪一行？</t>
-  </si>
-  <si>
-    <t>Closing Cash Balance</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>请恢复 81.png 中“School board classes table”的表头行结构。</t>
-  </si>
-  <si>
-    <t>{"row_count":2,"col_count":3,"cells":[{"text":"SCHOOL","row":0,"col":0,"rowspan":1,"colspan":1},{"text":"BOARD","row":0,"col":1,"rowspan":1,"colspan":1},{"text":"CLASSES","row":0,"col":2,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>{"row_count":3,"col_count":3,"cells":[{"text":"SCHOOL","row":0,"col":0,"rowspan":1,"colspan":1},{"text":"BOARD","row":0,"col":1,"rowspan":1,"colspan":1},{"text":"CLASSES","row":0,"col":2,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>{"row_count":8,"col_count":5,"cells":[{"text":"SCHOOL","row":0,"col":0,"rowspan":1,"colspan":1},{"text":"BOARD","row":0,"col":1,"rowspan":1,"colspan":1},{"text":"CLASSES","row":0,"col":2,"rowspan":1,"colspan":3},{"text":"CLASS","row":1,"col":2,"rowspan":1,"colspan":1},{"text":"STRENGTH","row":1,"col":3,"rowspan":1,"colspan":1},{"text":"SPORTS","row":1,"col":4,"rowspan":1,"colspan":1},{"text":"CLASS","row":4,"col":2,"rowspan":1,"colspan":1},{"text":"STRENGTH","row":4,"col":3,"rowspan":1,"colspan":1},{"text":"SPORTS","row":4,"col":4,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>请恢复 82.png 中“表1-2 分部分项工程量清单及计价表（号清单）”的表头行结构。</t>
-  </si>
-  <si>
-    <t>{"row_count":3,"col_count":12,"cells":[{"text":"序号","row":0,"col":0,"rowspan":3,"colspan":1},{"text":"项目编码","row":0,"col":1,"rowspan":3,"colspan":1},{"text":"项目名称","row":0,"col":2,"rowspan":3,"colspan":1},{"text":"项目特征描述","row":0,"col":3,"rowspan":3,"colspan":1},{"text":"计量单位","row":0,"col":4,"rowspan":3,"colspan":1},{"text":"工程量","row":0,"col":5,"rowspan":3,"colspan":1},{"text":"综合单价(元)","row":0,"col":6,"rowspan":3,"colspan":1},{"text":"合价(元)","row":0,"col":7,"rowspan":3,"colspan":1},{"text":"其中","row":0,"col":8,"rowspan":1,"colspan":3},{"text":"备注","row":0,"col":11,"rowspan":3,"colspan":1},{"text":"人工费","row":1,"col":8,"rowspan":2,"colspan":1},{"text":"机械费","row":1,"col":9,"rowspan":2,"colspan":1},{"text":"管理费","row":1,"col":10,"rowspan":2,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>{"row_count":2,"col_count":12,"cells":[{"text":"序号","row":0,"col":0,"rowspan":2,"colspan":1},{"text":"项目编码","row":0,"col":1,"rowspan":2,"colspan":1},{"text":"项目名称","row":0,"col":2,"rowspan":2,"colspan":1},{"text":"项目特征描述","row":0,"col":3,"rowspan":2,"colspan":1},{"text":"计量单位","row":0,"col":4,"rowspan":2,"colspan":1},{"text":"工程量","row":0,"col":5,"rowspan":2,"colspan":1},{"text":"综合单价(元)","row":0,"col":6,"rowspan":2,"colspan":1},{"text":"合价(元)","row":0,"col":7,"rowspan":2,"colspan":1},{"text":"其中","row":0,"col":8,"rowspan":1,"colspan":3},{"text":"备注","row":0,"col":11,"rowspan":2,"colspan":1},{"text":"人工费","row":1,"col":8,"rowspan":1,"colspan":1},{"text":"机械费","row":1,"col":9,"rowspan":1,"colspan":1},{"text":"管理费","row":1,"col":10,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>{"row_count":8,"col_count":12,"cells":[{"text":"序号","row":0,"col":0,"rowspan":2,"colspan":1},{"text":"项目编码","row":0,"col":1,"rowspan":2,"colspan":1},{"text":"项目名称","row":0,"col":2,"rowspan":2,"colspan":1},{"text":"项目特征描述","row":0,"col":3,"rowspan":2,"colspan":1},{"text":"计量单位","row":0,"col":4,"rowspan":2,"colspan":1},{"text":"工程量","row":0,"col":5,"rowspan":2,"colspan":1},{"text":"综合单价(元)","row":0,"col":6,"rowspan":2,"colspan":1},{"text":"合价(元)","row":0,"col":7,"rowspan":2,"colspan":1},{"text":"其中","row":0,"col":8,"rowspan":1,"colspan":3},{"text":"备注","row":0,"col":11,"rowspan":2,"colspan":1},{"text":"人工费","row":1,"col":8,"rowspan":1,"colspan":1},{"text":"机械费","row":1,"col":9,"rowspan":1,"colspan":1},{"text":"管理费","row":1,"col":10,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>请从 82.png 的“表1-2 分部分项工程量清单及计价表（号清单）”中提取：表格标题。</t>
-  </si>
-  <si>
-    <t>表1-2 分部分项工程量清单及计价表（号清单）</t>
-  </si>
-  <si>
-    <t>表1-2 分部分项工程量清单及计价表（ 号清单）</t>
-  </si>
-  <si>
-    <t>表1-2 分部分项工程量清单及计价表(号清单)</t>
-  </si>
-  <si>
-    <t>请计算序号24、25、26、27 四行合价合计。</t>
-  </si>
-  <si>
-    <t>10260</t>
-  </si>
-  <si>
-    <t>12786</t>
-  </si>
-  <si>
-    <t>12586</t>
-  </si>
-  <si>
-    <t>请恢复 83.png 中“The Error Rate on Different Forms”的表头行结构。</t>
-  </si>
-  <si>
-    <t>{"row_count":9,"col_count":7,"cells":[{"text":"Form name","row":0,"col":0,"rowspan":2,"colspan":1},{"text":"A","row":0,"col":1,"rowspan":2,"colspan":1},{"text":"B","row":0,"col":2,"rowspan":2,"colspan":1},{"text":"Total fields (X = A × B)","row":0,"col":3,"rowspan":2,"colspan":1},{"text":"Fields with errors (Y)","row":0,"col":4,"rowspan":2,"colspan":1},{"text":"Error rate* (Y/X) × 100 (%)","row":0,"col":5,"rowspan":1,"colspan":2},{"text":"X/Y","row":1,"col":5,"rowspan":1,"colspan":1},{"text":"%age","row":1,"col":6,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>{"row_count":3,"col_count":7,"cells":[{"text":"The Error Rate on Different Forms","row":0,"col":0,"rowspan":1,"colspan":7},{"text":"Form name","row":1,"col":0,"rowspan":2,"colspan":1},{"text":"A","row":1,"col":1,"rowspan":2,"colspan":1},{"text":"B","row":1,"col":2,"rowspan":2,"colspan":1},{"text":"Total fields (X = A × B)","row":1,"col":3,"rowspan":2,"colspan":1},{"text":"Fields with errors (Y)","row":1,"col":4,"rowspan":2,"colspan":1},{"text":"Error rate (Y/X) × 100 (%)","row":1,"col":5,"rowspan":1,"colspan":2},{"text":"X/Y","row":2,"col":5,"rowspan":1,"colspan":1},{"text":"%age","row":2,"col":6,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>{"row_count":11,"col_count":7,"cells":[{"text":"Form name","row":1,"col":0,"rowspan":2,"colspan":1},{"text":"A","row":1,"col":1,"rowspan":2,"colspan":1},{"text":"B","row":1,"col":2,"rowspan":2,"colspan":1},{"text":"Total fields (X = A × B)","row":1,"col":3,"rowspan":2,"colspan":1},{"text":"Fields with errors (Y)","row":1,"col":4,"rowspan":2,"colspan":1},{"text":"Error rate* (Y/X) × 100 (%)","row":1,"col":5,"rowspan":1,"colspan":2},{"text":"X/Y","row":2,"col":5,"rowspan":1,"colspan":1},{"text":"%age","row":2,"col":6,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>{"row_count":12,"col_count":7,"cells":[{"text":"Form name","row":1,"col":0,"rowspan":2,"colspan":1},{"text":"A","row":1,"col":1,"rowspan":2,"colspan":1},{"text":"B","row":1,"col":2,"rowspan":2,"colspan":1},{"text":"Total fields (X = A × B)","row":1,"col":3,"rowspan":2,"colspan":1},{"text":"Fields with errors (Y)","row":1,"col":4,"rowspan":2,"colspan":1},{"text":"Error rate* (Y/X) × 100 (%)","row":1,"col":5,"rowspan":1,"colspan":2},{"text":"X/Y","row":2,"col":5,"rowspan":1,"colspan":1},{"text":"%age","row":2,"col":6,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>请恢复 84.png 中“Catalog of chemicals”的表头行结构。</t>
-  </si>
-  <si>
-    <t>{"row_count":15,"col_count":12,"cells":[{"text":"Chemical name","row":0,"col":0,"rowspan":1,"colspan":1},{"text":"International number","row":0,"col":1,"rowspan":1,"colspan":1},{"text":"Vendor","row":0,"col":2,"rowspan":1,"colspan":1},{"text":"Resistance index","row":0,"col":3,"rowspan":1,"colspan":1},{"text":"Density","row":0,"col":4,"rowspan":1,"colspan":1},{"text":"Viscosity","row":0,"col":5,"rowspan":1,"colspan":1},{"text":"Freezing point","row":0,"col":6,"rowspan":1,"colspan":1},{"text":"Packaging","row":0,"col":7,"rowspan":1,"colspan":1},{"text":"Pack size","row":0,"col":8,"rowspan":1,"colspan":1},{"text":"Unit","row":0,"col":9,"rowspan":1,"colspan":1},{"text":"Price","row":0,"col":10,"rowspan":1,"colspan":1},{"text":"Last update","row":0,"col":11,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>{"row_count":2,"col_count":13,"cells":[{"text":"Chemical name","row":0,"col":1,"rowspan":1,"colspan":1},{"text":"International number","row":0,"col":2,"rowspan":1,"colspan":1},{"text":"Vendor","row":0,"col":3,"rowspan":1,"colspan":1},{"text":"Resistance index","row":0,"col":4,"rowspan":1,"colspan":1},{"text":"Density","row":0,"col":5,"rowspan":1,"colspan":1},{"text":"Viscosity","row":0,"col":6,"rowspan":1,"colspan":1},{"text":"Freezing point","row":0,"col":7,"rowspan":1,"colspan":1},{"text":"Packaging","row":0,"col":8,"rowspan":1,"colspan":1},{"text":"Pack size","row":0,"col":9,"rowspan":1,"colspan":1},{"text":"Unit","row":0,"col":10,"rowspan":1,"colspan":1},{"text":"Price","row":0,"col":11,"rowspan":1,"colspan":1},{"text":"Last update","row":0,"col":12,"rowspan":1,"colspan":1},{"text":"g/m³","row":1,"col":5,"rowspan":1,"colspan":1},{"text":"m²/s","row":1,"col":6,"rowspan":1,"colspan":1},{"text":"°C","row":1,"col":7,"rowspan":1,"colspan":1},{"text":"$","row":1,"col":11,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>{"row_count":16,"col_count":13,"cells":[{"text":"","row":0,"col":0,"rowspan":1,"colspan":1},{"text":"Chemical name","row":0,"col":1,"rowspan":1,"colspan":1},{"text":"International number","row":0,"col":2,"rowspan":1,"colspan":1},{"text":"Vendor","row":0,"col":3,"rowspan":1,"colspan":1},{"text":"Resistance index","row":0,"col":4,"rowspan":1,"colspan":1},{"text":"Density g/m³","row":0,"col":5,"rowspan":1,"colspan":1},{"text":"Viscosity m²/s","row":0,"col":6,"rowspan":1,"colspan":1},{"text":"Freezing point °C","row":0,"col":7,"rowspan":1,"colspan":1},{"text":"Packaging","row":0,"col":8,"rowspan":1,"colspan":1},{"text":"Pack size","row":0,"col":9,"rowspan":1,"colspan":1},{"text":"Unit","row":0,"col":10,"rowspan":1,"colspan":1},{"text":"Price $","row":0,"col":11,"rowspan":1,"colspan":1},{"text":"Last update","row":0,"col":12,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>{"row_count":17,"col_count":13,"cells":[{"text":"","row":0,"col":0,"rowspan":1,"colspan":1},{"text":"Chemical name","row":0,"col":1,"rowspan":1,"colspan":1},{"text":"International number","row":0,"col":2,"rowspan":1,"colspan":1},{"text":"Vendor","row":0,"col":3,"rowspan":1,"colspan":1},{"text":"Resistance index","row":0,"col":4,"rowspan":1,"colspan":1},{"text":"Density g/m³","row":0,"col":5,"rowspan":1,"colspan":1},{"text":"Viscosity m²/s","row":0,"col":6,"rowspan":1,"colspan":1},{"text":"Freezing point °C","row":0,"col":7,"rowspan":1,"colspan":1},{"text":"Packaging","row":0,"col":8,"rowspan":1,"colspan":1},{"text":"Pack size","row":0,"col":9,"rowspan":1,"colspan":1},{"text":"Unit","row":0,"col":10,"rowspan":1,"colspan":1},{"text":"Price $","row":0,"col":11,"rowspan":1,"colspan":1},{"text":"Last update","row":0,"col":12,"rowspan":1,"colspan":1},{"text":"","row":1,"col":0,"rowspan":1,"colspan":1},{"text":"","row":1,"col":1,"rowspan":1,"colspan":1},{"text":"","row":1,"col":2,"rowspan":1,"colspan":1},{"text":"All","row":1,"col":3,"rowspan":1,"colspan":1},{"text":"&lt; 1","row":1,"col":4,"rowspan":1,"colspan":1},{"text":"All","row":1,"col":5,"rowspan":1,"colspan":1},{"text":"All","row":1,"col":6,"rowspan":1,"colspan":1},{"text":"","row":1,"col":7,"rowspan":1,"colspan":1},{"text":"All","row":1,"col":8,"rowspan":1,"colspan":1},{"text":"","row":1,"col":9,"rowspan":1,"colspan":1},{"text":"All","row":1,"col":10,"rowspan":1,"colspan":1},{"text":"","row":1,"col":11,"rowspan":1,"colspan":1},{"text":"","row":1,"col":12,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>请找出可见行中 Resistance index 最高的化学品。</t>
-  </si>
-  <si>
-    <t>Caustic Potash</t>
-  </si>
-  <si>
-    <t>Stearalkonium Chloride</t>
-  </si>
-  <si>
-    <t>["Stearalkonium Chloride","Guar Gum"]</t>
-  </si>
-  <si>
-    <t>请恢复 88.png 中“Games by Continent”的表头行结构。</t>
-  </si>
-  <si>
-    <t>{"row_count":7,"col_count":10,"cells":[{"text":"Games by Continent","row":0,"col":0,"rowspan":1,"colspan":10},{"text":"Place","row":1,"col":1,"rowspan":1,"colspan":4},{"text":"Dates","row":1,"col":5,"rowspan":1,"colspan":4},{"text":"Season","row":3,"col":0,"rowspan":1,"colspan":1},{"text":"Number","row":3,"col":1,"rowspan":1,"colspan":1},{"text":"Flag","row":3,"col":2,"rowspan":1,"colspan":1},{"text":"City","row":3,"col":3,"rowspan":1,"colspan":1},{"text":"Country","row":3,"col":4,"rowspan":1,"colspan":1},{"text":"Year","row":3,"col":5,"rowspan":1,"colspan":1},{"text":"From","row":3,"col":6,"rowspan":1,"colspan":1},{"text":"To","row":3,"col":7,"rowspan":1,"colspan":1},{"text":"Status","row":3,"col":8,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>{"row_count":10,"col_count":9,"cells":[{"text":"Games by Continent","row":0,"col":0,"rowspan":1,"colspan":9},{"text":"","row":1,"col":0,"rowspan":1,"colspan":1},{"text":"Place","row":1,"col":1,"rowspan":1,"colspan":4},{"text":"Dates","row":1,"col":5,"rowspan":1,"colspan":3},{"text":"","row":1,"col":8,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>{"row_count":10,"col_count":9,"cells":[{"text":"Games by Continent","row":0,"col":0,"rowspan":1,"colspan":9},{"text":"","row":1,"col":0,"rowspan":1,"colspan":2},{"text":"Place","row":1,"col":2,"rowspan":1,"colspan":3},{"text":"Dates","row":1,"col":5,"rowspan":1,"colspan":3},{"text":"","row":1,"col":8,"rowspan":1,"colspan":1},{"text":"Season","row":6,"col":0,"rowspan":1,"colspan":1},{"text":"Number","row":6,"col":1,"rowspan":1,"colspan":1},{"text":"Flag","row":6,"col":2,"rowspan":1,"colspan":1},{"text":"City","row":6,"col":3,"rowspan":1,"colspan":1},{"text":"Country","row":6,"col":4,"rowspan":1,"colspan":1},{"text":"Year","row":6,"col":5,"rowspan":1,"colspan":1},{"text":"From","row":6,"col":6,"rowspan":1,"colspan":1},{"text":"To","row":6,"col":7,"rowspan":1,"colspan":1},{"text":"Status","row":6,"col":8,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>请恢复 89.png 中红色的方块一共有多少个？</t>
-  </si>
-  <si>
-    <t>{"row_count":18,"col_count":6,"cells":[{"text":"1","row":0,"col":0,"rowspan":1,"colspan":1},{"text":"","row":0,"col":1,"rowspan":1,"colspan":2},{"text":"2","row":0,"col":3,"rowspan":1,"colspan":2},{"text":"","row":1,"col":0,"rowspan":1,"colspan":1},{"text":"3","row":1,"col":1,"rowspan":1,"colspan":2},{"text":"","row":1,"col":3,"rowspan":1,"colspan":2},{"text":"4","row":2,"col":0,"rowspan":1,"colspan":4},{"text":"","row":2,"col":4,"rowspan":1,"colspan":2},{"text":"5","row":3,"col":0,"rowspan":1,"colspan":1},{"text":"","row":3,"col":1,"rowspan":1,"colspan":2},{"text":"","row":3,"col":3,"rowspan":1,"colspan":1},{"text":"","row":3,"col":4,"rowspan":1,"colspan":2},{"text":"6","row":4,"col":0,"rowspan":1,"colspan":1},{"text":"","row":4,"col":1,"rowspan":1,"colspan":2},{"text":"","row":4,"col":3,"rowspan":1,"colspan":1},{"text":"","row":4,"col":4,"rowspan":1,"colspan":2},{"text":"7","row":5,"col":0,"rowspan":3,"colspan":2},{"text":"9","row":5,"col":2,"rowspan":1,"colspan":1},{"text":"8","row":5,"col":3,"rowspan":2,"colspan":3},{"text":"10","row":6,"col":2,"rowspan":1,"colspan":1},{"text":"11","row":7,"col":0,"rowspan":1,"colspan":1},{"text":"12","row":7,"col":1,"rowspan":1,"colspan":2},{"text":"","row":7,"col":3,"rowspan":1,"colspan":1},{"text":"","row":7,"col":4,"rowspan":1,"colspan":2},{"text":"13","row":8,"col":0,"rowspan":5,"colspan":3},{"text":"","row":8,"col":3,"rowspan":1,"colspan":1},{"text":"","row":8,"col":4,"rowspan":1,"colspan":2},{"text":"14","row":9,"col":3,"rowspan":1,"colspan":1},{"text":"","row":9,"col":4,"rowspan":1,"colspan":2},{"text":"15","row":10,"col":3,"rowspan":1,"colspan":1},{"text":"","row":10,"col":4,"rowspan":1,"colspan":2},{"text":"16","row":11,"col":3,"rowspan":2,"colspan":2},{"text":"","row":11,"col":5,"rowspan":1,"colspan":1},{"text":"17","row":12,"col":0,"rowspan":1,"colspan":1},{"text":"","row":12,"col":1,"rowspan":1,"colspan":2},{"text":"","row":12,"col":3,"rowspan":1,"colspan":2},{"text":"18","row":13,"col":0,"rowspan":1,"colspan":6}]}</t>
-  </si>
-  <si>
-    <t>{"row_count":18,"col_count":8,"cells":[{"text":"1","row":0,"col":0,"rowspan":2,"colspan":1},{"text":"","row":0,"col":1,"rowspan":1,"colspan":1},{"text":"2","row":0,"col":2,"rowspan":1,"colspan":1},{"text":"","row":0,"col":3,"rowspan":1,"colspan":1},{"text":"","row":0,"col":4,"rowspan":2,"colspan":1},{"text":"","row":0,"col":5,"rowspan":1,"colspan":1},{"text":"","row":0,"col":6,"rowspan":1,"colspan":1},{"text":"","row":0,"col":7,"rowspan":1,"colspan":1},{"text":"","row":1,"col":1,"rowspan":1,"colspan":1},{"text":"3","row":1,"col":2,"rowspan":1,"colspan":1},{"text":"","row":1,"col":3,"rowspan":1,"colspan":1},{"text":"","row":1,"col":5,"rowspan":1,"colspan":1},{"text":"","row":1,"col":6,"rowspan":1,"colspan":1},{"text":"","row":1,"col":7,"rowspan":1,"colspan":1},{"text":"4","row":2,"col":0,"rowspan":1,"colspan":1},{"text":"","row":2,"col":1,"rowspan":1,"colspan":2},{"text":"","row":2,"col":3,"rowspan":1,"colspan":4},{"text":"","row":2,"col":7,"rowspan":2,"colspan":1},{"text":"5","row":3,"col":0,"rowspan":1,"colspan":1},{"text":"","row":3,"col":1,"rowspan":1,"colspan":2},{"text":"","row":3,"col":3,"rowspan":2,"colspan":1},{"text":"","row":3,"col":4,"rowspan":1,"colspan":3},{"text":"6","row":4,"col":0,"rowspan":1,"colspan":1},{"text":"","row":4,"col":1,"rowspan":1,"colspan":2},{"text":"","row":4,"col":4,"rowspan":1,"colspan":4},{"text":"7","row":5,"col":0,"rowspan":5,"colspan":1},{"text":"","row":5,"col":1,"rowspan":3,"colspan":2},{"text":"","row":5,"col":3,"rowspan":3,"colspan":5},{"text":"9","row":8,"col":1,"rowspan":1,"colspan":1},{"text":"","row":8,"col":2,"rowspan":1,"colspan":1},{"text":"8","row":8,"col":3,"rowspan":2,"colspan":1},{"text":"","row":8,"col":4,"rowspan":2,"colspan":4},{"text":"10","row":9,"col":1,"rowspan":1,"colspan":1},{"text":"","row":9,"col":2,"rowspan":1,"colspan":1},{"text":"11","row":10,"col":0,"rowspan":1,"colspan":1},{"text":"","row":10,"col":1,"rowspan":1,"colspan":5},{"text":"","row":10,"col":6,"rowspan":1,"colspan":1},{"text":"","row":10,"col":7,"rowspan":2,"colspan":1},{"text":"12","row":11,"col":0,"rowspan":1,"colspan":3},{"text":"","row":11,"col":3,"rowspan":2,"colspan":1},{"text":"","row":11,"col":4,"rowspan":1,"colspan":2},{"text":"","row":11,"col":6,"rowspan":1,"colspan":1},{"text":"13","row":12,"col":0,"rowspan":4,"colspan":3},{"text":"","row":12,"col":4,"rowspan":1,"colspan":2},{"text":"","row":12,"col":6,"rowspan":1,"colspan":1},{"text":"","row":12,"col":7,"rowspan":1,"colspan":1},{"text":"14","row":13,"col":3,"rowspan":1,"colspan":1},{"text":"","row":13,"col":4,"rowspan":1,"colspan":4},{"text":"15","row":14,"col":3,"rowspan":1,"colspan":1},{"text":"","row":14,"col":4,"rowspan":1,"colspan":4},{"text":"16","row":15,"col":3,"rowspan":2,"colspan":1},{"text":"","row":15,"col":4,"rowspan":1,"colspan":4},{"text":"17","row":16,"col":0,"rowspan":1,"colspan":1},{"text":"","row":16,"col":1,"rowspan":1,"colspan":2},{"text":"","row":16,"col":4,"rowspan":1,"colspan":4},{"text":"18","row":17,"col":0,"rowspan":1,"colspan":1},{"text":"","row":17,"col":1,"rowspan":1,"colspan":7}]}</t>
-  </si>
-  <si>
-    <t>{"row_count":17,"col_count":7,"cells":[{"text":"1","row":0,"col":0,"rowspan":3,"colspan":1},{"text":"","row":0,"col":1,"rowspan":2,"colspan":1},{"text":"","row":0,"col":2,"rowspan":1,"colspan":2},{"text":"","row":0,"col":4,"rowspan":3,"colspan":1},{"text":"","row":0,"col":5,"rowspan":1,"colspan":2},{"text":"8","row":7,"col":3,"rowspan":2,"colspan":1},{"text":"","row":7,"col":4,"rowspan":2,"colspan":3},{"text":"15","row":13,"col":3,"rowspan":1,"colspan":1},{"text":"","row":13,"col":4,"rowspan":1,"colspan":1},{"text":"","row":13,"col":5,"rowspan":2,"colspan":2}]}</t>
-  </si>
-  <si>
-    <t>{"row_count":18,"col_count":7,"cells":[{"text":"1","row":0,"col":0,"rowspan":3,"colspan":1},{"text":"","row":0,"col":1,"rowspan":2,"colspan":1},{"text":"","row":0,"col":2,"rowspan":1,"colspan":2},{"text":"","row":0,"col":4,"rowspan":3,"colspan":1},{"text":"","row":0,"col":5,"rowspan":1,"colspan":2},{"text":"8","row":8,"col":3,"rowspan":3,"colspan":1},{"text":"","row":8,"col":4,"rowspan":3,"colspan":3},{"text":"15","row":15,"col":3,"rowspan":1,"colspan":1},{"text":"","row":15,"col":4,"rowspan":1,"colspan":1},{"text":"","row":15,"col":5,"rowspan":2,"colspan":2}]}</t>
-  </si>
-  <si>
-    <t>请从 89.png 的“colored merged-cell layout”中提取：黄色小块中位于上方的编号。</t>
-  </si>
-  <si>
-    <t>请按从上到下列出最左列可见编号。</t>
-  </si>
-  <si>
-    <t>[1,4,5,6,7,11,13,17,18]</t>
-  </si>
-  <si>
-    <t>["1","4","5","6","7","11","12","13","17","18"]</t>
-  </si>
-  <si>
-    <t>[1,4,5,6,7,11,12,13,17,18]</t>
-  </si>
-  <si>
-    <t>请从 90.png 的“merged-cell spreadsheet example”中提取：Row 7 蓝色区域显示的文本。</t>
-  </si>
-  <si>
-    <t>Row 6</t>
-  </si>
-  <si>
-    <t>请恢复 92.jpg 中“Funnel management plan conversion rates”的表头行结构。</t>
-  </si>
-  <si>
-    <t>{"row_count":5,"col_count":12,"cells":[{"text":"Account Manager","row":0,"col":0,"rowspan":1,"colspan":1},{"text":"1","row":0,"col":1,"rowspan":1,"colspan":1},{"text":"2","row":0,"col":2,"rowspan":1,"colspan":1},{"text":"3","row":0,"col":3,"rowspan":1,"colspan":1},{"text":"4","row":0,"col":4,"rowspan":1,"colspan":1},{"text":"5","row":0,"col":5,"rowspan":1,"colspan":1},{"text":"6","row":0,"col":6,"rowspan":1,"colspan":1},{"text":"7","row":0,"col":7,"rowspan":1,"colspan":1},{"text":"8","row":0,"col":8,"rowspan":1,"colspan":1},{"text":"9","row":0,"col":9,"rowspan":1,"colspan":1},{"text":"10","row":0,"col":10,"rowspan":1,"colspan":1},{"text":"11","row":0,"col":11,"rowspan":1,"colspan":1},{"text":"ANNUAL TARGET","row":1,"col":0,"rowspan":1,"colspan":1},{"text":"AVG CONTRACT VALUE (CURRENT AVG VALUE)","row":1,"col":1,"rowspan":1,"colspan":1},{"text":"NO. OF CONTRACTS REQUIRED","row":1,"col":2,"rowspan":1,"colspan":1},{"text":"TOTAL MEETINGS TO BE DONE PER MONTH","row":1,"col":3,"rowspan":1,"colspan":1},{"text":"DISCUSSION TO PROPOSAL CONVERSION RATIO (CURRENT RATIO)","row":1,"col":4,"rowspan":1,"colspan":1},{"text":"# PROPOSALS TO BE GENERATED PER MONTH","row":1,"col":5,"rowspan":1,"colspan":1},{"text":"PIPELINE VALUE PER MONTH","row":1,"col":6,"rowspan":1,"colspan":1},{"text":"PROPOSAL TO ORDERBOOK (CURRENT RATIO)","row":1,"col":7,"rowspan":1,"colspan":1},{"text":"# CONTRACTS GENERATED PER MONTH","row":1,"col":8,"rowspan":1,"colspan":1},{"text":"ORDER BOOK VALUE GENERATED PER MONTH","row":1,"col":9,"rowspan":1,"colspan":1},{"text":"AVG TARGET PER MONTH","row":1,"col":10,"rowspan":1,"colspan":1},{"text":"SHORTFALL / SURPLUS","row":1,"col":11,"rowspan":1,"colspan":1},{"text":"DATA FROM","row":2,"col":0,"rowspan":1,"colspan":1},{"text":"TARGET SHEET","row":2,"col":1,"rowspan":1,"colspan":1},{"text":"APRIL TO JAN CONTRACT AVG","row":2,"col":2,"rowspan":1,"colspan":1},{"text":"STEP 1 / STEP 2","row":2,"col":3,"rowspan":1,"colspan":1},{"text":"ACCOUNT MANAGEMENT PLAN","row":2,"col":4,"rowspan":1,"colspan":1},{"text":"YTD DAILY ACTIVITY REPORT (PROPOSAL / DISCUSSION %)","row":2,"col":5,"rowspan":1,"colspan":1},{"text":"STEP 4 * STEP 5","row":2,"col":6,"rowspan":1,"colspan":1},{"text":"STEP 6 * STEP 2","row":2,"col":7,"rowspan":1,"colspan":1},{"text":"YTD DAILY ACTIVITY REPORT (PROPOSAL / BUSINESS GENERATED %)","row":2,"col":8,"rowspan":1,"colspan":1},{"text":"STEP 6 * STEP 8","row":2,"col":9,"rowspan":1,"colspan":1},{"text":"STEP 9 * STEP 2","row":2,"col":10,"rowspan":1,"colspan":1},{"text":"STEP 11 / 12","row":2,"col":11,"rowspan":1,"colspan":1},{"text":"2016-17","row":3,"col":0,"rowspan":1,"colspan":1},{"text":"16000000","row":3,"col":1,"rowspan":1,"colspan":1},{"text":"214500","row":3,"col":2,"rowspan":1,"colspan":1},{"text":"75","row":3,"col":3,"rowspan":1,"colspan":1},{"text":"19","row":3,"col":4,"rowspan":1,"colspan":1},{"text":"13%","row":3,"col":5,"rowspan":1,"colspan":1},{"text":"2","row":3,"col":6,"rowspan":1,"colspan":1},{"text":"535113","row":3,"col":7,"rowspan":1,"colspan":1},{"text":"42%","row":3,"col":8,"rowspan":1,"colspan":1},{"text":"1.05","row":3,"col":9,"rowspan":1,"colspan":1},{"text":"224426","row":3,"col":10,"rowspan":1,"colspan":1},{"text":"1333333","row":3,"col":11,"rowspan":1,"colspan":1},{"text":"Rework","row":4,"col":0,"rowspan":1,"colspan":1},{"text":"16000000","row":4,"col":1,"rowspan":1,"colspan":1},{"text":"500000","row":4,"col":2,"rowspan":1,"colspan":1},{"text":"32","row":4,"col":3,"rowspan":1,"colspan":1},{"text":"30","row":4,"col":4,"rowspan":1,"colspan":1},{"text":"25%","row":4,"col":5,"rowspan":1,"colspan":1},{"text":"8","row":4,"col":6,"rowspan":1,"colspan":1},{"text":"3750000","row":4,"col":7,"rowspan":1,"colspan":1},{"text":"90%","row":4,"col":8,"rowspan":1,"colspan":1},{"text":"6.75","row":4,"col":9,"rowspan":1,"colspan":1},{"text":"3375000","row":4,"col":10,"rowspan":1,"colspan":1},{"text":"1333333","row":4,"col":11,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>{"row_count":3,"col_count":13,"cells":[{"text":"FUNNEL MANAGEMENT PLAN BASED ON INDIVIDUAL CONVERSION RATES","row":0,"col":0,"rowspan":1,"colspan":13},{"text":"Account Manager","row":1,"col":0,"rowspan":1,"colspan":2},{"text":"Debjit Mukherjee","row":1,"col":2,"rowspan":1,"colspan":11},{"text":"1","row":2,"col":0,"rowspan":1,"colspan":1},{"text":"2","row":2,"col":1,"rowspan":1,"colspan":1},{"text":"3","row":2,"col":2,"rowspan":1,"colspan":1},{"text":"4","row":2,"col":3,"rowspan":1,"colspan":1},{"text":"5","row":2,"col":4,"rowspan":1,"colspan":1},{"text":"6","row":2,"col":5,"rowspan":1,"colspan":1},{"text":"7","row":2,"col":6,"rowspan":1,"colspan":1},{"text":"8","row":2,"col":7,"rowspan":1,"colspan":1},{"text":"9","row":2,"col":8,"rowspan":1,"colspan":1},{"text":"10","row":2,"col":9,"rowspan":1,"colspan":1},{"text":"11","row":2,"col":10,"rowspan":1,"colspan":1},{"text":"12","row":2,"col":11,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>{"row_count":11,"col_count":13,"cells":[{"text":"FUNNEL MANAGEMENT PLAN BASED ON INDIVIDUAL CONVERSION RATES","row":0,"col":0,"rowspan":1,"colspan":13},{"text":"Account Manager","row":1,"col":0,"rowspan":1,"colspan":3},{"text":"Debajit Mukherjee","row":1,"col":3,"rowspan":1,"colspan":10},{"text":"","row":2,"col":0,"rowspan":1,"colspan":1},{"text":"1","row":2,"col":1,"rowspan":1,"colspan":1},{"text":"2","row":2,"col":2,"rowspan":1,"colspan":1},{"text":"3","row":2,"col":3,"rowspan":1,"colspan":1},{"text":"4","row":2,"col":4,"rowspan":1,"colspan":1},{"text":"5","row":2,"col":5,"rowspan":1,"colspan":1},{"text":"6","row":2,"col":6,"rowspan":1,"colspan":1},{"text":"7","row":2,"col":7,"rowspan":1,"colspan":1},{"text":"8","row":2,"col":8,"rowspan":1,"colspan":1},{"text":"9","row":2,"col":9,"rowspan":1,"colspan":1},{"text":"10","row":2,"col":10,"rowspan":1,"colspan":1},{"text":"11","row":2,"col":11,"rowspan":1,"colspan":1},{"text":"12","row":2,"col":12,"rowspan":1,"colspan":1},{"text":"","row":3,"col":0,"rowspan":1,"colspan":1},{"text":"ANNUAL TARGET","row":3,"col":1,"rowspan":1,"colspan":1},{"text":"AVG CONTRACT VALUE (CURRENT AVG VALUE)","row":3,"col":2,"rowspan":1,"colspan":1},{"text":"NO. OF CONTRACTS REQUIRED","row":3,"col":3,"rowspan":1,"colspan":1},{"text":"TOTAL MEETINGS TO BE DONE PER MONTH","row":3,"col":4,"rowspan":1,"colspan":1},{"text":"DISCUSSION TO PROPOSAL CONVERSION RATIO (CURRENT RATIO)","row":3,"col":5,"rowspan":1,"colspan":1},{"text":"# PROPOSALS TO BE GENERATED PER MONTH","row":3,"col":6,"rowspan":1,"colspan":1},{"text":"PIPELINE VALUE PER MONTH","row":3,"col":7,"rowspan":1,"colspan":1},{"text":"PROPOSAL TO ORDERBOOK (CURRENT RATIO)","row":3,"col":8,"rowspan":1,"colspan":1},{"text":"# CONTRACTS GENERATED PER MONTH","row":3,"col":9,"rowspan":1,"colspan":1},{"text":"ORDER BOOK VALUE GENERATED PER MONTH","row":3,"col":10,"rowspan":1,"colspan":1},{"text":"AVG TARGET PER MONTH","row":3,"col":11,"rowspan":1,"colspan":1},{"text":"SHORTFALL / SURPLUS","row":3,"col":12,"rowspan":1,"colspan":1},{"text":"ANNUAL","row":4,"col":0,"rowspan":1,"colspan":13},{"text":"DATA FROM","row":5,"col":0,"rowspan":1,"colspan":1},{"text":"TARGET SHEET","row":5,"col":1,"rowspan":1,"colspan":1},{"text":"APRIL TO JAN CONTRACT AVG","row":5,"col":2,"rowspan":1,"colspan":1},{"text":"STEP 1 / STEP 2","row":5,"col":3,"rowspan":1,"colspan":1},{"text":"ACCOUNT MANAGEMENT PLAN","row":5,"col":4,"rowspan":1,"colspan":1},{"text":"YTD DAILY ACTIVITY REPORT (PROPOSAL / DISCUSSION %)","row":5,"col":5,"rowspan":1,"colspan":1},{"text":"STEP 4 * STEP 5","row":5,"col":6,"rowspan":1,"colspan":1},{"text":"STEP 6 * STEP 2","row":5,"col":7,"rowspan":1,"colspan":1},{"text":"YTD DAILY ACTIVITY REPORT (PROPOSAL / BUSINESS GENERATED %)","row":5,"col":8,"rowspan":1,"colspan":1},{"text":"STEP 6 * STEP 8","row":5,"col":9,"rowspan":1,"colspan":1},{"text":"STEP 9 * STEP 2","row":5,"col":10,"rowspan":1,"colspan":1},{"text":"STEP 1 / 12","row":5,"col":11,"rowspan":1,"colspan":1},{"text":"STEP 10- STEP 11","row":5,"col":12,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>请从 92.jpg 的“Funnel management plan conversion rates”中提取：Account Manager。</t>
-  </si>
-  <si>
-    <t>Account Manager</t>
-  </si>
-  <si>
-    <t>Debash Mukherjee</t>
-  </si>
-  <si>
-    <t>Debajit Mukherjee</t>
-  </si>
-  <si>
-    <t>请恢复 93.jpg 中“ASCII Summary records table”的表头行结构。</t>
-  </si>
-  <si>
-    <t>{"row_count":5,"col_count":3,"cells":[{"text":"XXX","row":0,"col":0,"rowspan":1,"colspan":1},{"text":"Summary","row":0,"col":1,"rowspan":1,"colspan":2},{"text":"Description","row":1,"col":1,"rowspan":1,"colspan":1},{"text":"Variable Names(units)","row":1,"col":2,"rowspan":1,"colspan":1},{"text":"Note: The following records relate to first pass","row":2,"col":0,"rowspan":1,"colspan":3}]}</t>
-  </si>
-  <si>
-    <t>{"row_count":6,"col_count":3,"cells":[{"text":"XXX","row":0,"col":0,"rowspan":2,"colspan":1},{"text":"Summary","row":0,"col":1,"rowspan":1,"colspan":2},{"text":"Description","row":1,"col":1,"rowspan":1,"colspan":1},{"text":"Variable Names(units)","row":1,"col":2,"rowspan":1,"colspan":1},{"text":"Note: The following records relate to first pass","row":2,"col":0,"rowspan":1,"colspan":3}]}</t>
-  </si>
-  <si>
-    <t>{"row_count":5,"col_count":3,"cells":[{"text":"XXX","row":0,"col":0,"rowspan":2,"colspan":1},{"text":"Summary","row":0,"col":1,"rowspan":1,"colspan":2},{"text":"Description","row":1,"col":1,"rowspan":1,"colspan":1},{"text":"Variable Names(units)","row":1,"col":2,"rowspan":1,"colspan":1},{"text":"Note: The following records relate to first pass","row":2,"col":0,"rowspan":1,"colspan":3}]}</t>
-  </si>
-  <si>
-    <t>{"row_count":5,"col_count":3,"cells":[{"text":"XXX","row":0,"col":0,"rowspan":2,"colspan":1},{"text":"Summary","row":0,"col":1,"rowspan":1,"colspan":2},{"text":"Description","row":1,"col":1,"rowspan":1,"colspan":1},{"text":"Variable Names(units)","row":1,"col":2,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>请从 93.jpg 的“ASCII Summary records table”中提取：RECORDS 下 basic structure 的变量名。</t>
-  </si>
-  <si>
-    <t>["NNN","NNN1","NNN2","NNNNN2","XYZDDD","SOURCE","TARGET"]</t>
-  </si>
-  <si>
-    <t>NNN, NNN1, NNN2, NNNNNNN2, XYZDDD, SOURCE, TARGET</t>
-  </si>
-  <si>
-    <t>["NNN","NNN1","NNN2","NNNNNN2","XYZDDD","SOURCE","TARGET"]</t>
-  </si>
-  <si>
-    <t>[""]</t>
-  </si>
-  <si>
-    <t>{"row_count":39,"col_count":25,"cells":[{"text":"合金牌号","row":0,"col":0,"rowspan":4,"colspan":1},{"text":"名义化学成分","row":0,"col":1,"rowspan":4,"colspan":1},{"text":"化学成分(质量分数)/%","row":0,"col":2,"rowspan":1,"colspan":23},{"text":"主要成分","row":1,"col":2,"rowspan":1,"colspan":16},{"text":"杂质,不大于","row":1,"col":18,"rowspan":1,"colspan":7},{"text":"Ti","row":2,"col":2,"rowspan":2,"colspan":1},{"text":"Al","row":2,"col":3,"rowspan":2,"colspan":1},{"text":"Si","row":2,"col":4,"rowspan":2,"colspan":1},{"text":"V","row":2,"col":5,"rowspan":2,"colspan":1},{"text":"Mn","row":2,"col":6,"rowspan":2,"colspan":1},{"text":"Fe","row":2,"col":7,"rowspan":2,"colspan":1},{"text":"Ni","row":2,"col":8,"rowspan":2,"colspan":1},{"text":"Cu","row":2,"col":9,"rowspan":2,"colspan":1},{"text":"Zr","row":2,"col":10,"rowspan":2,"colspan":1},{"text":"Nb","row":2,"col":11,"rowspan":2,"colspan":1},{"text":"Mo","row":2,"col":12,"rowspan":2,"colspan":1},{"text":"Ru","row":2,"col":13,"rowspan":2,"colspan":1},{"text":"Pd","row":2,"col":14,"rowspan":2,"colspan":1},{"text":"Sn","row":2,"col":15,"rowspan":2,"colspan":1},{"text":"Ta","row":2,"col":16,"rowspan":2,"colspan":1},{"text":"Nd","row":2,"col":17,"rowspan":2,"colspan":1},{"text":"Fe","row":2,"col":18,"rowspan":2,"colspan":1},{"text":"C","row":2,"col":19,"rowspan":2,"colspan":1},{"text":"N","row":2,"col":20,"rowspan":2,"colspan":1},{"text":"H","row":2,"col":21,"rowspan":2,"colspan":1},{"text":"O","row":2,"col":22,"rowspan":2,"colspan":1},{"text":"其他元素","row":2,"col":23,"rowspan":1,"colspan":2},{"text":"单一","row":3,"col":23,"rowspan":1,"colspan":1},{"text":"总和","row":3,"col":24,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>{"row_count":21,"col_count":20,"cells":[{"text":"合金牌号","row":0,"col":0,"rowspan":4,"colspan":1},{"text":"名义化学成分","row":0,"col":1,"rowspan":4,"colspan":1},{"text":"化学成分(质量分数)/%","row":0,"col":2,"rowspan":1,"colspan":18},{"text":"主要成分","row":1,"col":2,"rowspan":1,"colspan":11},{"text":"杂质,不大于","row":1,"col":13,"rowspan":1,"colspan":7},{"text":"Ti","row":2,"col":2,"rowspan":2,"colspan":1},{"text":"Al","row":2,"col":3,"rowspan":2,"colspan":1},{"text":"Si","row":2,"col":4,"rowspan":2,"colspan":1},{"text":"V","row":2,"col":5,"rowspan":2,"colspan":1},{"text":"Cr","row":2,"col":6,"rowspan":2,"colspan":1},{"text":"Fe","row":2,"col":7,"rowspan":2,"colspan":1},{"text":"Zr","row":2,"col":8,"rowspan":2,"colspan":1},{"text":"Nb","row":2,"col":9,"rowspan":2,"colspan":1},{"text":"Mo","row":2,"col":10,"rowspan":2,"colspan":1},{"text":"Pd","row":2,"col":11,"rowspan":2,"colspan":1},{"text":"Sn","row":2,"col":12,"rowspan":2,"colspan":1},{"text":"Fe","row":2,"col":13,"rowspan":2,"colspan":1},{"text":"C","row":2,"col":14,"rowspan":2,"colspan":1},{"text":"N","row":2,"col":15,"rowspan":2,"colspan":1},{"text":"H","row":2,"col":16,"rowspan":2,"colspan":1},{"text":"O","row":2,"col":17,"rowspan":2,"colspan":1},{"text":"其他元素","row":2,"col":18,"rowspan":1,"colspan":2},{"text":"单一","row":3,"col":18,"rowspan":1,"colspan":1},{"text":"总和","row":3,"col":19,"rowspan":1,"colspan":1}]}</t>
-  </si>
-  <si>
-    <t>["营业成本","税金及附加","销售费用","管理费用","研发费用","财务费用","其他收益","投资收益(损失以\"-\"号填列)","净敞口套期收益(损失以\"-\"号填列)","公允价值变动收益(损失以\"-\"号填列)","信用减值损失(损失以\"-\"号填列)","资产减值损失(损失以\"-\"号填列)","资产处置收益(损失以\"-\"号填列)"]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6343,7 +6344,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G498"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -16317,7 +16318,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G856"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -16702,7 +16703,7 @@
         <v>903</v>
       </c>
       <c r="F19" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -33454,7 +33455,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F517"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -39090,7 +39091,7 @@
         <v>899</v>
       </c>
       <c r="F282" t="s">
-        <v>1783</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
@@ -39110,7 +39111,7 @@
         <v>901</v>
       </c>
       <c r="F283" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
@@ -39130,7 +39131,7 @@
         <v>903</v>
       </c>
       <c r="F284" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
@@ -39150,7 +39151,7 @@
         <v>1559</v>
       </c>
       <c r="F285" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
@@ -39250,7 +39251,7 @@
         <v>899</v>
       </c>
       <c r="F290" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -39270,7 +39271,7 @@
         <v>901</v>
       </c>
       <c r="F291" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
@@ -39290,7 +39291,7 @@
         <v>903</v>
       </c>
       <c r="F292" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -39310,7 +39311,7 @@
         <v>1559</v>
       </c>
       <c r="F293" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -39350,7 +39351,7 @@
         <v>901</v>
       </c>
       <c r="F295" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -39490,7 +39491,7 @@
         <v>899</v>
       </c>
       <c r="F302" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
@@ -39510,7 +39511,7 @@
         <v>901</v>
       </c>
       <c r="F303" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
@@ -39530,7 +39531,7 @@
         <v>903</v>
       </c>
       <c r="F304" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
@@ -39550,7 +39551,7 @@
         <v>1559</v>
       </c>
       <c r="F305" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
@@ -39570,7 +39571,7 @@
         <v>899</v>
       </c>
       <c r="F306" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
@@ -39590,7 +39591,7 @@
         <v>901</v>
       </c>
       <c r="F307" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
@@ -39610,7 +39611,7 @@
         <v>903</v>
       </c>
       <c r="F308" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
@@ -39630,7 +39631,7 @@
         <v>1559</v>
       </c>
       <c r="F309" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
@@ -39644,13 +39645,13 @@
         <v>8</v>
       </c>
       <c r="D310" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="E310" t="s">
         <v>899</v>
       </c>
       <c r="F310" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
@@ -39664,13 +39665,13 @@
         <v>8</v>
       </c>
       <c r="D311" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="E311" t="s">
         <v>901</v>
       </c>
       <c r="F311" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
@@ -39684,13 +39685,13 @@
         <v>8</v>
       </c>
       <c r="D312" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="E312" t="s">
         <v>903</v>
       </c>
       <c r="F312" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
@@ -39704,13 +39705,13 @@
         <v>8</v>
       </c>
       <c r="D313" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="E313" t="s">
         <v>1559</v>
       </c>
       <c r="F313" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
@@ -39724,13 +39725,13 @@
         <v>11</v>
       </c>
       <c r="D314" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="E314" t="s">
         <v>899</v>
       </c>
       <c r="F314" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
@@ -39744,13 +39745,13 @@
         <v>11</v>
       </c>
       <c r="D315" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="E315" t="s">
         <v>901</v>
       </c>
       <c r="F315" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
@@ -39764,13 +39765,13 @@
         <v>11</v>
       </c>
       <c r="D316" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="E316" t="s">
         <v>903</v>
       </c>
       <c r="F316" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
@@ -39784,13 +39785,13 @@
         <v>11</v>
       </c>
       <c r="D317" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="E317" t="s">
         <v>1559</v>
       </c>
       <c r="F317" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
@@ -39804,7 +39805,7 @@
         <v>8</v>
       </c>
       <c r="D318" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="E318" t="s">
         <v>899</v>
@@ -39824,7 +39825,7 @@
         <v>8</v>
       </c>
       <c r="D319" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="E319" t="s">
         <v>901</v>
@@ -39844,7 +39845,7 @@
         <v>8</v>
       </c>
       <c r="D320" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="E320" t="s">
         <v>903</v>
@@ -39864,7 +39865,7 @@
         <v>8</v>
       </c>
       <c r="D321" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="E321" t="s">
         <v>1559</v>
@@ -39910,7 +39911,7 @@
         <v>901</v>
       </c>
       <c r="F323" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
@@ -39970,7 +39971,7 @@
         <v>899</v>
       </c>
       <c r="F326" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
@@ -39990,7 +39991,7 @@
         <v>901</v>
       </c>
       <c r="F327" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
@@ -40010,7 +40011,7 @@
         <v>903</v>
       </c>
       <c r="F328" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
@@ -40030,7 +40031,7 @@
         <v>1559</v>
       </c>
       <c r="F329" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
@@ -40044,13 +40045,13 @@
         <v>897</v>
       </c>
       <c r="D330" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="E330" t="s">
         <v>899</v>
       </c>
       <c r="F330" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
@@ -40064,13 +40065,13 @@
         <v>897</v>
       </c>
       <c r="D331" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="E331" t="s">
         <v>901</v>
       </c>
       <c r="F331" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
@@ -40084,13 +40085,13 @@
         <v>897</v>
       </c>
       <c r="D332" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="E332" t="s">
         <v>903</v>
       </c>
       <c r="F332" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
@@ -40104,13 +40105,13 @@
         <v>897</v>
       </c>
       <c r="D333" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="E333" t="s">
         <v>1559</v>
       </c>
       <c r="F333" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
@@ -40124,13 +40125,13 @@
         <v>8</v>
       </c>
       <c r="D334" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="E334" t="s">
         <v>899</v>
       </c>
       <c r="F334" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
@@ -40144,13 +40145,13 @@
         <v>8</v>
       </c>
       <c r="D335" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="E335" t="s">
         <v>901</v>
       </c>
       <c r="F335" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
@@ -40164,13 +40165,13 @@
         <v>8</v>
       </c>
       <c r="D336" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="E336" t="s">
         <v>903</v>
       </c>
       <c r="F336" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
@@ -40184,13 +40185,13 @@
         <v>8</v>
       </c>
       <c r="D337" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="E337" t="s">
         <v>1559</v>
       </c>
       <c r="F337" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
@@ -40204,13 +40205,13 @@
         <v>897</v>
       </c>
       <c r="D338" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="E338" t="s">
         <v>899</v>
       </c>
       <c r="F338" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
@@ -40224,13 +40225,13 @@
         <v>897</v>
       </c>
       <c r="D339" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="E339" t="s">
         <v>901</v>
       </c>
       <c r="F339" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
@@ -40244,13 +40245,13 @@
         <v>897</v>
       </c>
       <c r="D340" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="E340" t="s">
         <v>903</v>
       </c>
       <c r="F340" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
@@ -40264,13 +40265,13 @@
         <v>897</v>
       </c>
       <c r="D341" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="E341" t="s">
         <v>1559</v>
       </c>
       <c r="F341" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
@@ -40284,13 +40285,13 @@
         <v>8</v>
       </c>
       <c r="D342" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="E342" t="s">
         <v>899</v>
       </c>
       <c r="F342" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
@@ -40304,13 +40305,13 @@
         <v>8</v>
       </c>
       <c r="D343" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="E343" t="s">
         <v>901</v>
       </c>
       <c r="F343" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
@@ -40324,13 +40325,13 @@
         <v>8</v>
       </c>
       <c r="D344" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="E344" t="s">
         <v>903</v>
       </c>
       <c r="F344" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
@@ -40344,13 +40345,13 @@
         <v>8</v>
       </c>
       <c r="D345" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="E345" t="s">
         <v>1559</v>
       </c>
       <c r="F345" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
@@ -40364,13 +40365,13 @@
         <v>11</v>
       </c>
       <c r="D346" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="E346" t="s">
         <v>899</v>
       </c>
       <c r="F346" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
@@ -40384,13 +40385,13 @@
         <v>11</v>
       </c>
       <c r="D347" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="E347" t="s">
         <v>901</v>
       </c>
       <c r="F347" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
@@ -40404,13 +40405,13 @@
         <v>11</v>
       </c>
       <c r="D348" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="E348" t="s">
         <v>903</v>
       </c>
       <c r="F348" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
@@ -40424,13 +40425,13 @@
         <v>11</v>
       </c>
       <c r="D349" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="E349" t="s">
         <v>1559</v>
       </c>
       <c r="F349" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
@@ -40444,13 +40445,13 @@
         <v>8</v>
       </c>
       <c r="D350" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="E350" t="s">
         <v>899</v>
       </c>
       <c r="F350" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
@@ -40464,13 +40465,13 @@
         <v>8</v>
       </c>
       <c r="D351" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="E351" t="s">
         <v>901</v>
       </c>
       <c r="F351" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
@@ -40484,13 +40485,13 @@
         <v>8</v>
       </c>
       <c r="D352" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="E352" t="s">
         <v>903</v>
       </c>
       <c r="F352" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
@@ -40504,13 +40505,13 @@
         <v>8</v>
       </c>
       <c r="D353" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="E353" t="s">
         <v>1559</v>
       </c>
       <c r="F353" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
@@ -40524,13 +40525,13 @@
         <v>11</v>
       </c>
       <c r="D354" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="E354" t="s">
         <v>899</v>
       </c>
       <c r="F354" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
@@ -40544,7 +40545,7 @@
         <v>11</v>
       </c>
       <c r="D355" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="E355" t="s">
         <v>901</v>
@@ -40564,7 +40565,7 @@
         <v>11</v>
       </c>
       <c r="D356" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="E356" t="s">
         <v>903</v>
@@ -40584,7 +40585,7 @@
         <v>11</v>
       </c>
       <c r="D357" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="E357" t="s">
         <v>1559</v>
@@ -40604,13 +40605,13 @@
         <v>11</v>
       </c>
       <c r="D358" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="E358" t="s">
         <v>899</v>
       </c>
       <c r="F358" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.25">
@@ -40624,13 +40625,13 @@
         <v>11</v>
       </c>
       <c r="D359" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="E359" t="s">
         <v>901</v>
       </c>
       <c r="F359" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.25">
@@ -40644,13 +40645,13 @@
         <v>11</v>
       </c>
       <c r="D360" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="E360" t="s">
         <v>903</v>
       </c>
       <c r="F360" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.25">
@@ -40664,13 +40665,13 @@
         <v>11</v>
       </c>
       <c r="D361" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="E361" t="s">
         <v>1559</v>
       </c>
       <c r="F361" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.25">
@@ -40684,13 +40685,13 @@
         <v>897</v>
       </c>
       <c r="D362" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="E362" t="s">
         <v>899</v>
       </c>
       <c r="F362" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.25">
@@ -40704,13 +40705,13 @@
         <v>897</v>
       </c>
       <c r="D363" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="E363" t="s">
         <v>901</v>
       </c>
       <c r="F363" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.25">
@@ -40724,13 +40725,13 @@
         <v>897</v>
       </c>
       <c r="D364" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="E364" t="s">
         <v>903</v>
       </c>
       <c r="F364" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.25">
@@ -40744,13 +40745,13 @@
         <v>897</v>
       </c>
       <c r="D365" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="E365" t="s">
         <v>1559</v>
       </c>
       <c r="F365" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.25">
@@ -40764,13 +40765,13 @@
         <v>11</v>
       </c>
       <c r="D366" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
       <c r="E366" t="s">
         <v>899</v>
       </c>
       <c r="F366" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.25">
@@ -40784,13 +40785,13 @@
         <v>11</v>
       </c>
       <c r="D367" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
       <c r="E367" t="s">
         <v>901</v>
       </c>
       <c r="F367" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.25">
@@ -40804,13 +40805,13 @@
         <v>11</v>
       </c>
       <c r="D368" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
       <c r="E368" t="s">
         <v>903</v>
       </c>
       <c r="F368" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.25">
@@ -40824,13 +40825,13 @@
         <v>11</v>
       </c>
       <c r="D369" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
       <c r="E369" t="s">
         <v>1559</v>
       </c>
       <c r="F369" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.25">
@@ -40844,13 +40845,13 @@
         <v>897</v>
       </c>
       <c r="D370" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="E370" t="s">
         <v>899</v>
       </c>
       <c r="F370" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.25">
@@ -40864,13 +40865,13 @@
         <v>897</v>
       </c>
       <c r="D371" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="E371" t="s">
         <v>901</v>
       </c>
       <c r="F371" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.25">
@@ -40884,13 +40885,13 @@
         <v>897</v>
       </c>
       <c r="D372" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="E372" t="s">
         <v>903</v>
       </c>
       <c r="F372" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.25">
@@ -40904,13 +40905,13 @@
         <v>897</v>
       </c>
       <c r="D373" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="E373" t="s">
         <v>1559</v>
       </c>
       <c r="F373" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.25">
@@ -40924,13 +40925,13 @@
         <v>8</v>
       </c>
       <c r="D374" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="E374" t="s">
         <v>899</v>
       </c>
       <c r="F374" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.25">
@@ -40944,13 +40945,13 @@
         <v>8</v>
       </c>
       <c r="D375" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="E375" t="s">
         <v>901</v>
       </c>
       <c r="F375" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.25">
@@ -40964,13 +40965,13 @@
         <v>8</v>
       </c>
       <c r="D376" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="E376" t="s">
         <v>903</v>
       </c>
       <c r="F376" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.25">
@@ -40984,13 +40985,13 @@
         <v>8</v>
       </c>
       <c r="D377" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="E377" t="s">
         <v>1559</v>
       </c>
       <c r="F377" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.25">
@@ -41004,13 +41005,13 @@
         <v>8</v>
       </c>
       <c r="D378" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="E378" t="s">
         <v>899</v>
       </c>
       <c r="F378" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.25">
@@ -41024,13 +41025,13 @@
         <v>8</v>
       </c>
       <c r="D379" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="E379" t="s">
         <v>901</v>
       </c>
       <c r="F379" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.25">
@@ -41044,13 +41045,13 @@
         <v>8</v>
       </c>
       <c r="D380" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="E380" t="s">
         <v>903</v>
       </c>
       <c r="F380" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.25">
@@ -41064,13 +41065,13 @@
         <v>8</v>
       </c>
       <c r="D381" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="E381" t="s">
         <v>1559</v>
       </c>
       <c r="F381" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.25">
@@ -41084,13 +41085,13 @@
         <v>11</v>
       </c>
       <c r="D382" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="E382" t="s">
         <v>899</v>
       </c>
       <c r="F382" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.25">
@@ -41104,13 +41105,13 @@
         <v>11</v>
       </c>
       <c r="D383" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="E383" t="s">
         <v>901</v>
       </c>
       <c r="F383" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.25">
@@ -41124,13 +41125,13 @@
         <v>11</v>
       </c>
       <c r="D384" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="E384" t="s">
         <v>903</v>
       </c>
       <c r="F384" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.25">
@@ -41144,13 +41145,13 @@
         <v>11</v>
       </c>
       <c r="D385" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="E385" t="s">
         <v>1559</v>
       </c>
       <c r="F385" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.25">
@@ -41164,13 +41165,13 @@
         <v>8</v>
       </c>
       <c r="D386" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="E386" t="s">
         <v>899</v>
       </c>
       <c r="F386" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.25">
@@ -41184,13 +41185,13 @@
         <v>8</v>
       </c>
       <c r="D387" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="E387" t="s">
         <v>901</v>
       </c>
       <c r="F387" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.25">
@@ -41204,13 +41205,13 @@
         <v>8</v>
       </c>
       <c r="D388" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="E388" t="s">
         <v>903</v>
       </c>
       <c r="F388" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.25">
@@ -41224,13 +41225,13 @@
         <v>8</v>
       </c>
       <c r="D389" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="E389" t="s">
         <v>1559</v>
       </c>
       <c r="F389" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.25">
@@ -41244,13 +41245,13 @@
         <v>8</v>
       </c>
       <c r="D390" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="E390" t="s">
         <v>899</v>
       </c>
       <c r="F390" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.25">
@@ -41264,13 +41265,13 @@
         <v>8</v>
       </c>
       <c r="D391" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="E391" t="s">
         <v>901</v>
       </c>
       <c r="F391" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.25">
@@ -41284,13 +41285,13 @@
         <v>8</v>
       </c>
       <c r="D392" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="E392" t="s">
         <v>903</v>
       </c>
       <c r="F392" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.25">
@@ -41304,13 +41305,13 @@
         <v>8</v>
       </c>
       <c r="D393" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="E393" t="s">
         <v>1559</v>
       </c>
       <c r="F393" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.25">
@@ -41324,13 +41325,13 @@
         <v>897</v>
       </c>
       <c r="D394" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="E394" t="s">
         <v>899</v>
       </c>
       <c r="F394" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.25">
@@ -41344,13 +41345,13 @@
         <v>897</v>
       </c>
       <c r="D395" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="E395" t="s">
         <v>901</v>
       </c>
       <c r="F395" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.25">
@@ -41364,13 +41365,13 @@
         <v>897</v>
       </c>
       <c r="D396" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="E396" t="s">
         <v>903</v>
       </c>
       <c r="F396" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.25">
@@ -41384,13 +41385,13 @@
         <v>897</v>
       </c>
       <c r="D397" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="E397" t="s">
         <v>1559</v>
       </c>
       <c r="F397" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.25">
@@ -41404,7 +41405,7 @@
         <v>8</v>
       </c>
       <c r="D398" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="E398" t="s">
         <v>899</v>
@@ -41424,13 +41425,13 @@
         <v>8</v>
       </c>
       <c r="D399" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="E399" t="s">
         <v>901</v>
       </c>
       <c r="F399" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.25">
@@ -41444,13 +41445,13 @@
         <v>8</v>
       </c>
       <c r="D400" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="E400" t="s">
         <v>903</v>
       </c>
       <c r="F400" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.25">
@@ -41464,13 +41465,13 @@
         <v>8</v>
       </c>
       <c r="D401" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="E401" t="s">
         <v>1559</v>
       </c>
       <c r="F401" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.25">
@@ -41484,13 +41485,13 @@
         <v>8</v>
       </c>
       <c r="D402" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="E402" t="s">
         <v>899</v>
       </c>
       <c r="F402" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.25">
@@ -41504,13 +41505,13 @@
         <v>8</v>
       </c>
       <c r="D403" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="E403" t="s">
         <v>901</v>
       </c>
       <c r="F403" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.25">
@@ -41524,13 +41525,13 @@
         <v>8</v>
       </c>
       <c r="D404" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="E404" t="s">
         <v>903</v>
       </c>
       <c r="F404" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.25">
@@ -41544,13 +41545,13 @@
         <v>8</v>
       </c>
       <c r="D405" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="E405" t="s">
         <v>1559</v>
       </c>
       <c r="F405" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.25">
@@ -41564,13 +41565,13 @@
         <v>8</v>
       </c>
       <c r="D406" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="E406" t="s">
         <v>899</v>
       </c>
       <c r="F406" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.25">
@@ -41584,13 +41585,13 @@
         <v>8</v>
       </c>
       <c r="D407" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="E407" t="s">
         <v>901</v>
       </c>
       <c r="F407" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.25">
@@ -41604,13 +41605,13 @@
         <v>8</v>
       </c>
       <c r="D408" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="E408" t="s">
         <v>903</v>
       </c>
       <c r="F408" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.25">
@@ -41624,13 +41625,13 @@
         <v>8</v>
       </c>
       <c r="D409" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="E409" t="s">
         <v>1559</v>
       </c>
       <c r="F409" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.25">
@@ -41644,7 +41645,7 @@
         <v>8</v>
       </c>
       <c r="D410" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="E410" t="s">
         <v>899</v>
@@ -41664,7 +41665,7 @@
         <v>8</v>
       </c>
       <c r="D411" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="E411" t="s">
         <v>901</v>
@@ -41684,7 +41685,7 @@
         <v>8</v>
       </c>
       <c r="D412" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="E412" t="s">
         <v>903</v>
@@ -41704,7 +41705,7 @@
         <v>8</v>
       </c>
       <c r="D413" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="E413" t="s">
         <v>1559</v>
@@ -41724,13 +41725,13 @@
         <v>11</v>
       </c>
       <c r="D414" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="E414" t="s">
         <v>899</v>
       </c>
       <c r="F414" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.25">
@@ -41744,13 +41745,13 @@
         <v>11</v>
       </c>
       <c r="D415" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="E415" t="s">
         <v>901</v>
       </c>
       <c r="F415" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.25">
@@ -41764,13 +41765,13 @@
         <v>11</v>
       </c>
       <c r="D416" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="E416" t="s">
         <v>903</v>
       </c>
       <c r="F416" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.25">
@@ -41784,13 +41785,13 @@
         <v>11</v>
       </c>
       <c r="D417" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="E417" t="s">
         <v>1559</v>
       </c>
       <c r="F417" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.25">
@@ -41804,13 +41805,13 @@
         <v>897</v>
       </c>
       <c r="D418" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="E418" t="s">
         <v>899</v>
       </c>
       <c r="F418" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.25">
@@ -41824,13 +41825,13 @@
         <v>897</v>
       </c>
       <c r="D419" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="E419" t="s">
         <v>901</v>
       </c>
       <c r="F419" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.25">
@@ -41844,13 +41845,13 @@
         <v>897</v>
       </c>
       <c r="D420" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="E420" t="s">
         <v>903</v>
       </c>
       <c r="F420" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.25">
@@ -41864,13 +41865,13 @@
         <v>897</v>
       </c>
       <c r="D421" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="E421" t="s">
         <v>1559</v>
       </c>
       <c r="F421" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.25">
@@ -41884,13 +41885,13 @@
         <v>897</v>
       </c>
       <c r="D422" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="E422" t="s">
         <v>899</v>
       </c>
       <c r="F422" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.25">
@@ -41904,13 +41905,13 @@
         <v>897</v>
       </c>
       <c r="D423" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="E423" t="s">
         <v>901</v>
       </c>
       <c r="F423" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.25">
@@ -41924,13 +41925,13 @@
         <v>897</v>
       </c>
       <c r="D424" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="E424" t="s">
         <v>903</v>
       </c>
       <c r="F424" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.25">
@@ -41944,13 +41945,13 @@
         <v>897</v>
       </c>
       <c r="D425" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="E425" t="s">
         <v>1559</v>
       </c>
       <c r="F425" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.25">
@@ -41964,13 +41965,13 @@
         <v>897</v>
       </c>
       <c r="D426" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="E426" t="s">
         <v>899</v>
       </c>
       <c r="F426" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.25">
@@ -41984,13 +41985,13 @@
         <v>897</v>
       </c>
       <c r="D427" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="E427" t="s">
         <v>901</v>
       </c>
       <c r="F427" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.25">
@@ -42004,13 +42005,13 @@
         <v>897</v>
       </c>
       <c r="D428" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="E428" t="s">
         <v>903</v>
       </c>
       <c r="F428" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.25">
@@ -42024,13 +42025,13 @@
         <v>897</v>
       </c>
       <c r="D429" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="E429" t="s">
         <v>1559</v>
       </c>
       <c r="F429" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.25">
@@ -42044,13 +42045,13 @@
         <v>897</v>
       </c>
       <c r="D430" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="E430" t="s">
         <v>899</v>
       </c>
       <c r="F430" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.25">
@@ -42064,13 +42065,13 @@
         <v>897</v>
       </c>
       <c r="D431" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="E431" t="s">
         <v>901</v>
       </c>
       <c r="F431" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.25">
@@ -42084,13 +42085,13 @@
         <v>897</v>
       </c>
       <c r="D432" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="E432" t="s">
         <v>903</v>
       </c>
       <c r="F432" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.25">
@@ -42104,13 +42105,13 @@
         <v>897</v>
       </c>
       <c r="D433" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="E433" t="s">
         <v>1559</v>
       </c>
       <c r="F433" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.25">
@@ -42124,13 +42125,13 @@
         <v>11</v>
       </c>
       <c r="D434" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="E434" t="s">
         <v>899</v>
       </c>
       <c r="F434" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.25">
@@ -42144,13 +42145,13 @@
         <v>11</v>
       </c>
       <c r="D435" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="E435" t="s">
         <v>901</v>
       </c>
       <c r="F435" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.25">
@@ -42164,13 +42165,13 @@
         <v>11</v>
       </c>
       <c r="D436" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="E436" t="s">
         <v>903</v>
       </c>
       <c r="F436" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.25">
@@ -42184,13 +42185,13 @@
         <v>11</v>
       </c>
       <c r="D437" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="E437" t="s">
         <v>1559</v>
       </c>
       <c r="F437" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.25">
@@ -42204,7 +42205,7 @@
         <v>11</v>
       </c>
       <c r="D438" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="E438" t="s">
         <v>899</v>
@@ -42224,13 +42225,13 @@
         <v>11</v>
       </c>
       <c r="D439" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="E439" t="s">
         <v>901</v>
       </c>
       <c r="F439" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.25">
@@ -42244,13 +42245,13 @@
         <v>11</v>
       </c>
       <c r="D440" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="E440" t="s">
         <v>903</v>
       </c>
       <c r="F440" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.25">
@@ -42264,7 +42265,7 @@
         <v>11</v>
       </c>
       <c r="D441" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="E441" t="s">
         <v>1559</v>
@@ -42284,13 +42285,13 @@
         <v>897</v>
       </c>
       <c r="D442" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="E442" t="s">
         <v>899</v>
       </c>
       <c r="F442" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.25">
@@ -42304,13 +42305,13 @@
         <v>897</v>
       </c>
       <c r="D443" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="E443" t="s">
         <v>901</v>
       </c>
       <c r="F443" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.25">
@@ -42324,13 +42325,13 @@
         <v>897</v>
       </c>
       <c r="D444" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="E444" t="s">
         <v>903</v>
       </c>
       <c r="F444" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.25">
@@ -42344,13 +42345,13 @@
         <v>897</v>
       </c>
       <c r="D445" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="E445" t="s">
         <v>1559</v>
       </c>
       <c r="F445" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.25">
@@ -42364,13 +42365,13 @@
         <v>897</v>
       </c>
       <c r="D446" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="E446" t="s">
         <v>899</v>
       </c>
       <c r="F446" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.25">
@@ -42384,13 +42385,13 @@
         <v>897</v>
       </c>
       <c r="D447" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="E447" t="s">
         <v>901</v>
       </c>
       <c r="F447" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.25">
@@ -42404,13 +42405,13 @@
         <v>897</v>
       </c>
       <c r="D448" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="E448" t="s">
         <v>903</v>
       </c>
       <c r="F448" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.25">
@@ -42424,13 +42425,13 @@
         <v>897</v>
       </c>
       <c r="D449" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="E449" t="s">
         <v>1559</v>
       </c>
       <c r="F449" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.25">
@@ -42444,13 +42445,13 @@
         <v>8</v>
       </c>
       <c r="D450" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="E450" t="s">
         <v>899</v>
       </c>
       <c r="F450" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.25">
@@ -42464,13 +42465,13 @@
         <v>8</v>
       </c>
       <c r="D451" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="E451" t="s">
         <v>901</v>
       </c>
       <c r="F451" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.25">
@@ -42484,13 +42485,13 @@
         <v>8</v>
       </c>
       <c r="D452" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="E452" t="s">
         <v>903</v>
       </c>
       <c r="F452" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.25">
@@ -42504,13 +42505,13 @@
         <v>8</v>
       </c>
       <c r="D453" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="E453" t="s">
         <v>1559</v>
       </c>
       <c r="F453" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.25">
@@ -42524,13 +42525,13 @@
         <v>11</v>
       </c>
       <c r="D454" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="E454" t="s">
         <v>899</v>
       </c>
       <c r="F454" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.25">
@@ -42544,13 +42545,13 @@
         <v>11</v>
       </c>
       <c r="D455" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="E455" t="s">
         <v>901</v>
       </c>
       <c r="F455" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.25">
@@ -42564,13 +42565,13 @@
         <v>11</v>
       </c>
       <c r="D456" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="E456" t="s">
         <v>903</v>
       </c>
       <c r="F456" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.25">
@@ -42584,13 +42585,13 @@
         <v>11</v>
       </c>
       <c r="D457" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="E457" t="s">
         <v>1559</v>
       </c>
       <c r="F457" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.25">
@@ -42604,13 +42605,13 @@
         <v>897</v>
       </c>
       <c r="D458" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="E458" t="s">
         <v>899</v>
       </c>
       <c r="F458" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.25">
@@ -42624,13 +42625,13 @@
         <v>897</v>
       </c>
       <c r="D459" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="E459" t="s">
         <v>901</v>
       </c>
       <c r="F459" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.25">
@@ -42644,13 +42645,13 @@
         <v>897</v>
       </c>
       <c r="D460" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="E460" t="s">
         <v>903</v>
       </c>
       <c r="F460" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.25">
@@ -42664,13 +42665,13 @@
         <v>897</v>
       </c>
       <c r="D461" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="E461" t="s">
         <v>1559</v>
       </c>
       <c r="F461" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.25">
@@ -42684,13 +42685,13 @@
         <v>897</v>
       </c>
       <c r="D462" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="E462" t="s">
         <v>899</v>
       </c>
       <c r="F462" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.25">
@@ -42704,13 +42705,13 @@
         <v>897</v>
       </c>
       <c r="D463" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="E463" t="s">
         <v>901</v>
       </c>
       <c r="F463" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.25">
@@ -42724,13 +42725,13 @@
         <v>897</v>
       </c>
       <c r="D464" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="E464" t="s">
         <v>903</v>
       </c>
       <c r="F464" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.25">
@@ -42744,13 +42745,13 @@
         <v>897</v>
       </c>
       <c r="D465" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="E465" t="s">
         <v>1559</v>
       </c>
       <c r="F465" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.25">
@@ -42764,13 +42765,13 @@
         <v>11</v>
       </c>
       <c r="D466" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="E466" t="s">
         <v>899</v>
       </c>
       <c r="F466" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.25">
@@ -42784,13 +42785,13 @@
         <v>11</v>
       </c>
       <c r="D467" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="E467" t="s">
         <v>901</v>
       </c>
       <c r="F467" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.25">
@@ -42804,13 +42805,13 @@
         <v>11</v>
       </c>
       <c r="D468" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="E468" t="s">
         <v>903</v>
       </c>
       <c r="F468" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.25">
@@ -42824,13 +42825,13 @@
         <v>11</v>
       </c>
       <c r="D469" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="E469" t="s">
         <v>1559</v>
       </c>
       <c r="F469" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.25">
@@ -42844,13 +42845,13 @@
         <v>897</v>
       </c>
       <c r="D470" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="E470" t="s">
         <v>899</v>
       </c>
       <c r="F470" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.25">
@@ -42864,13 +42865,13 @@
         <v>897</v>
       </c>
       <c r="D471" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="E471" t="s">
         <v>901</v>
       </c>
       <c r="F471" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.25">
@@ -42884,13 +42885,13 @@
         <v>897</v>
       </c>
       <c r="D472" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="E472" t="s">
         <v>903</v>
       </c>
       <c r="F472" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.25">
@@ -42904,13 +42905,13 @@
         <v>897</v>
       </c>
       <c r="D473" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="E473" t="s">
         <v>1559</v>
       </c>
       <c r="F473" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.25">
@@ -42924,13 +42925,13 @@
         <v>11</v>
       </c>
       <c r="D474" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="E474" t="s">
         <v>899</v>
       </c>
       <c r="F474" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.25">
@@ -42944,13 +42945,13 @@
         <v>11</v>
       </c>
       <c r="D475" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="E475" t="s">
         <v>901</v>
       </c>
       <c r="F475" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.25">
@@ -42964,13 +42965,13 @@
         <v>11</v>
       </c>
       <c r="D476" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="E476" t="s">
         <v>903</v>
       </c>
       <c r="F476" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.25">
@@ -42984,13 +42985,13 @@
         <v>11</v>
       </c>
       <c r="D477" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="E477" t="s">
         <v>1559</v>
       </c>
       <c r="F477" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.25">
@@ -43004,7 +43005,7 @@
         <v>8</v>
       </c>
       <c r="D478" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="E478" t="s">
         <v>899</v>
@@ -43024,7 +43025,7 @@
         <v>8</v>
       </c>
       <c r="D479" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="E479" t="s">
         <v>901</v>
@@ -43044,7 +43045,7 @@
         <v>8</v>
       </c>
       <c r="D480" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="E480" t="s">
         <v>903</v>
@@ -43064,7 +43065,7 @@
         <v>8</v>
       </c>
       <c r="D481" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="E481" t="s">
         <v>1559</v>
@@ -43084,13 +43085,13 @@
         <v>11</v>
       </c>
       <c r="D482" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="E482" t="s">
         <v>899</v>
       </c>
       <c r="F482" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.25">
@@ -43104,13 +43105,13 @@
         <v>11</v>
       </c>
       <c r="D483" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="E483" t="s">
         <v>901</v>
       </c>
       <c r="F483" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.25">
@@ -43124,13 +43125,13 @@
         <v>11</v>
       </c>
       <c r="D484" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="E484" t="s">
         <v>903</v>
       </c>
       <c r="F484" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.25">
@@ -43144,13 +43145,13 @@
         <v>11</v>
       </c>
       <c r="D485" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="E485" t="s">
         <v>1559</v>
       </c>
       <c r="F485" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.25">
@@ -43164,13 +43165,13 @@
         <v>8</v>
       </c>
       <c r="D486" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="E486" t="s">
         <v>899</v>
       </c>
       <c r="F486" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.25">
@@ -43184,7 +43185,7 @@
         <v>8</v>
       </c>
       <c r="D487" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="E487" t="s">
         <v>901</v>
@@ -43204,7 +43205,7 @@
         <v>8</v>
       </c>
       <c r="D488" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="E488" t="s">
         <v>903</v>
@@ -43224,7 +43225,7 @@
         <v>8</v>
       </c>
       <c r="D489" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="E489" t="s">
         <v>1559</v>
@@ -43244,13 +43245,13 @@
         <v>897</v>
       </c>
       <c r="D490" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="E490" t="s">
         <v>899</v>
       </c>
       <c r="F490" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.25">
@@ -43264,13 +43265,13 @@
         <v>897</v>
       </c>
       <c r="D491" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="E491" t="s">
         <v>901</v>
       </c>
       <c r="F491" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.25">
@@ -43284,7 +43285,7 @@
         <v>897</v>
       </c>
       <c r="D492" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="E492" t="s">
         <v>903</v>
@@ -43301,13 +43302,13 @@
         <v>897</v>
       </c>
       <c r="D493" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="E493" t="s">
         <v>1559</v>
       </c>
       <c r="F493" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.25">
@@ -43321,13 +43322,13 @@
         <v>8</v>
       </c>
       <c r="D494" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="E494" t="s">
         <v>899</v>
       </c>
       <c r="F494" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.25">
@@ -43341,13 +43342,13 @@
         <v>8</v>
       </c>
       <c r="D495" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="E495" t="s">
         <v>901</v>
       </c>
       <c r="F495" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.25">
@@ -43361,13 +43362,13 @@
         <v>8</v>
       </c>
       <c r="D496" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="E496" t="s">
         <v>903</v>
       </c>
       <c r="F496" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.25">
@@ -43381,13 +43382,13 @@
         <v>8</v>
       </c>
       <c r="D497" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="E497" t="s">
         <v>1559</v>
       </c>
       <c r="F497" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.25">
@@ -43401,13 +43402,13 @@
         <v>897</v>
       </c>
       <c r="D498" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="E498" t="s">
         <v>899</v>
       </c>
       <c r="F498" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="499" spans="1:6" x14ac:dyDescent="0.25">
@@ -43421,13 +43422,13 @@
         <v>897</v>
       </c>
       <c r="D499" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="E499" t="s">
         <v>901</v>
       </c>
       <c r="F499" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="500" spans="1:6" x14ac:dyDescent="0.25">
@@ -43441,13 +43442,13 @@
         <v>897</v>
       </c>
       <c r="D500" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="E500" t="s">
         <v>903</v>
       </c>
       <c r="F500" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="501" spans="1:6" x14ac:dyDescent="0.25">
@@ -43461,13 +43462,13 @@
         <v>897</v>
       </c>
       <c r="D501" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="E501" t="s">
         <v>1559</v>
       </c>
       <c r="F501" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="502" spans="1:6" x14ac:dyDescent="0.25">
@@ -43481,13 +43482,13 @@
         <v>8</v>
       </c>
       <c r="D502" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="E502" t="s">
         <v>899</v>
       </c>
       <c r="F502" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="503" spans="1:6" x14ac:dyDescent="0.25">
@@ -43501,13 +43502,13 @@
         <v>8</v>
       </c>
       <c r="D503" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="E503" t="s">
         <v>901</v>
       </c>
       <c r="F503" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="504" spans="1:6" x14ac:dyDescent="0.25">
@@ -43521,13 +43522,13 @@
         <v>8</v>
       </c>
       <c r="D504" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="E504" t="s">
         <v>903</v>
       </c>
       <c r="F504" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="505" spans="1:6" x14ac:dyDescent="0.25">
@@ -43541,13 +43542,13 @@
         <v>8</v>
       </c>
       <c r="D505" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="E505" t="s">
         <v>1559</v>
       </c>
       <c r="F505" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="506" spans="1:6" x14ac:dyDescent="0.25">
@@ -43627,7 +43628,7 @@
         <v>1559</v>
       </c>
       <c r="F509" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="510" spans="1:6" x14ac:dyDescent="0.25">
@@ -43707,7 +43708,7 @@
         <v>1559</v>
       </c>
       <c r="F513" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="514" spans="1:6" x14ac:dyDescent="0.25">
@@ -43787,7 +43788,7 @@
         <v>1559</v>
       </c>
       <c r="F517" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
     </row>
   </sheetData>
